--- a/artfynd/A 36309-2024 artfynd.xlsx
+++ b/artfynd/A 36309-2024 artfynd.xlsx
@@ -2073,10 +2073,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120040187</v>
+        <v>120040177</v>
       </c>
       <c r="B15" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2085,25 +2085,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2113,10 +2113,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>477525</v>
+        <v>477856</v>
       </c>
       <c r="R15" t="n">
-        <v>7069106</v>
+        <v>7069020</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2149,6 +2149,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2175,7 +2180,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120040177</v>
+        <v>120040153</v>
       </c>
       <c r="B16" t="n">
         <v>57310</v>
@@ -2215,10 +2220,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>477856</v>
+        <v>477547</v>
       </c>
       <c r="R16" t="n">
-        <v>7069020</v>
+        <v>7069271</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2255,7 +2260,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2282,7 +2287,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120040153</v>
+        <v>120040170</v>
       </c>
       <c r="B17" t="n">
         <v>57310</v>
@@ -2322,10 +2327,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>477547</v>
+        <v>477755</v>
       </c>
       <c r="R17" t="n">
-        <v>7069271</v>
+        <v>7069016</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2389,7 +2394,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120040170</v>
+        <v>120040140</v>
       </c>
       <c r="B18" t="n">
         <v>57310</v>
@@ -2429,10 +2434,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>477755</v>
+        <v>477472</v>
       </c>
       <c r="R18" t="n">
-        <v>7069016</v>
+        <v>7069006</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2496,7 +2501,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120040140</v>
+        <v>120040158</v>
       </c>
       <c r="B19" t="n">
         <v>57310</v>
@@ -2536,10 +2541,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>477472</v>
+        <v>477446</v>
       </c>
       <c r="R19" t="n">
-        <v>7069006</v>
+        <v>7069039</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2576,7 +2581,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2603,10 +2608,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120040158</v>
+        <v>120040187</v>
       </c>
       <c r="B20" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2615,25 +2620,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2643,10 +2648,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>477446</v>
+        <v>477525</v>
       </c>
       <c r="R20" t="n">
-        <v>7069039</v>
+        <v>7069106</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2679,11 +2684,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -4183,10 +4183,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120040199</v>
+        <v>120040182</v>
       </c>
       <c r="B35" t="n">
-        <v>90558</v>
+        <v>57421</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4195,38 +4195,50 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1108</v>
+        <v>103031</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>477671</v>
+        <v>477760</v>
       </c>
       <c r="R35" t="n">
-        <v>7068973</v>
+        <v>7069037</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4285,10 +4297,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120040174</v>
+        <v>120040199</v>
       </c>
       <c r="B36" t="n">
-        <v>57310</v>
+        <v>90558</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4301,21 +4313,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4325,10 +4337,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>477825</v>
+        <v>477671</v>
       </c>
       <c r="R36" t="n">
-        <v>7069031</v>
+        <v>7068973</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4361,11 +4373,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4392,10 +4399,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120040182</v>
+        <v>120040174</v>
       </c>
       <c r="B37" t="n">
-        <v>57421</v>
+        <v>57310</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4404,20 +4411,20 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4425,29 +4432,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>477760</v>
+        <v>477825</v>
       </c>
       <c r="R37" t="n">
-        <v>7069037</v>
+        <v>7069031</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4480,6 +4475,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4715,10 +4715,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120040190</v>
+        <v>120040136</v>
       </c>
       <c r="B40" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4727,25 +4727,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4755,10 +4755,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>477530</v>
+        <v>477434</v>
       </c>
       <c r="R40" t="n">
-        <v>7069276</v>
+        <v>7069116</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4817,10 +4817,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120040139</v>
+        <v>120040190</v>
       </c>
       <c r="B41" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4829,25 +4829,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4857,10 +4857,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>477517</v>
+        <v>477530</v>
       </c>
       <c r="R41" t="n">
-        <v>7068992</v>
+        <v>7069276</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4893,11 +4893,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4924,7 +4919,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120040171</v>
+        <v>120040139</v>
       </c>
       <c r="B42" t="n">
         <v>57310</v>
@@ -4964,10 +4959,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>477759</v>
+        <v>477517</v>
       </c>
       <c r="R42" t="n">
-        <v>7069019</v>
+        <v>7068992</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5031,10 +5026,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120040136</v>
+        <v>120040171</v>
       </c>
       <c r="B43" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5047,21 +5042,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5071,10 +5066,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>477434</v>
+        <v>477759</v>
       </c>
       <c r="R43" t="n">
-        <v>7069116</v>
+        <v>7069019</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5107,6 +5102,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5133,10 +5133,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120040185</v>
+        <v>120040203</v>
       </c>
       <c r="B44" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5145,25 +5145,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5173,10 +5173,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>477507</v>
+        <v>477472</v>
       </c>
       <c r="R44" t="n">
-        <v>7069056</v>
+        <v>7069087</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5235,10 +5235,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120040203</v>
+        <v>120040146</v>
       </c>
       <c r="B45" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5251,21 +5251,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5275,10 +5275,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>477472</v>
+        <v>477599</v>
       </c>
       <c r="R45" t="n">
-        <v>7069087</v>
+        <v>7069105</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5311,6 +5311,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5337,7 +5342,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120040146</v>
+        <v>120040157</v>
       </c>
       <c r="B46" t="n">
         <v>57310</v>
@@ -5377,10 +5382,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>477599</v>
+        <v>477397</v>
       </c>
       <c r="R46" t="n">
-        <v>7069105</v>
+        <v>7069068</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5417,7 +5422,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5444,10 +5449,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120040157</v>
+        <v>120040185</v>
       </c>
       <c r="B47" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5456,25 +5461,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5484,10 +5489,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>477397</v>
+        <v>477507</v>
       </c>
       <c r="R47" t="n">
-        <v>7069068</v>
+        <v>7069056</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5520,11 +5525,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">

--- a/artfynd/A 36309-2024 artfynd.xlsx
+++ b/artfynd/A 36309-2024 artfynd.xlsx
@@ -4183,10 +4183,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120040182</v>
+        <v>120040199</v>
       </c>
       <c r="B35" t="n">
-        <v>57421</v>
+        <v>90558</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4195,50 +4195,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103031</v>
+        <v>1108</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>477760</v>
+        <v>477671</v>
       </c>
       <c r="R35" t="n">
-        <v>7069037</v>
+        <v>7068973</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4297,10 +4285,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120040199</v>
+        <v>120040174</v>
       </c>
       <c r="B36" t="n">
-        <v>90558</v>
+        <v>57310</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4313,21 +4301,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4337,10 +4325,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>477671</v>
+        <v>477825</v>
       </c>
       <c r="R36" t="n">
-        <v>7068973</v>
+        <v>7069031</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4373,6 +4361,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4399,10 +4392,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120040174</v>
+        <v>120040182</v>
       </c>
       <c r="B37" t="n">
-        <v>57310</v>
+        <v>57421</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4411,20 +4404,20 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4432,17 +4425,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>477825</v>
+        <v>477760</v>
       </c>
       <c r="R37" t="n">
-        <v>7069031</v>
+        <v>7069037</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4475,11 +4480,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4506,10 +4506,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120040149</v>
+        <v>120040201</v>
       </c>
       <c r="B38" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4522,21 +4522,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4546,10 +4546,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>477423</v>
+        <v>477484</v>
       </c>
       <c r="R38" t="n">
-        <v>7069180</v>
+        <v>7068927</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4582,11 +4582,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4613,10 +4608,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120040201</v>
+        <v>120040149</v>
       </c>
       <c r="B39" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4629,21 +4624,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4653,10 +4648,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>477484</v>
+        <v>477423</v>
       </c>
       <c r="R39" t="n">
-        <v>7068927</v>
+        <v>7069180</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4689,6 +4684,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">

--- a/artfynd/A 36309-2024 artfynd.xlsx
+++ b/artfynd/A 36309-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120040175</v>
+        <v>120040172</v>
       </c>
       <c r="B2" t="n">
         <v>57310</v>
@@ -708,37 +708,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477822</v>
+        <v>477777</v>
       </c>
       <c r="R2" t="n">
-        <v>7069037</v>
+        <v>7069022</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -771,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120040144</v>
+        <v>120040145</v>
       </c>
       <c r="B3" t="n">
         <v>57310</v>
@@ -837,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477644</v>
+        <v>477626</v>
       </c>
       <c r="R3" t="n">
-        <v>7069114</v>
+        <v>7069105</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -904,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120040148</v>
+        <v>120040191</v>
       </c>
       <c r="B4" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,25 +901,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -944,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477438</v>
+        <v>477440</v>
       </c>
       <c r="R4" t="n">
-        <v>7069178</v>
+        <v>7069251</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,11 +965,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120040168</v>
+        <v>120040146</v>
       </c>
       <c r="B5" t="n">
         <v>57310</v>
@@ -1051,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477664</v>
+        <v>477599</v>
       </c>
       <c r="R5" t="n">
-        <v>7068971</v>
+        <v>7069105</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,7 +1071,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1118,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120040173</v>
+        <v>120040199</v>
       </c>
       <c r="B6" t="n">
-        <v>57310</v>
+        <v>90558</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1158,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477786</v>
+        <v>477671</v>
       </c>
       <c r="R6" t="n">
-        <v>7069029</v>
+        <v>7068973</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,11 +1174,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1225,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120040167</v>
+        <v>120040180</v>
       </c>
       <c r="B7" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1241,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1265,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477641</v>
+        <v>477415</v>
       </c>
       <c r="R7" t="n">
-        <v>7068958</v>
+        <v>7069070</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1301,11 +1276,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack ganska färska</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1332,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120040179</v>
+        <v>120040200</v>
       </c>
       <c r="B8" t="n">
-        <v>79608</v>
+        <v>90580</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1348,21 +1318,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1372,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477437</v>
+        <v>477439</v>
       </c>
       <c r="R8" t="n">
-        <v>7068991</v>
+        <v>7069086</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1434,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120040183</v>
+        <v>120040204</v>
       </c>
       <c r="B9" t="n">
-        <v>57421</v>
+        <v>78526</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1446,50 +1416,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>477821</v>
+        <v>477534</v>
       </c>
       <c r="R9" t="n">
-        <v>7069026</v>
+        <v>7069288</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1548,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120040135</v>
+        <v>120040181</v>
       </c>
       <c r="B10" t="n">
-        <v>90562</v>
+        <v>79607</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1564,21 +1522,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1588,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>477507</v>
+        <v>477437</v>
       </c>
       <c r="R10" t="n">
-        <v>7069055</v>
+        <v>7068991</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1650,7 +1608,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120040151</v>
+        <v>120040165</v>
       </c>
       <c r="B11" t="n">
         <v>57310</v>
@@ -1690,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>477460</v>
+        <v>477596</v>
       </c>
       <c r="R11" t="n">
-        <v>7069166</v>
+        <v>7068950</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1730,7 +1688,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack färska och något äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1757,10 +1715,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120040189</v>
+        <v>120040176</v>
       </c>
       <c r="B12" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1769,25 +1727,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1797,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>477498</v>
+        <v>477852</v>
       </c>
       <c r="R12" t="n">
-        <v>7069206</v>
+        <v>7069022</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1833,6 +1791,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack ganska färska till äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1859,7 +1822,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120040138</v>
+        <v>120040166</v>
       </c>
       <c r="B13" t="n">
         <v>57310</v>
@@ -1899,10 +1862,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>477726</v>
+        <v>477622</v>
       </c>
       <c r="R13" t="n">
-        <v>7069062</v>
+        <v>7068965</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1939,7 +1902,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1966,7 +1929,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120040152</v>
+        <v>120040158</v>
       </c>
       <c r="B14" t="n">
         <v>57310</v>
@@ -2006,10 +1969,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>477472</v>
+        <v>477446</v>
       </c>
       <c r="R14" t="n">
-        <v>7069168</v>
+        <v>7069039</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2046,7 +2009,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2073,7 +2036,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120040177</v>
+        <v>120040144</v>
       </c>
       <c r="B15" t="n">
         <v>57310</v>
@@ -2113,10 +2076,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>477856</v>
+        <v>477644</v>
       </c>
       <c r="R15" t="n">
-        <v>7069020</v>
+        <v>7069114</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2153,7 +2116,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2180,7 +2143,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120040153</v>
+        <v>120040142</v>
       </c>
       <c r="B16" t="n">
         <v>57310</v>
@@ -2220,10 +2183,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>477547</v>
+        <v>477614</v>
       </c>
       <c r="R16" t="n">
-        <v>7069271</v>
+        <v>7069089</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2287,10 +2250,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120040170</v>
+        <v>120040134</v>
       </c>
       <c r="B17" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2303,21 +2266,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2327,10 +2290,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>477755</v>
+        <v>477522</v>
       </c>
       <c r="R17" t="n">
-        <v>7069016</v>
+        <v>7068987</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2363,11 +2326,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2394,10 +2352,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120040140</v>
+        <v>120040136</v>
       </c>
       <c r="B18" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2410,21 +2368,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2434,10 +2392,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>477472</v>
+        <v>477434</v>
       </c>
       <c r="R18" t="n">
-        <v>7069006</v>
+        <v>7069116</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2470,11 +2428,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2501,10 +2454,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120040158</v>
+        <v>120040203</v>
       </c>
       <c r="B19" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2517,21 +2470,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2541,10 +2494,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>477446</v>
+        <v>477472</v>
       </c>
       <c r="R19" t="n">
-        <v>7069039</v>
+        <v>7069087</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2577,11 +2530,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2608,7 +2556,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120040187</v>
+        <v>120040192</v>
       </c>
       <c r="B20" t="n">
         <v>97907</v>
@@ -2648,10 +2596,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>477525</v>
+        <v>477445</v>
       </c>
       <c r="R20" t="n">
-        <v>7069106</v>
+        <v>7068977</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2710,10 +2658,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120040154</v>
+        <v>120040135</v>
       </c>
       <c r="B21" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2726,21 +2674,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2750,10 +2698,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>477476</v>
+        <v>477507</v>
       </c>
       <c r="R21" t="n">
-        <v>7069264</v>
+        <v>7069055</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2786,11 +2734,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2817,10 +2760,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120040145</v>
+        <v>120040201</v>
       </c>
       <c r="B22" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2833,21 +2776,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2857,10 +2800,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>477626</v>
+        <v>477484</v>
       </c>
       <c r="R22" t="n">
-        <v>7069105</v>
+        <v>7068927</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2893,11 +2836,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2924,10 +2862,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120040188</v>
+        <v>120040139</v>
       </c>
       <c r="B23" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2936,25 +2874,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2964,10 +2902,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>477454</v>
+        <v>477517</v>
       </c>
       <c r="R23" t="n">
-        <v>7069190</v>
+        <v>7068992</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3000,6 +2938,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3026,10 +2969,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120040204</v>
+        <v>120040141</v>
       </c>
       <c r="B24" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3042,21 +2985,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3066,10 +3009,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>477534</v>
+        <v>477562</v>
       </c>
       <c r="R24" t="n">
-        <v>7069288</v>
+        <v>7069078</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3102,6 +3045,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3128,10 +3076,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120040202</v>
+        <v>120040189</v>
       </c>
       <c r="B25" t="n">
-        <v>90580</v>
+        <v>97907</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3140,25 +3088,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3168,10 +3116,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>477674</v>
+        <v>477498</v>
       </c>
       <c r="R25" t="n">
-        <v>7069000</v>
+        <v>7069206</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3230,10 +3178,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120040147</v>
+        <v>120040183</v>
       </c>
       <c r="B26" t="n">
-        <v>57310</v>
+        <v>57421</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3242,20 +3190,20 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3263,17 +3211,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>477581</v>
+        <v>477821</v>
       </c>
       <c r="R26" t="n">
-        <v>7069095</v>
+        <v>7069026</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3306,11 +3266,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3337,7 +3292,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120040172</v>
+        <v>120040159</v>
       </c>
       <c r="B27" t="n">
         <v>57310</v>
@@ -3377,10 +3332,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>477777</v>
+        <v>477444</v>
       </c>
       <c r="R27" t="n">
-        <v>7069022</v>
+        <v>7068963</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3417,7 +3372,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack ganska färska till äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3444,7 +3399,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120040163</v>
+        <v>120040160</v>
       </c>
       <c r="B28" t="n">
         <v>57310</v>
@@ -3484,10 +3439,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>477544</v>
+        <v>477440</v>
       </c>
       <c r="R28" t="n">
-        <v>7068952</v>
+        <v>7068958</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3524,7 +3479,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3551,10 +3506,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120040150</v>
+        <v>120040190</v>
       </c>
       <c r="B29" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3563,25 +3518,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3591,10 +3546,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>477457</v>
+        <v>477530</v>
       </c>
       <c r="R29" t="n">
-        <v>7069186</v>
+        <v>7069276</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3627,11 +3582,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3658,10 +3608,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120040160</v>
+        <v>120040187</v>
       </c>
       <c r="B30" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3670,25 +3620,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3698,10 +3648,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>477440</v>
+        <v>477525</v>
       </c>
       <c r="R30" t="n">
-        <v>7068958</v>
+        <v>7069106</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3734,11 +3684,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3765,7 +3710,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120040164</v>
+        <v>120040173</v>
       </c>
       <c r="B31" t="n">
         <v>57310</v>
@@ -3805,10 +3750,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>477597</v>
+        <v>477786</v>
       </c>
       <c r="R31" t="n">
-        <v>7068964</v>
+        <v>7069029</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3845,7 +3790,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3872,7 +3817,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120040141</v>
+        <v>120040177</v>
       </c>
       <c r="B32" t="n">
         <v>57310</v>
@@ -3912,10 +3857,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>477562</v>
+        <v>477856</v>
       </c>
       <c r="R32" t="n">
-        <v>7069078</v>
+        <v>7069020</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3952,7 +3897,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3979,10 +3924,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120040134</v>
+        <v>120040147</v>
       </c>
       <c r="B33" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3995,21 +3940,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4019,10 +3964,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>477522</v>
+        <v>477581</v>
       </c>
       <c r="R33" t="n">
-        <v>7068987</v>
+        <v>7069095</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4055,6 +4000,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4081,10 +4031,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120040191</v>
+        <v>120040161</v>
       </c>
       <c r="B34" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4093,25 +4043,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4121,10 +4071,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>477440</v>
+        <v>477426</v>
       </c>
       <c r="R34" t="n">
-        <v>7069251</v>
+        <v>7068947</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4157,6 +4107,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4183,10 +4138,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120040199</v>
+        <v>120040152</v>
       </c>
       <c r="B35" t="n">
-        <v>90558</v>
+        <v>57310</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4199,21 +4154,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4223,10 +4178,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>477671</v>
+        <v>477472</v>
       </c>
       <c r="R35" t="n">
-        <v>7068973</v>
+        <v>7069168</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4259,6 +4214,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4285,7 +4245,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120040174</v>
+        <v>120040154</v>
       </c>
       <c r="B36" t="n">
         <v>57310</v>
@@ -4325,10 +4285,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>477825</v>
+        <v>477476</v>
       </c>
       <c r="R36" t="n">
-        <v>7069031</v>
+        <v>7069264</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4392,10 +4352,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120040182</v>
+        <v>120040140</v>
       </c>
       <c r="B37" t="n">
-        <v>57421</v>
+        <v>57310</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4404,20 +4364,20 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4425,29 +4385,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>477760</v>
+        <v>477472</v>
       </c>
       <c r="R37" t="n">
-        <v>7069037</v>
+        <v>7069006</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4480,6 +4428,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4506,10 +4459,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120040201</v>
+        <v>120040207</v>
       </c>
       <c r="B38" t="n">
-        <v>90580</v>
+        <v>86878</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4522,21 +4475,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4546,10 +4499,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>477484</v>
+        <v>477473</v>
       </c>
       <c r="R38" t="n">
-        <v>7068927</v>
+        <v>7069007</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4608,10 +4561,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120040149</v>
+        <v>120040205</v>
       </c>
       <c r="B39" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4624,21 +4577,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4648,10 +4601,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>477423</v>
+        <v>477382</v>
       </c>
       <c r="R39" t="n">
-        <v>7069180</v>
+        <v>7069247</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4684,11 +4637,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4715,10 +4663,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120040136</v>
+        <v>120040155</v>
       </c>
       <c r="B40" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4731,21 +4679,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4755,10 +4703,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>477434</v>
+        <v>477377</v>
       </c>
       <c r="R40" t="n">
-        <v>7069116</v>
+        <v>7069208</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4791,6 +4739,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4817,10 +4770,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120040190</v>
+        <v>120040148</v>
       </c>
       <c r="B41" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4829,25 +4782,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4857,10 +4810,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>477530</v>
+        <v>477438</v>
       </c>
       <c r="R41" t="n">
-        <v>7069276</v>
+        <v>7069178</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4893,6 +4846,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4919,7 +4877,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120040139</v>
+        <v>120040151</v>
       </c>
       <c r="B42" t="n">
         <v>57310</v>
@@ -4959,10 +4917,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>477517</v>
+        <v>477460</v>
       </c>
       <c r="R42" t="n">
-        <v>7068992</v>
+        <v>7069166</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4999,7 +4957,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och något äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5026,7 +4984,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120040171</v>
+        <v>120040170</v>
       </c>
       <c r="B43" t="n">
         <v>57310</v>
@@ -5066,10 +5024,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>477759</v>
+        <v>477755</v>
       </c>
       <c r="R43" t="n">
-        <v>7069019</v>
+        <v>7069016</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5133,10 +5091,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120040203</v>
+        <v>120040138</v>
       </c>
       <c r="B44" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5149,21 +5107,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5173,10 +5131,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>477472</v>
+        <v>477726</v>
       </c>
       <c r="R44" t="n">
-        <v>7069087</v>
+        <v>7069062</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5209,6 +5167,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5235,7 +5198,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120040146</v>
+        <v>120040162</v>
       </c>
       <c r="B45" t="n">
         <v>57310</v>
@@ -5275,10 +5238,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>477599</v>
+        <v>477471</v>
       </c>
       <c r="R45" t="n">
-        <v>7069105</v>
+        <v>7068928</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5342,10 +5305,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120040157</v>
+        <v>120040184</v>
       </c>
       <c r="B46" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5354,25 +5317,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5382,10 +5345,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>477397</v>
+        <v>477481</v>
       </c>
       <c r="R46" t="n">
-        <v>7069068</v>
+        <v>7069004</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5418,11 +5381,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5449,10 +5407,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120040185</v>
+        <v>120040153</v>
       </c>
       <c r="B47" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5461,25 +5419,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5489,10 +5447,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>477507</v>
+        <v>477547</v>
       </c>
       <c r="R47" t="n">
-        <v>7069056</v>
+        <v>7069271</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5525,6 +5483,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5551,10 +5514,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120040207</v>
+        <v>120040167</v>
       </c>
       <c r="B48" t="n">
-        <v>86878</v>
+        <v>57310</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5567,21 +5530,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5591,10 +5554,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>477473</v>
+        <v>477641</v>
       </c>
       <c r="R48" t="n">
-        <v>7069007</v>
+        <v>7068958</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5627,6 +5590,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack ganska färska</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5653,10 +5621,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120040205</v>
+        <v>120040175</v>
       </c>
       <c r="B49" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5669,34 +5637,54 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>477382</v>
+        <v>477822</v>
       </c>
       <c r="R49" t="n">
-        <v>7069247</v>
+        <v>7069037</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5755,10 +5743,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120040184</v>
+        <v>120040163</v>
       </c>
       <c r="B50" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5767,25 +5755,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5795,10 +5783,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>477481</v>
+        <v>477544</v>
       </c>
       <c r="R50" t="n">
-        <v>7069004</v>
+        <v>7068952</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5831,6 +5819,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5857,7 +5850,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120040155</v>
+        <v>120040157</v>
       </c>
       <c r="B51" t="n">
         <v>57310</v>
@@ -5897,10 +5890,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>477377</v>
+        <v>477397</v>
       </c>
       <c r="R51" t="n">
-        <v>7069208</v>
+        <v>7069068</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5937,7 +5930,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5964,7 +5957,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120040162</v>
+        <v>120040174</v>
       </c>
       <c r="B52" t="n">
         <v>57310</v>
@@ -6004,10 +5997,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>477471</v>
+        <v>477825</v>
       </c>
       <c r="R52" t="n">
-        <v>7068928</v>
+        <v>7069031</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6071,7 +6064,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120040161</v>
+        <v>120040168</v>
       </c>
       <c r="B53" t="n">
         <v>57310</v>
@@ -6111,10 +6104,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>477426</v>
+        <v>477664</v>
       </c>
       <c r="R53" t="n">
-        <v>7068947</v>
+        <v>7068971</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6151,7 +6144,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6178,10 +6171,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120040181</v>
+        <v>120040179</v>
       </c>
       <c r="B54" t="n">
-        <v>79607</v>
+        <v>79608</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6194,21 +6187,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6280,10 +6273,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120040165</v>
+        <v>120040202</v>
       </c>
       <c r="B55" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6296,21 +6289,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6320,10 +6313,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>477596</v>
+        <v>477674</v>
       </c>
       <c r="R55" t="n">
-        <v>7068950</v>
+        <v>7069000</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6356,11 +6349,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6387,10 +6375,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120040169</v>
+        <v>120040188</v>
       </c>
       <c r="B56" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6399,25 +6387,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6427,10 +6415,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>477688</v>
+        <v>477454</v>
       </c>
       <c r="R56" t="n">
-        <v>7069010</v>
+        <v>7069190</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6463,11 +6451,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6494,10 +6477,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120040142</v>
+        <v>120040185</v>
       </c>
       <c r="B57" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6506,25 +6489,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6534,10 +6517,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>477614</v>
+        <v>477507</v>
       </c>
       <c r="R57" t="n">
-        <v>7069089</v>
+        <v>7069056</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6570,11 +6553,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6601,10 +6579,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120040200</v>
+        <v>120040206</v>
       </c>
       <c r="B58" t="n">
-        <v>90580</v>
+        <v>78526</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6617,21 +6595,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6641,10 +6619,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>477439</v>
+        <v>477405</v>
       </c>
       <c r="R58" t="n">
-        <v>7069086</v>
+        <v>7069105</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6703,10 +6681,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120040192</v>
+        <v>120040164</v>
       </c>
       <c r="B59" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6715,25 +6693,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6743,10 +6721,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>477445</v>
+        <v>477597</v>
       </c>
       <c r="R59" t="n">
-        <v>7068977</v>
+        <v>7068964</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6779,6 +6757,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6805,7 +6788,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120040166</v>
+        <v>120040171</v>
       </c>
       <c r="B60" t="n">
         <v>57310</v>
@@ -6845,10 +6828,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>477622</v>
+        <v>477759</v>
       </c>
       <c r="R60" t="n">
-        <v>7068965</v>
+        <v>7069019</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6885,7 +6868,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6912,7 +6895,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120040176</v>
+        <v>120040149</v>
       </c>
       <c r="B61" t="n">
         <v>57310</v>
@@ -6952,10 +6935,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>477852</v>
+        <v>477423</v>
       </c>
       <c r="R61" t="n">
-        <v>7069022</v>
+        <v>7069180</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6992,7 +6975,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Ringhack ganska färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7019,10 +7002,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120040206</v>
+        <v>120040169</v>
       </c>
       <c r="B62" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7035,21 +7018,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7059,10 +7042,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>477405</v>
+        <v>477688</v>
       </c>
       <c r="R62" t="n">
-        <v>7069105</v>
+        <v>7069010</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7095,6 +7078,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7121,10 +7109,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120040180</v>
+        <v>120040150</v>
       </c>
       <c r="B63" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7137,21 +7125,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7161,10 +7149,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>477415</v>
+        <v>477457</v>
       </c>
       <c r="R63" t="n">
-        <v>7069070</v>
+        <v>7069186</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7197,6 +7185,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7223,10 +7216,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120040159</v>
+        <v>120040182</v>
       </c>
       <c r="B64" t="n">
-        <v>57310</v>
+        <v>57421</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7235,20 +7228,20 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -7256,17 +7249,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>477444</v>
+        <v>477760</v>
       </c>
       <c r="R64" t="n">
-        <v>7068963</v>
+        <v>7069037</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7299,11 +7304,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Ringhack ganska färska till äldre</t>
         </is>
       </c>
       <c r="AD64" t="b">

--- a/artfynd/A 36309-2024 artfynd.xlsx
+++ b/artfynd/A 36309-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120040172</v>
+        <v>120040180</v>
       </c>
       <c r="B2" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477777</v>
+        <v>477415</v>
       </c>
       <c r="R2" t="n">
-        <v>7069022</v>
+        <v>7069070</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120040145</v>
+        <v>120040167</v>
       </c>
       <c r="B3" t="n">
         <v>57310</v>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477626</v>
+        <v>477641</v>
       </c>
       <c r="R3" t="n">
-        <v>7069105</v>
+        <v>7068958</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +857,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack ganska färska</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120040191</v>
+        <v>120040164</v>
       </c>
       <c r="B4" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,25 +896,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477440</v>
+        <v>477597</v>
       </c>
       <c r="R4" t="n">
-        <v>7069251</v>
+        <v>7068964</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,6 +960,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120040146</v>
+        <v>120040148</v>
       </c>
       <c r="B5" t="n">
         <v>57310</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477599</v>
+        <v>477438</v>
       </c>
       <c r="R5" t="n">
-        <v>7069105</v>
+        <v>7069178</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120040199</v>
+        <v>120040188</v>
       </c>
       <c r="B6" t="n">
-        <v>90558</v>
+        <v>97907</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1110,25 +1110,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477671</v>
+        <v>477454</v>
       </c>
       <c r="R6" t="n">
-        <v>7068973</v>
+        <v>7069190</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120040180</v>
+        <v>120040205</v>
       </c>
       <c r="B7" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1216,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477415</v>
+        <v>477382</v>
       </c>
       <c r="R7" t="n">
-        <v>7069070</v>
+        <v>7069247</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1302,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120040200</v>
+        <v>120040155</v>
       </c>
       <c r="B8" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1318,21 +1318,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477439</v>
+        <v>477377</v>
       </c>
       <c r="R8" t="n">
-        <v>7069086</v>
+        <v>7069208</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1378,6 +1378,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1404,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120040204</v>
+        <v>120040140</v>
       </c>
       <c r="B9" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1420,21 +1425,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1444,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>477534</v>
+        <v>477472</v>
       </c>
       <c r="R9" t="n">
-        <v>7069288</v>
+        <v>7069006</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1480,6 +1485,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1506,10 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120040181</v>
+        <v>120040144</v>
       </c>
       <c r="B10" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1522,21 +1532,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1546,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>477437</v>
+        <v>477644</v>
       </c>
       <c r="R10" t="n">
-        <v>7068991</v>
+        <v>7069114</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1582,6 +1592,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1608,10 +1623,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120040165</v>
+        <v>120040179</v>
       </c>
       <c r="B11" t="n">
-        <v>57310</v>
+        <v>79608</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1624,21 +1639,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1648,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>477596</v>
+        <v>477437</v>
       </c>
       <c r="R11" t="n">
-        <v>7068950</v>
+        <v>7068991</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1684,11 +1699,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1715,10 +1725,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120040176</v>
+        <v>120040207</v>
       </c>
       <c r="B12" t="n">
-        <v>57310</v>
+        <v>86878</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1731,21 +1741,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1755,10 +1765,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>477852</v>
+        <v>477473</v>
       </c>
       <c r="R12" t="n">
-        <v>7069022</v>
+        <v>7069007</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1791,11 +1801,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack ganska färska till äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1822,10 +1827,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120040166</v>
+        <v>120040199</v>
       </c>
       <c r="B13" t="n">
-        <v>57310</v>
+        <v>90558</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1838,21 +1843,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1862,10 +1867,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>477622</v>
+        <v>477671</v>
       </c>
       <c r="R13" t="n">
-        <v>7068965</v>
+        <v>7068973</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1898,11 +1903,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1929,7 +1929,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120040158</v>
+        <v>120040138</v>
       </c>
       <c r="B14" t="n">
         <v>57310</v>
@@ -1969,10 +1969,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>477446</v>
+        <v>477726</v>
       </c>
       <c r="R14" t="n">
-        <v>7069039</v>
+        <v>7069062</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2009,7 +2009,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2036,7 +2036,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120040144</v>
+        <v>120040174</v>
       </c>
       <c r="B15" t="n">
         <v>57310</v>
@@ -2076,10 +2076,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>477644</v>
+        <v>477825</v>
       </c>
       <c r="R15" t="n">
-        <v>7069114</v>
+        <v>7069031</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2143,10 +2143,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120040142</v>
+        <v>120040192</v>
       </c>
       <c r="B16" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2155,25 +2155,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2183,10 +2183,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>477614</v>
+        <v>477445</v>
       </c>
       <c r="R16" t="n">
-        <v>7069089</v>
+        <v>7068977</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2219,11 +2219,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2250,10 +2245,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120040134</v>
+        <v>120040206</v>
       </c>
       <c r="B17" t="n">
-        <v>90562</v>
+        <v>78526</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2266,21 +2261,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2290,10 +2285,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>477522</v>
+        <v>477405</v>
       </c>
       <c r="R17" t="n">
-        <v>7068987</v>
+        <v>7069105</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2352,10 +2347,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120040136</v>
+        <v>120040152</v>
       </c>
       <c r="B18" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2368,21 +2363,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2392,10 +2387,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>477434</v>
+        <v>477472</v>
       </c>
       <c r="R18" t="n">
-        <v>7069116</v>
+        <v>7069168</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2428,6 +2423,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2454,10 +2454,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120040203</v>
+        <v>120040162</v>
       </c>
       <c r="B19" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2470,21 +2470,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2494,10 +2494,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>477472</v>
+        <v>477471</v>
       </c>
       <c r="R19" t="n">
-        <v>7069087</v>
+        <v>7068928</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2530,6 +2530,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2556,10 +2561,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120040192</v>
+        <v>120040134</v>
       </c>
       <c r="B20" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2568,25 +2573,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2596,10 +2601,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>477445</v>
+        <v>477522</v>
       </c>
       <c r="R20" t="n">
-        <v>7068977</v>
+        <v>7068987</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2658,10 +2663,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120040135</v>
+        <v>120040203</v>
       </c>
       <c r="B21" t="n">
-        <v>90562</v>
+        <v>78526</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2674,21 +2679,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2698,10 +2703,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>477507</v>
+        <v>477472</v>
       </c>
       <c r="R21" t="n">
-        <v>7069055</v>
+        <v>7069087</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2760,10 +2765,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120040201</v>
+        <v>120040187</v>
       </c>
       <c r="B22" t="n">
-        <v>90580</v>
+        <v>97907</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2772,25 +2777,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2800,10 +2805,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>477484</v>
+        <v>477525</v>
       </c>
       <c r="R22" t="n">
-        <v>7068927</v>
+        <v>7069106</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2862,7 +2867,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120040139</v>
+        <v>120040171</v>
       </c>
       <c r="B23" t="n">
         <v>57310</v>
@@ -2902,10 +2907,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>477517</v>
+        <v>477759</v>
       </c>
       <c r="R23" t="n">
-        <v>7068992</v>
+        <v>7069019</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2969,10 +2974,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120040141</v>
+        <v>120040184</v>
       </c>
       <c r="B24" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2981,25 +2986,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3009,10 +3014,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>477562</v>
+        <v>477481</v>
       </c>
       <c r="R24" t="n">
-        <v>7069078</v>
+        <v>7069004</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3045,11 +3050,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3076,10 +3076,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120040189</v>
+        <v>120040159</v>
       </c>
       <c r="B25" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3088,25 +3088,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3116,10 +3116,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>477498</v>
+        <v>477444</v>
       </c>
       <c r="R25" t="n">
-        <v>7069206</v>
+        <v>7068963</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3152,6 +3152,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack ganska färska till äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3178,10 +3183,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120040183</v>
+        <v>120040142</v>
       </c>
       <c r="B26" t="n">
-        <v>57421</v>
+        <v>57310</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3190,20 +3195,20 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3211,29 +3216,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>477821</v>
+        <v>477614</v>
       </c>
       <c r="R26" t="n">
-        <v>7069026</v>
+        <v>7069089</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3266,6 +3259,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3292,10 +3290,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120040159</v>
+        <v>120040189</v>
       </c>
       <c r="B27" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3304,25 +3302,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3332,10 +3330,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>477444</v>
+        <v>477498</v>
       </c>
       <c r="R27" t="n">
-        <v>7068963</v>
+        <v>7069206</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3368,11 +3366,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack ganska färska till äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3399,10 +3392,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120040160</v>
+        <v>120040182</v>
       </c>
       <c r="B28" t="n">
-        <v>57310</v>
+        <v>57421</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3411,20 +3404,20 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3432,17 +3425,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>477440</v>
+        <v>477760</v>
       </c>
       <c r="R28" t="n">
-        <v>7068958</v>
+        <v>7069037</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3475,11 +3480,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3506,10 +3506,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120040190</v>
+        <v>120040202</v>
       </c>
       <c r="B29" t="n">
-        <v>97907</v>
+        <v>90580</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3518,25 +3518,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3546,10 +3546,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>477530</v>
+        <v>477674</v>
       </c>
       <c r="R29" t="n">
-        <v>7069276</v>
+        <v>7069000</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3608,10 +3608,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120040187</v>
+        <v>120040176</v>
       </c>
       <c r="B30" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3620,25 +3620,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3648,10 +3648,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>477525</v>
+        <v>477852</v>
       </c>
       <c r="R30" t="n">
-        <v>7069106</v>
+        <v>7069022</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3684,6 +3684,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack ganska färska till äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3710,7 +3715,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120040173</v>
+        <v>120040163</v>
       </c>
       <c r="B31" t="n">
         <v>57310</v>
@@ -3750,10 +3755,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>477786</v>
+        <v>477544</v>
       </c>
       <c r="R31" t="n">
-        <v>7069029</v>
+        <v>7068952</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3790,7 +3795,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3817,10 +3822,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120040177</v>
+        <v>120040201</v>
       </c>
       <c r="B32" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3833,21 +3838,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3857,10 +3862,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>477856</v>
+        <v>477484</v>
       </c>
       <c r="R32" t="n">
-        <v>7069020</v>
+        <v>7068927</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3893,11 +3898,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3924,10 +3924,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120040147</v>
+        <v>120040200</v>
       </c>
       <c r="B33" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3940,21 +3940,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3964,10 +3964,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>477581</v>
+        <v>477439</v>
       </c>
       <c r="R33" t="n">
-        <v>7069095</v>
+        <v>7069086</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4000,11 +4000,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4031,7 +4026,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120040161</v>
+        <v>120040153</v>
       </c>
       <c r="B34" t="n">
         <v>57310</v>
@@ -4071,10 +4066,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>477426</v>
+        <v>477547</v>
       </c>
       <c r="R34" t="n">
-        <v>7068947</v>
+        <v>7069271</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4138,10 +4133,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120040152</v>
+        <v>120040183</v>
       </c>
       <c r="B35" t="n">
-        <v>57310</v>
+        <v>57421</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4150,20 +4145,20 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4171,17 +4166,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>477472</v>
+        <v>477821</v>
       </c>
       <c r="R35" t="n">
-        <v>7069168</v>
+        <v>7069026</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4214,11 +4221,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4245,7 +4247,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120040154</v>
+        <v>120040150</v>
       </c>
       <c r="B36" t="n">
         <v>57310</v>
@@ -4285,10 +4287,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>477476</v>
+        <v>477457</v>
       </c>
       <c r="R36" t="n">
-        <v>7069264</v>
+        <v>7069186</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4352,10 +4354,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120040140</v>
+        <v>120040185</v>
       </c>
       <c r="B37" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4364,25 +4366,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4392,10 +4394,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>477472</v>
+        <v>477507</v>
       </c>
       <c r="R37" t="n">
-        <v>7069006</v>
+        <v>7069056</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4428,11 +4430,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4459,10 +4456,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120040207</v>
+        <v>120040146</v>
       </c>
       <c r="B38" t="n">
-        <v>86878</v>
+        <v>57310</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4475,21 +4472,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4499,10 +4496,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>477473</v>
+        <v>477599</v>
       </c>
       <c r="R38" t="n">
-        <v>7069007</v>
+        <v>7069105</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4535,6 +4532,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4561,10 +4563,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120040205</v>
+        <v>120040154</v>
       </c>
       <c r="B39" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4577,21 +4579,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4601,10 +4603,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>477382</v>
+        <v>477476</v>
       </c>
       <c r="R39" t="n">
-        <v>7069247</v>
+        <v>7069264</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4637,6 +4639,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4663,7 +4670,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120040155</v>
+        <v>120040158</v>
       </c>
       <c r="B40" t="n">
         <v>57310</v>
@@ -4703,10 +4710,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>477377</v>
+        <v>477446</v>
       </c>
       <c r="R40" t="n">
-        <v>7069208</v>
+        <v>7069039</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4743,7 +4750,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4770,7 +4777,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120040148</v>
+        <v>120040168</v>
       </c>
       <c r="B41" t="n">
         <v>57310</v>
@@ -4810,10 +4817,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>477438</v>
+        <v>477664</v>
       </c>
       <c r="R41" t="n">
-        <v>7069178</v>
+        <v>7068971</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4850,7 +4857,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4877,10 +4884,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120040151</v>
+        <v>120040204</v>
       </c>
       <c r="B42" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4893,21 +4900,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4917,10 +4924,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>477460</v>
+        <v>477534</v>
       </c>
       <c r="R42" t="n">
-        <v>7069166</v>
+        <v>7069288</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4953,11 +4960,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack färska och något äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4984,10 +4986,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120040170</v>
+        <v>120040181</v>
       </c>
       <c r="B43" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5000,21 +5002,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5024,10 +5026,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>477755</v>
+        <v>477437</v>
       </c>
       <c r="R43" t="n">
-        <v>7069016</v>
+        <v>7068991</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5060,11 +5062,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5091,7 +5088,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120040138</v>
+        <v>120040166</v>
       </c>
       <c r="B44" t="n">
         <v>57310</v>
@@ -5131,10 +5128,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>477726</v>
+        <v>477622</v>
       </c>
       <c r="R44" t="n">
-        <v>7069062</v>
+        <v>7068965</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5171,7 +5168,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5198,7 +5195,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120040162</v>
+        <v>120040161</v>
       </c>
       <c r="B45" t="n">
         <v>57310</v>
@@ -5238,10 +5235,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>477471</v>
+        <v>477426</v>
       </c>
       <c r="R45" t="n">
-        <v>7068928</v>
+        <v>7068947</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5305,10 +5302,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120040184</v>
+        <v>120040139</v>
       </c>
       <c r="B46" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5317,25 +5314,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5345,10 +5342,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>477481</v>
+        <v>477517</v>
       </c>
       <c r="R46" t="n">
-        <v>7069004</v>
+        <v>7068992</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5381,6 +5378,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5407,7 +5409,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120040153</v>
+        <v>120040157</v>
       </c>
       <c r="B47" t="n">
         <v>57310</v>
@@ -5447,10 +5449,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>477547</v>
+        <v>477397</v>
       </c>
       <c r="R47" t="n">
-        <v>7069271</v>
+        <v>7069068</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5487,7 +5489,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5514,10 +5516,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120040167</v>
+        <v>120040191</v>
       </c>
       <c r="B48" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5526,25 +5528,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5554,10 +5556,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>477641</v>
+        <v>477440</v>
       </c>
       <c r="R48" t="n">
-        <v>7068958</v>
+        <v>7069251</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5590,11 +5592,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack ganska färska</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5621,10 +5618,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120040175</v>
+        <v>120040135</v>
       </c>
       <c r="B49" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5637,54 +5634,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>477822</v>
+        <v>477507</v>
       </c>
       <c r="R49" t="n">
-        <v>7069037</v>
+        <v>7069055</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5743,7 +5720,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120040163</v>
+        <v>120040169</v>
       </c>
       <c r="B50" t="n">
         <v>57310</v>
@@ -5783,10 +5760,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>477544</v>
+        <v>477688</v>
       </c>
       <c r="R50" t="n">
-        <v>7068952</v>
+        <v>7069010</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5823,7 +5800,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5850,7 +5827,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120040157</v>
+        <v>120040173</v>
       </c>
       <c r="B51" t="n">
         <v>57310</v>
@@ -5890,10 +5867,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>477397</v>
+        <v>477786</v>
       </c>
       <c r="R51" t="n">
-        <v>7069068</v>
+        <v>7069029</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5930,7 +5907,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5957,7 +5934,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120040174</v>
+        <v>120040145</v>
       </c>
       <c r="B52" t="n">
         <v>57310</v>
@@ -5997,10 +5974,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>477825</v>
+        <v>477626</v>
       </c>
       <c r="R52" t="n">
-        <v>7069031</v>
+        <v>7069105</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6064,7 +6041,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120040168</v>
+        <v>120040149</v>
       </c>
       <c r="B53" t="n">
         <v>57310</v>
@@ -6104,10 +6081,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>477664</v>
+        <v>477423</v>
       </c>
       <c r="R53" t="n">
-        <v>7068971</v>
+        <v>7069180</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6144,7 +6121,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6171,10 +6148,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120040179</v>
+        <v>120040136</v>
       </c>
       <c r="B54" t="n">
-        <v>79608</v>
+        <v>90562</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6187,21 +6164,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6211,10 +6188,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>477437</v>
+        <v>477434</v>
       </c>
       <c r="R54" t="n">
-        <v>7068991</v>
+        <v>7069116</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6273,10 +6250,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120040202</v>
+        <v>120040170</v>
       </c>
       <c r="B55" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6289,21 +6266,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6313,10 +6290,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>477674</v>
+        <v>477755</v>
       </c>
       <c r="R55" t="n">
-        <v>7069000</v>
+        <v>7069016</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6349,6 +6326,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6375,10 +6357,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120040188</v>
+        <v>120040175</v>
       </c>
       <c r="B56" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6387,38 +6369,58 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>477454</v>
+        <v>477822</v>
       </c>
       <c r="R56" t="n">
-        <v>7069190</v>
+        <v>7069037</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6477,10 +6479,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120040185</v>
+        <v>120040172</v>
       </c>
       <c r="B57" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6489,25 +6491,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6517,10 +6519,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>477507</v>
+        <v>477777</v>
       </c>
       <c r="R57" t="n">
-        <v>7069056</v>
+        <v>7069022</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6553,6 +6555,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6579,10 +6586,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120040206</v>
+        <v>120040147</v>
       </c>
       <c r="B58" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6595,21 +6602,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6619,10 +6626,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>477405</v>
+        <v>477581</v>
       </c>
       <c r="R58" t="n">
-        <v>7069105</v>
+        <v>7069095</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6655,6 +6662,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6681,7 +6693,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120040164</v>
+        <v>120040160</v>
       </c>
       <c r="B59" t="n">
         <v>57310</v>
@@ -6721,10 +6733,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>477597</v>
+        <v>477440</v>
       </c>
       <c r="R59" t="n">
-        <v>7068964</v>
+        <v>7068958</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6761,7 +6773,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6788,7 +6800,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120040171</v>
+        <v>120040165</v>
       </c>
       <c r="B60" t="n">
         <v>57310</v>
@@ -6828,10 +6840,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>477759</v>
+        <v>477596</v>
       </c>
       <c r="R60" t="n">
-        <v>7069019</v>
+        <v>7068950</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6868,7 +6880,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6895,7 +6907,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120040149</v>
+        <v>120040177</v>
       </c>
       <c r="B61" t="n">
         <v>57310</v>
@@ -6935,10 +6947,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>477423</v>
+        <v>477856</v>
       </c>
       <c r="R61" t="n">
-        <v>7069180</v>
+        <v>7069020</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6975,7 +6987,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7002,7 +7014,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120040169</v>
+        <v>120040141</v>
       </c>
       <c r="B62" t="n">
         <v>57310</v>
@@ -7042,10 +7054,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>477688</v>
+        <v>477562</v>
       </c>
       <c r="R62" t="n">
-        <v>7069010</v>
+        <v>7069078</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7109,10 +7121,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120040150</v>
+        <v>120040190</v>
       </c>
       <c r="B63" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7121,25 +7133,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7149,10 +7161,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>477457</v>
+        <v>477530</v>
       </c>
       <c r="R63" t="n">
-        <v>7069186</v>
+        <v>7069276</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7185,11 +7197,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7216,10 +7223,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120040182</v>
+        <v>120040151</v>
       </c>
       <c r="B64" t="n">
-        <v>57421</v>
+        <v>57310</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7228,20 +7235,20 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -7249,29 +7256,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>477760</v>
+        <v>477460</v>
       </c>
       <c r="R64" t="n">
-        <v>7069037</v>
+        <v>7069166</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7304,6 +7299,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Ringhack färska och något äldre</t>
         </is>
       </c>
       <c r="AD64" t="b">

--- a/artfynd/A 36309-2024 artfynd.xlsx
+++ b/artfynd/A 36309-2024 artfynd.xlsx
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120040148</v>
+        <v>120040188</v>
       </c>
       <c r="B5" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,25 +1003,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477438</v>
+        <v>477454</v>
       </c>
       <c r="R5" t="n">
-        <v>7069178</v>
+        <v>7069190</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,11 +1067,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120040188</v>
+        <v>120040148</v>
       </c>
       <c r="B6" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1110,25 +1105,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477454</v>
+        <v>477438</v>
       </c>
       <c r="R6" t="n">
-        <v>7069190</v>
+        <v>7069178</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1174,6 +1169,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1623,10 +1623,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120040179</v>
+        <v>120040207</v>
       </c>
       <c r="B11" t="n">
-        <v>79608</v>
+        <v>86878</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1639,21 +1639,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>510</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1663,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>477437</v>
+        <v>477473</v>
       </c>
       <c r="R11" t="n">
-        <v>7068991</v>
+        <v>7069007</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1725,10 +1725,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120040207</v>
+        <v>120040199</v>
       </c>
       <c r="B12" t="n">
-        <v>86878</v>
+        <v>90558</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1741,21 +1741,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>510</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1765,10 +1765,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>477473</v>
+        <v>477671</v>
       </c>
       <c r="R12" t="n">
-        <v>7069007</v>
+        <v>7068973</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1827,10 +1827,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120040199</v>
+        <v>120040179</v>
       </c>
       <c r="B13" t="n">
-        <v>90558</v>
+        <v>79608</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1843,21 +1843,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1867,10 +1867,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>477671</v>
+        <v>477437</v>
       </c>
       <c r="R13" t="n">
-        <v>7068973</v>
+        <v>7068991</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -4247,10 +4247,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120040150</v>
+        <v>120040185</v>
       </c>
       <c r="B36" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4259,25 +4259,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4287,10 +4287,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>477457</v>
+        <v>477507</v>
       </c>
       <c r="R36" t="n">
-        <v>7069186</v>
+        <v>7069056</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4323,11 +4323,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4354,10 +4349,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120040185</v>
+        <v>120040150</v>
       </c>
       <c r="B37" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4366,25 +4361,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4394,10 +4389,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>477507</v>
+        <v>477457</v>
       </c>
       <c r="R37" t="n">
-        <v>7069056</v>
+        <v>7069186</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4430,6 +4425,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4986,10 +4986,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120040181</v>
+        <v>120040166</v>
       </c>
       <c r="B43" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5002,21 +5002,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5026,10 +5026,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>477437</v>
+        <v>477622</v>
       </c>
       <c r="R43" t="n">
-        <v>7068991</v>
+        <v>7068965</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5062,6 +5062,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5088,7 +5093,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120040166</v>
+        <v>120040161</v>
       </c>
       <c r="B44" t="n">
         <v>57310</v>
@@ -5128,10 +5133,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>477622</v>
+        <v>477426</v>
       </c>
       <c r="R44" t="n">
-        <v>7068965</v>
+        <v>7068947</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5168,7 +5173,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5195,10 +5200,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120040161</v>
+        <v>120040181</v>
       </c>
       <c r="B45" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5211,21 +5216,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5235,10 +5240,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>477426</v>
+        <v>477437</v>
       </c>
       <c r="R45" t="n">
-        <v>7068947</v>
+        <v>7068991</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5271,11 +5276,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5302,10 +5302,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120040139</v>
+        <v>120040191</v>
       </c>
       <c r="B46" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5314,25 +5314,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5342,10 +5342,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>477517</v>
+        <v>477440</v>
       </c>
       <c r="R46" t="n">
-        <v>7068992</v>
+        <v>7069251</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5378,11 +5378,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5409,7 +5404,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120040157</v>
+        <v>120040139</v>
       </c>
       <c r="B47" t="n">
         <v>57310</v>
@@ -5449,10 +5444,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>477397</v>
+        <v>477517</v>
       </c>
       <c r="R47" t="n">
-        <v>7069068</v>
+        <v>7068992</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5489,7 +5484,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5516,10 +5511,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120040191</v>
+        <v>120040157</v>
       </c>
       <c r="B48" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5528,25 +5523,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5556,10 +5551,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>477440</v>
+        <v>477397</v>
       </c>
       <c r="R48" t="n">
-        <v>7069251</v>
+        <v>7069068</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5592,6 +5587,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">

--- a/artfynd/A 36309-2024 artfynd.xlsx
+++ b/artfynd/A 36309-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120040180</v>
+        <v>120040202</v>
       </c>
       <c r="B2" t="n">
-        <v>79607</v>
+        <v>90580</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477415</v>
+        <v>477674</v>
       </c>
       <c r="R2" t="n">
-        <v>7069070</v>
+        <v>7069000</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120040167</v>
+        <v>120040201</v>
       </c>
       <c r="B3" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477641</v>
+        <v>477484</v>
       </c>
       <c r="R3" t="n">
-        <v>7068958</v>
+        <v>7068927</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack ganska färska</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120040164</v>
+        <v>120040160</v>
       </c>
       <c r="B4" t="n">
         <v>57310</v>
@@ -924,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477597</v>
+        <v>477440</v>
       </c>
       <c r="R4" t="n">
-        <v>7068964</v>
+        <v>7068958</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +959,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120040188</v>
+        <v>120040158</v>
       </c>
       <c r="B5" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,25 +998,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477454</v>
+        <v>477446</v>
       </c>
       <c r="R5" t="n">
-        <v>7069190</v>
+        <v>7069039</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,6 +1062,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120040148</v>
+        <v>120040206</v>
       </c>
       <c r="B6" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477438</v>
+        <v>477405</v>
       </c>
       <c r="R6" t="n">
-        <v>7069178</v>
+        <v>7069105</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,11 +1169,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120040205</v>
+        <v>120040146</v>
       </c>
       <c r="B7" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1216,21 +1211,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477382</v>
+        <v>477599</v>
       </c>
       <c r="R7" t="n">
-        <v>7069247</v>
+        <v>7069105</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1276,6 +1271,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1302,7 +1302,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120040155</v>
+        <v>120040153</v>
       </c>
       <c r="B8" t="n">
         <v>57310</v>
@@ -1342,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477377</v>
+        <v>477547</v>
       </c>
       <c r="R8" t="n">
-        <v>7069208</v>
+        <v>7069271</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1409,7 +1409,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120040140</v>
+        <v>120040165</v>
       </c>
       <c r="B9" t="n">
         <v>57310</v>
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>477472</v>
+        <v>477596</v>
       </c>
       <c r="R9" t="n">
-        <v>7069006</v>
+        <v>7068950</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1489,7 +1489,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1516,7 +1516,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120040144</v>
+        <v>120040166</v>
       </c>
       <c r="B10" t="n">
         <v>57310</v>
@@ -1556,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>477644</v>
+        <v>477622</v>
       </c>
       <c r="R10" t="n">
-        <v>7069114</v>
+        <v>7068965</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1623,10 +1623,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120040207</v>
+        <v>120040176</v>
       </c>
       <c r="B11" t="n">
-        <v>86878</v>
+        <v>57310</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1639,21 +1639,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1663,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>477473</v>
+        <v>477852</v>
       </c>
       <c r="R11" t="n">
-        <v>7069007</v>
+        <v>7069022</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1699,6 +1699,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack ganska färska till äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1725,10 +1730,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120040199</v>
+        <v>120040145</v>
       </c>
       <c r="B12" t="n">
-        <v>90558</v>
+        <v>57310</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1741,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1765,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>477671</v>
+        <v>477626</v>
       </c>
       <c r="R12" t="n">
-        <v>7068973</v>
+        <v>7069105</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1801,6 +1806,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1827,10 +1837,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120040179</v>
+        <v>120040181</v>
       </c>
       <c r="B13" t="n">
-        <v>79608</v>
+        <v>79607</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1843,21 +1853,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1929,7 +1939,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120040138</v>
+        <v>120040169</v>
       </c>
       <c r="B14" t="n">
         <v>57310</v>
@@ -1969,10 +1979,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>477726</v>
+        <v>477688</v>
       </c>
       <c r="R14" t="n">
-        <v>7069062</v>
+        <v>7069010</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2036,7 +2046,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120040174</v>
+        <v>120040177</v>
       </c>
       <c r="B15" t="n">
         <v>57310</v>
@@ -2076,10 +2086,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>477825</v>
+        <v>477856</v>
       </c>
       <c r="R15" t="n">
-        <v>7069031</v>
+        <v>7069020</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2116,7 +2126,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2143,7 +2153,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120040192</v>
+        <v>120040191</v>
       </c>
       <c r="B16" t="n">
         <v>97907</v>
@@ -2183,10 +2193,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>477445</v>
+        <v>477440</v>
       </c>
       <c r="R16" t="n">
-        <v>7068977</v>
+        <v>7069251</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2245,10 +2255,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120040206</v>
+        <v>120040162</v>
       </c>
       <c r="B17" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2261,21 +2271,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2285,10 +2295,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>477405</v>
+        <v>477471</v>
       </c>
       <c r="R17" t="n">
-        <v>7069105</v>
+        <v>7068928</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2321,6 +2331,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2347,7 +2362,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120040152</v>
+        <v>120040139</v>
       </c>
       <c r="B18" t="n">
         <v>57310</v>
@@ -2387,10 +2402,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>477472</v>
+        <v>477517</v>
       </c>
       <c r="R18" t="n">
-        <v>7069168</v>
+        <v>7068992</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2454,10 +2469,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120040162</v>
+        <v>120040134</v>
       </c>
       <c r="B19" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2470,21 +2485,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2494,10 +2509,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>477471</v>
+        <v>477522</v>
       </c>
       <c r="R19" t="n">
-        <v>7068928</v>
+        <v>7068987</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2530,11 +2545,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2561,10 +2571,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120040134</v>
+        <v>120040148</v>
       </c>
       <c r="B20" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2577,21 +2587,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2601,10 +2611,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>477522</v>
+        <v>477438</v>
       </c>
       <c r="R20" t="n">
-        <v>7068987</v>
+        <v>7069178</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2637,6 +2647,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2663,10 +2678,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120040203</v>
+        <v>120040185</v>
       </c>
       <c r="B21" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2675,25 +2690,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2703,10 +2718,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>477472</v>
+        <v>477507</v>
       </c>
       <c r="R21" t="n">
-        <v>7069087</v>
+        <v>7069056</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2765,10 +2780,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120040187</v>
+        <v>120040204</v>
       </c>
       <c r="B22" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2777,25 +2792,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2805,10 +2820,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>477525</v>
+        <v>477534</v>
       </c>
       <c r="R22" t="n">
-        <v>7069106</v>
+        <v>7069288</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2867,7 +2882,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120040171</v>
+        <v>120040163</v>
       </c>
       <c r="B23" t="n">
         <v>57310</v>
@@ -2907,10 +2922,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>477759</v>
+        <v>477544</v>
       </c>
       <c r="R23" t="n">
-        <v>7069019</v>
+        <v>7068952</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2947,7 +2962,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2974,10 +2989,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120040184</v>
+        <v>120040171</v>
       </c>
       <c r="B24" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2986,25 +3001,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3014,10 +3029,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>477481</v>
+        <v>477759</v>
       </c>
       <c r="R24" t="n">
-        <v>7069004</v>
+        <v>7069019</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3050,6 +3065,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3076,10 +3096,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120040159</v>
+        <v>120040200</v>
       </c>
       <c r="B25" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3092,21 +3112,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3116,10 +3136,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>477444</v>
+        <v>477439</v>
       </c>
       <c r="R25" t="n">
-        <v>7068963</v>
+        <v>7069086</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3152,11 +3172,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack ganska färska till äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3183,10 +3198,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120040142</v>
+        <v>120040189</v>
       </c>
       <c r="B26" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3195,25 +3210,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3223,10 +3238,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>477614</v>
+        <v>477498</v>
       </c>
       <c r="R26" t="n">
-        <v>7069089</v>
+        <v>7069206</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3259,11 +3274,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3290,7 +3300,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120040189</v>
+        <v>120040192</v>
       </c>
       <c r="B27" t="n">
         <v>97907</v>
@@ -3330,10 +3340,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>477498</v>
+        <v>477445</v>
       </c>
       <c r="R27" t="n">
-        <v>7069206</v>
+        <v>7068977</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3392,10 +3402,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120040182</v>
+        <v>120040161</v>
       </c>
       <c r="B28" t="n">
-        <v>57421</v>
+        <v>57310</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3404,20 +3414,20 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3425,29 +3435,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>477760</v>
+        <v>477426</v>
       </c>
       <c r="R28" t="n">
-        <v>7069037</v>
+        <v>7068947</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3480,6 +3478,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3506,10 +3509,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120040202</v>
+        <v>120040140</v>
       </c>
       <c r="B29" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3522,21 +3525,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3546,10 +3549,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>477674</v>
+        <v>477472</v>
       </c>
       <c r="R29" t="n">
-        <v>7069000</v>
+        <v>7069006</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3582,6 +3585,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3608,10 +3616,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120040176</v>
+        <v>120040135</v>
       </c>
       <c r="B30" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3624,21 +3632,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3648,10 +3656,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>477852</v>
+        <v>477507</v>
       </c>
       <c r="R30" t="n">
-        <v>7069022</v>
+        <v>7069055</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3684,11 +3692,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack ganska färska till äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3715,7 +3718,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120040163</v>
+        <v>120040156</v>
       </c>
       <c r="B31" t="n">
         <v>57310</v>
@@ -3755,10 +3758,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>477544</v>
+        <v>477377</v>
       </c>
       <c r="R31" t="n">
-        <v>7068952</v>
+        <v>7069208</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3795,7 +3798,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3822,10 +3825,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120040201</v>
+        <v>120040173</v>
       </c>
       <c r="B32" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3838,21 +3841,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3862,10 +3865,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>477484</v>
+        <v>477786</v>
       </c>
       <c r="R32" t="n">
-        <v>7068927</v>
+        <v>7069029</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3898,6 +3901,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3924,10 +3932,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120040200</v>
+        <v>120040151</v>
       </c>
       <c r="B33" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3940,21 +3948,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3964,10 +3972,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>477439</v>
+        <v>477460</v>
       </c>
       <c r="R33" t="n">
-        <v>7069086</v>
+        <v>7069166</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4000,6 +4008,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack färska och något äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4026,7 +4039,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120040153</v>
+        <v>120040164</v>
       </c>
       <c r="B34" t="n">
         <v>57310</v>
@@ -4066,10 +4079,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>477547</v>
+        <v>477597</v>
       </c>
       <c r="R34" t="n">
-        <v>7069271</v>
+        <v>7068964</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4106,7 +4119,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4133,10 +4146,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120040183</v>
+        <v>120040168</v>
       </c>
       <c r="B35" t="n">
-        <v>57421</v>
+        <v>57310</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4145,20 +4158,20 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4166,29 +4179,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>477821</v>
+        <v>477664</v>
       </c>
       <c r="R35" t="n">
-        <v>7069026</v>
+        <v>7068971</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4221,6 +4222,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4247,7 +4253,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120040185</v>
+        <v>120040184</v>
       </c>
       <c r="B36" t="n">
         <v>97907</v>
@@ -4287,10 +4293,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>477507</v>
+        <v>477481</v>
       </c>
       <c r="R36" t="n">
-        <v>7069056</v>
+        <v>7069004</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4349,7 +4355,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120040150</v>
+        <v>120040157</v>
       </c>
       <c r="B37" t="n">
         <v>57310</v>
@@ -4389,10 +4395,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>477457</v>
+        <v>477397</v>
       </c>
       <c r="R37" t="n">
-        <v>7069186</v>
+        <v>7069068</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4429,7 +4435,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4456,10 +4462,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120040146</v>
+        <v>120040199</v>
       </c>
       <c r="B38" t="n">
-        <v>57310</v>
+        <v>90558</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4472,21 +4478,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4496,10 +4502,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>477599</v>
+        <v>477671</v>
       </c>
       <c r="R38" t="n">
-        <v>7069105</v>
+        <v>7068973</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4532,11 +4538,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4563,7 +4564,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120040154</v>
+        <v>120040170</v>
       </c>
       <c r="B39" t="n">
         <v>57310</v>
@@ -4603,10 +4604,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>477476</v>
+        <v>477755</v>
       </c>
       <c r="R39" t="n">
-        <v>7069264</v>
+        <v>7069016</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4670,7 +4671,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120040158</v>
+        <v>120040138</v>
       </c>
       <c r="B40" t="n">
         <v>57310</v>
@@ -4710,10 +4711,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>477446</v>
+        <v>477726</v>
       </c>
       <c r="R40" t="n">
-        <v>7069039</v>
+        <v>7069062</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4750,7 +4751,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4777,7 +4778,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120040168</v>
+        <v>120040167</v>
       </c>
       <c r="B41" t="n">
         <v>57310</v>
@@ -4817,10 +4818,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>477664</v>
+        <v>477641</v>
       </c>
       <c r="R41" t="n">
-        <v>7068971</v>
+        <v>7068958</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4857,7 +4858,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack ganska färska</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4884,10 +4885,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120040204</v>
+        <v>120040187</v>
       </c>
       <c r="B42" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4896,25 +4897,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4924,10 +4925,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>477534</v>
+        <v>477525</v>
       </c>
       <c r="R42" t="n">
-        <v>7069288</v>
+        <v>7069106</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4986,10 +4987,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120040166</v>
+        <v>120040188</v>
       </c>
       <c r="B43" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4998,25 +4999,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5026,10 +5027,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>477622</v>
+        <v>477454</v>
       </c>
       <c r="R43" t="n">
-        <v>7068965</v>
+        <v>7069190</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5062,11 +5063,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5093,7 +5089,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120040161</v>
+        <v>120040175</v>
       </c>
       <c r="B44" t="n">
         <v>57310</v>
@@ -5126,17 +5122,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>477426</v>
+        <v>477822</v>
       </c>
       <c r="R44" t="n">
-        <v>7068947</v>
+        <v>7069037</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5169,11 +5185,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5200,10 +5211,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120040181</v>
+        <v>120040207</v>
       </c>
       <c r="B45" t="n">
-        <v>79607</v>
+        <v>86878</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5216,21 +5227,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>510</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5240,10 +5251,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>477437</v>
+        <v>477473</v>
       </c>
       <c r="R45" t="n">
-        <v>7068991</v>
+        <v>7069007</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5302,10 +5313,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120040191</v>
+        <v>120040172</v>
       </c>
       <c r="B46" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5314,25 +5325,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5342,10 +5353,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>477440</v>
+        <v>477777</v>
       </c>
       <c r="R46" t="n">
-        <v>7069251</v>
+        <v>7069022</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5378,6 +5389,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5404,10 +5420,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120040139</v>
+        <v>120040182</v>
       </c>
       <c r="B47" t="n">
-        <v>57310</v>
+        <v>57421</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5416,20 +5432,20 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -5437,17 +5453,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>477517</v>
+        <v>477760</v>
       </c>
       <c r="R47" t="n">
-        <v>7068992</v>
+        <v>7069037</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5480,11 +5508,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5511,7 +5534,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120040157</v>
+        <v>120040174</v>
       </c>
       <c r="B48" t="n">
         <v>57310</v>
@@ -5551,10 +5574,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>477397</v>
+        <v>477825</v>
       </c>
       <c r="R48" t="n">
-        <v>7069068</v>
+        <v>7069031</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5591,7 +5614,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5618,10 +5641,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120040135</v>
+        <v>120040144</v>
       </c>
       <c r="B49" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5634,21 +5657,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5658,10 +5681,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>477507</v>
+        <v>477644</v>
       </c>
       <c r="R49" t="n">
-        <v>7069055</v>
+        <v>7069114</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5694,6 +5717,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5720,7 +5748,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120040169</v>
+        <v>120040142</v>
       </c>
       <c r="B50" t="n">
         <v>57310</v>
@@ -5760,10 +5788,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>477688</v>
+        <v>477614</v>
       </c>
       <c r="R50" t="n">
-        <v>7069010</v>
+        <v>7069089</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5827,10 +5855,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120040173</v>
+        <v>120040183</v>
       </c>
       <c r="B51" t="n">
-        <v>57310</v>
+        <v>57421</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5839,20 +5867,20 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -5860,17 +5888,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>477786</v>
+        <v>477821</v>
       </c>
       <c r="R51" t="n">
-        <v>7069029</v>
+        <v>7069026</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5903,11 +5943,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5934,7 +5969,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120040145</v>
+        <v>120040149</v>
       </c>
       <c r="B52" t="n">
         <v>57310</v>
@@ -5974,10 +6009,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>477626</v>
+        <v>477423</v>
       </c>
       <c r="R52" t="n">
-        <v>7069105</v>
+        <v>7069180</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6041,10 +6076,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120040149</v>
+        <v>120040190</v>
       </c>
       <c r="B53" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6053,25 +6088,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6081,10 +6116,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>477423</v>
+        <v>477530</v>
       </c>
       <c r="R53" t="n">
-        <v>7069180</v>
+        <v>7069276</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6117,11 +6152,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6148,10 +6178,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120040136</v>
+        <v>120040159</v>
       </c>
       <c r="B54" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6164,21 +6194,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6188,10 +6218,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>477434</v>
+        <v>477444</v>
       </c>
       <c r="R54" t="n">
-        <v>7069116</v>
+        <v>7068963</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6224,6 +6254,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack ganska färska till äldre</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6250,7 +6285,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120040170</v>
+        <v>120040141</v>
       </c>
       <c r="B55" t="n">
         <v>57310</v>
@@ -6290,10 +6325,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>477755</v>
+        <v>477562</v>
       </c>
       <c r="R55" t="n">
-        <v>7069016</v>
+        <v>7069078</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6357,10 +6392,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120040175</v>
+        <v>120040205</v>
       </c>
       <c r="B56" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6373,54 +6408,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>477822</v>
+        <v>477382</v>
       </c>
       <c r="R56" t="n">
-        <v>7069037</v>
+        <v>7069247</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6479,7 +6494,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120040172</v>
+        <v>120040152</v>
       </c>
       <c r="B57" t="n">
         <v>57310</v>
@@ -6519,10 +6534,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>477777</v>
+        <v>477472</v>
       </c>
       <c r="R57" t="n">
-        <v>7069022</v>
+        <v>7069168</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6586,7 +6601,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120040147</v>
+        <v>120040150</v>
       </c>
       <c r="B58" t="n">
         <v>57310</v>
@@ -6626,10 +6641,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>477581</v>
+        <v>477457</v>
       </c>
       <c r="R58" t="n">
-        <v>7069095</v>
+        <v>7069186</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6693,10 +6708,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120040160</v>
+        <v>120040180</v>
       </c>
       <c r="B59" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6709,21 +6724,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6733,10 +6748,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>477440</v>
+        <v>477415</v>
       </c>
       <c r="R59" t="n">
-        <v>7068958</v>
+        <v>7069070</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6769,11 +6784,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6800,7 +6810,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120040165</v>
+        <v>120040147</v>
       </c>
       <c r="B60" t="n">
         <v>57310</v>
@@ -6840,10 +6850,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>477596</v>
+        <v>477581</v>
       </c>
       <c r="R60" t="n">
-        <v>7068950</v>
+        <v>7069095</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6880,7 +6890,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6907,10 +6917,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120040177</v>
+        <v>120040179</v>
       </c>
       <c r="B61" t="n">
-        <v>57310</v>
+        <v>79608</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6923,21 +6933,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6947,10 +6957,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>477856</v>
+        <v>477437</v>
       </c>
       <c r="R61" t="n">
-        <v>7069020</v>
+        <v>7068991</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6983,11 +6993,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7014,10 +7019,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120040141</v>
+        <v>120040136</v>
       </c>
       <c r="B62" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7030,21 +7035,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7054,10 +7059,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>477562</v>
+        <v>477434</v>
       </c>
       <c r="R62" t="n">
-        <v>7069078</v>
+        <v>7069116</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7090,11 +7095,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7121,10 +7121,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120040190</v>
+        <v>120040203</v>
       </c>
       <c r="B63" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7133,25 +7133,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7161,10 +7161,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>477530</v>
+        <v>477472</v>
       </c>
       <c r="R63" t="n">
-        <v>7069276</v>
+        <v>7069087</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7223,7 +7223,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120040151</v>
+        <v>120040154</v>
       </c>
       <c r="B64" t="n">
         <v>57310</v>
@@ -7263,10 +7263,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>477460</v>
+        <v>477476</v>
       </c>
       <c r="R64" t="n">
-        <v>7069166</v>
+        <v>7069264</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7303,7 +7303,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Ringhack färska och något äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD64" t="b">

--- a/artfynd/A 36309-2024 artfynd.xlsx
+++ b/artfynd/A 36309-2024 artfynd.xlsx
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120040160</v>
+        <v>120040206</v>
       </c>
       <c r="B4" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477440</v>
+        <v>477405</v>
       </c>
       <c r="R4" t="n">
-        <v>7068958</v>
+        <v>7069105</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,11 +955,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120040158</v>
+        <v>120040160</v>
       </c>
       <c r="B5" t="n">
         <v>57310</v>
@@ -1026,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477446</v>
+        <v>477440</v>
       </c>
       <c r="R5" t="n">
-        <v>7069039</v>
+        <v>7068958</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1061,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120040206</v>
+        <v>120040158</v>
       </c>
       <c r="B6" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477405</v>
+        <v>477446</v>
       </c>
       <c r="R6" t="n">
-        <v>7069105</v>
+        <v>7069039</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,6 +1164,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1939,10 +1939,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120040169</v>
+        <v>120040191</v>
       </c>
       <c r="B14" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1951,25 +1951,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1979,10 +1979,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>477688</v>
+        <v>477440</v>
       </c>
       <c r="R14" t="n">
-        <v>7069010</v>
+        <v>7069251</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2015,11 +2015,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2046,7 +2041,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120040177</v>
+        <v>120040169</v>
       </c>
       <c r="B15" t="n">
         <v>57310</v>
@@ -2086,10 +2081,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>477856</v>
+        <v>477688</v>
       </c>
       <c r="R15" t="n">
-        <v>7069020</v>
+        <v>7069010</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2126,7 +2121,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2153,10 +2148,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120040191</v>
+        <v>120040177</v>
       </c>
       <c r="B16" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2165,25 +2160,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2193,10 +2188,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>477440</v>
+        <v>477856</v>
       </c>
       <c r="R16" t="n">
-        <v>7069251</v>
+        <v>7069020</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2229,6 +2224,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -3198,10 +3198,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120040189</v>
+        <v>120040140</v>
       </c>
       <c r="B26" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3210,25 +3210,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3238,10 +3238,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>477498</v>
+        <v>477472</v>
       </c>
       <c r="R26" t="n">
-        <v>7069206</v>
+        <v>7069006</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3274,6 +3274,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3300,7 +3305,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120040192</v>
+        <v>120040189</v>
       </c>
       <c r="B27" t="n">
         <v>97907</v>
@@ -3340,10 +3345,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>477445</v>
+        <v>477498</v>
       </c>
       <c r="R27" t="n">
-        <v>7068977</v>
+        <v>7069206</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3402,10 +3407,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120040161</v>
+        <v>120040192</v>
       </c>
       <c r="B28" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3414,25 +3419,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3442,10 +3447,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>477426</v>
+        <v>477445</v>
       </c>
       <c r="R28" t="n">
-        <v>7068947</v>
+        <v>7068977</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3478,11 +3483,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3509,7 +3509,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120040140</v>
+        <v>120040161</v>
       </c>
       <c r="B29" t="n">
         <v>57310</v>
@@ -3549,10 +3549,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>477472</v>
+        <v>477426</v>
       </c>
       <c r="R29" t="n">
-        <v>7069006</v>
+        <v>7068947</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4671,10 +4671,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120040138</v>
+        <v>120040187</v>
       </c>
       <c r="B40" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4683,25 +4683,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4711,10 +4711,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>477726</v>
+        <v>477525</v>
       </c>
       <c r="R40" t="n">
-        <v>7069062</v>
+        <v>7069106</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4747,11 +4747,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4778,10 +4773,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120040167</v>
+        <v>120040188</v>
       </c>
       <c r="B41" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4790,25 +4785,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4818,10 +4813,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>477641</v>
+        <v>477454</v>
       </c>
       <c r="R41" t="n">
-        <v>7068958</v>
+        <v>7069190</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4854,11 +4849,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack ganska färska</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4885,10 +4875,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120040187</v>
+        <v>120040138</v>
       </c>
       <c r="B42" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4897,25 +4887,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4925,10 +4915,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>477525</v>
+        <v>477726</v>
       </c>
       <c r="R42" t="n">
-        <v>7069106</v>
+        <v>7069062</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4961,6 +4951,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4987,10 +4982,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120040188</v>
+        <v>120040167</v>
       </c>
       <c r="B43" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4999,25 +4994,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5027,10 +5022,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>477454</v>
+        <v>477641</v>
       </c>
       <c r="R43" t="n">
-        <v>7069190</v>
+        <v>7068958</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5063,6 +5058,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack ganska färska</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5313,10 +5313,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120040172</v>
+        <v>120040182</v>
       </c>
       <c r="B46" t="n">
-        <v>57310</v>
+        <v>57421</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5325,20 +5325,20 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5346,17 +5346,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>477777</v>
+        <v>477760</v>
       </c>
       <c r="R46" t="n">
-        <v>7069022</v>
+        <v>7069037</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5389,11 +5401,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5420,10 +5427,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120040182</v>
+        <v>120040172</v>
       </c>
       <c r="B47" t="n">
-        <v>57421</v>
+        <v>57310</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5432,20 +5439,20 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -5453,29 +5460,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>477760</v>
+        <v>477777</v>
       </c>
       <c r="R47" t="n">
-        <v>7069037</v>
+        <v>7069022</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5508,6 +5503,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5534,10 +5534,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120040174</v>
+        <v>120040183</v>
       </c>
       <c r="B48" t="n">
-        <v>57310</v>
+        <v>57421</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5546,20 +5546,20 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -5567,17 +5567,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>477825</v>
+        <v>477821</v>
       </c>
       <c r="R48" t="n">
-        <v>7069031</v>
+        <v>7069026</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5610,11 +5622,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5641,7 +5648,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120040144</v>
+        <v>120040174</v>
       </c>
       <c r="B49" t="n">
         <v>57310</v>
@@ -5681,10 +5688,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>477644</v>
+        <v>477825</v>
       </c>
       <c r="R49" t="n">
-        <v>7069114</v>
+        <v>7069031</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5748,7 +5755,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120040142</v>
+        <v>120040144</v>
       </c>
       <c r="B50" t="n">
         <v>57310</v>
@@ -5788,10 +5795,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>477614</v>
+        <v>477644</v>
       </c>
       <c r="R50" t="n">
-        <v>7069089</v>
+        <v>7069114</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5855,10 +5862,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120040183</v>
+        <v>120040142</v>
       </c>
       <c r="B51" t="n">
-        <v>57421</v>
+        <v>57310</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5867,20 +5874,20 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -5888,29 +5895,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>477821</v>
+        <v>477614</v>
       </c>
       <c r="R51" t="n">
-        <v>7069026</v>
+        <v>7069089</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5943,6 +5938,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6392,10 +6392,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120040205</v>
+        <v>120040152</v>
       </c>
       <c r="B56" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6408,21 +6408,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6432,10 +6432,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>477382</v>
+        <v>477472</v>
       </c>
       <c r="R56" t="n">
-        <v>7069247</v>
+        <v>7069168</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6468,6 +6468,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6494,7 +6499,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120040152</v>
+        <v>120040150</v>
       </c>
       <c r="B57" t="n">
         <v>57310</v>
@@ -6534,10 +6539,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>477472</v>
+        <v>477457</v>
       </c>
       <c r="R57" t="n">
-        <v>7069168</v>
+        <v>7069186</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6601,10 +6606,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120040150</v>
+        <v>120040205</v>
       </c>
       <c r="B58" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6617,21 +6622,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6641,10 +6646,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>477457</v>
+        <v>477382</v>
       </c>
       <c r="R58" t="n">
-        <v>7069186</v>
+        <v>7069247</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6677,11 +6682,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD58" t="b">

--- a/artfynd/A 36309-2024 artfynd.xlsx
+++ b/artfynd/A 36309-2024 artfynd.xlsx
@@ -5313,10 +5313,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120040182</v>
+        <v>120040172</v>
       </c>
       <c r="B46" t="n">
-        <v>57421</v>
+        <v>57310</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5325,20 +5325,20 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5346,29 +5346,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>477760</v>
+        <v>477777</v>
       </c>
       <c r="R46" t="n">
-        <v>7069037</v>
+        <v>7069022</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5401,6 +5389,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5427,10 +5420,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120040172</v>
+        <v>120040182</v>
       </c>
       <c r="B47" t="n">
-        <v>57310</v>
+        <v>57421</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5439,20 +5432,20 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -5460,17 +5453,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>477777</v>
+        <v>477760</v>
       </c>
       <c r="R47" t="n">
-        <v>7069022</v>
+        <v>7069037</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5503,11 +5508,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5534,10 +5534,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120040183</v>
+        <v>120040174</v>
       </c>
       <c r="B48" t="n">
-        <v>57421</v>
+        <v>57310</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5546,20 +5546,20 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -5567,29 +5567,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>477821</v>
+        <v>477825</v>
       </c>
       <c r="R48" t="n">
-        <v>7069026</v>
+        <v>7069031</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5622,6 +5610,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5648,7 +5641,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120040174</v>
+        <v>120040144</v>
       </c>
       <c r="B49" t="n">
         <v>57310</v>
@@ -5688,10 +5681,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>477825</v>
+        <v>477644</v>
       </c>
       <c r="R49" t="n">
-        <v>7069031</v>
+        <v>7069114</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5755,7 +5748,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120040144</v>
+        <v>120040142</v>
       </c>
       <c r="B50" t="n">
         <v>57310</v>
@@ -5795,10 +5788,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>477644</v>
+        <v>477614</v>
       </c>
       <c r="R50" t="n">
-        <v>7069114</v>
+        <v>7069089</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5862,10 +5855,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120040142</v>
+        <v>120040183</v>
       </c>
       <c r="B51" t="n">
-        <v>57310</v>
+        <v>57421</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5874,20 +5867,20 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -5895,17 +5888,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>477614</v>
+        <v>477821</v>
       </c>
       <c r="R51" t="n">
-        <v>7069089</v>
+        <v>7069026</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5938,11 +5943,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6392,10 +6392,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120040152</v>
+        <v>120040205</v>
       </c>
       <c r="B56" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6408,21 +6408,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6432,10 +6432,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>477472</v>
+        <v>477382</v>
       </c>
       <c r="R56" t="n">
-        <v>7069168</v>
+        <v>7069247</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6468,11 +6468,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6499,7 +6494,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120040150</v>
+        <v>120040152</v>
       </c>
       <c r="B57" t="n">
         <v>57310</v>
@@ -6539,10 +6534,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>477457</v>
+        <v>477472</v>
       </c>
       <c r="R57" t="n">
-        <v>7069186</v>
+        <v>7069168</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6606,10 +6601,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120040205</v>
+        <v>120040150</v>
       </c>
       <c r="B58" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6622,21 +6617,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6646,10 +6641,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>477382</v>
+        <v>477457</v>
       </c>
       <c r="R58" t="n">
-        <v>7069247</v>
+        <v>7069186</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6682,6 +6677,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD58" t="b">

--- a/artfynd/A 36309-2024 artfynd.xlsx
+++ b/artfynd/A 36309-2024 artfynd.xlsx
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120040206</v>
+        <v>120040160</v>
       </c>
       <c r="B4" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477405</v>
+        <v>477440</v>
       </c>
       <c r="R4" t="n">
-        <v>7069105</v>
+        <v>7068958</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,6 +955,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,7 +986,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120040160</v>
+        <v>120040158</v>
       </c>
       <c r="B5" t="n">
         <v>57310</v>
@@ -1021,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477440</v>
+        <v>477446</v>
       </c>
       <c r="R5" t="n">
-        <v>7068958</v>
+        <v>7069039</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,7 +1066,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120040158</v>
+        <v>120040206</v>
       </c>
       <c r="B6" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477446</v>
+        <v>477405</v>
       </c>
       <c r="R6" t="n">
-        <v>7069039</v>
+        <v>7069105</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1164,11 +1169,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -3198,10 +3198,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120040140</v>
+        <v>120040189</v>
       </c>
       <c r="B26" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3210,25 +3210,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3238,10 +3238,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>477472</v>
+        <v>477498</v>
       </c>
       <c r="R26" t="n">
-        <v>7069006</v>
+        <v>7069206</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3274,11 +3274,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3305,7 +3300,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120040189</v>
+        <v>120040192</v>
       </c>
       <c r="B27" t="n">
         <v>97907</v>
@@ -3345,10 +3340,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>477498</v>
+        <v>477445</v>
       </c>
       <c r="R27" t="n">
-        <v>7069206</v>
+        <v>7068977</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3407,10 +3402,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120040192</v>
+        <v>120040161</v>
       </c>
       <c r="B28" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3419,25 +3414,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3447,10 +3442,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>477445</v>
+        <v>477426</v>
       </c>
       <c r="R28" t="n">
-        <v>7068977</v>
+        <v>7068947</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3483,6 +3478,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3509,7 +3509,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120040161</v>
+        <v>120040140</v>
       </c>
       <c r="B29" t="n">
         <v>57310</v>
@@ -3549,10 +3549,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>477426</v>
+        <v>477472</v>
       </c>
       <c r="R29" t="n">
-        <v>7068947</v>
+        <v>7069006</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -5534,10 +5534,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120040174</v>
+        <v>120040183</v>
       </c>
       <c r="B48" t="n">
-        <v>57310</v>
+        <v>57421</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5546,20 +5546,20 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -5567,17 +5567,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>477825</v>
+        <v>477821</v>
       </c>
       <c r="R48" t="n">
-        <v>7069031</v>
+        <v>7069026</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5610,11 +5622,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5641,7 +5648,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120040144</v>
+        <v>120040174</v>
       </c>
       <c r="B49" t="n">
         <v>57310</v>
@@ -5681,10 +5688,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>477644</v>
+        <v>477825</v>
       </c>
       <c r="R49" t="n">
-        <v>7069114</v>
+        <v>7069031</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5748,7 +5755,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120040142</v>
+        <v>120040144</v>
       </c>
       <c r="B50" t="n">
         <v>57310</v>
@@ -5788,10 +5795,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>477614</v>
+        <v>477644</v>
       </c>
       <c r="R50" t="n">
-        <v>7069089</v>
+        <v>7069114</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5855,10 +5862,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120040183</v>
+        <v>120040142</v>
       </c>
       <c r="B51" t="n">
-        <v>57421</v>
+        <v>57310</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5867,20 +5874,20 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -5888,29 +5895,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>477821</v>
+        <v>477614</v>
       </c>
       <c r="R51" t="n">
-        <v>7069026</v>
+        <v>7069089</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5943,6 +5938,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6392,10 +6392,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120040205</v>
+        <v>120040152</v>
       </c>
       <c r="B56" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6408,21 +6408,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6432,10 +6432,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>477382</v>
+        <v>477472</v>
       </c>
       <c r="R56" t="n">
-        <v>7069247</v>
+        <v>7069168</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6468,6 +6468,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6494,7 +6499,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120040152</v>
+        <v>120040150</v>
       </c>
       <c r="B57" t="n">
         <v>57310</v>
@@ -6534,10 +6539,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>477472</v>
+        <v>477457</v>
       </c>
       <c r="R57" t="n">
-        <v>7069168</v>
+        <v>7069186</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6601,10 +6606,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120040150</v>
+        <v>120040205</v>
       </c>
       <c r="B58" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6617,21 +6622,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6641,10 +6646,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>477457</v>
+        <v>477382</v>
       </c>
       <c r="R58" t="n">
-        <v>7069186</v>
+        <v>7069247</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6677,11 +6682,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD58" t="b">

--- a/artfynd/A 36309-2024 artfynd.xlsx
+++ b/artfynd/A 36309-2024 artfynd.xlsx
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120040160</v>
+        <v>120040206</v>
       </c>
       <c r="B4" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477440</v>
+        <v>477405</v>
       </c>
       <c r="R4" t="n">
-        <v>7068958</v>
+        <v>7069105</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,11 +955,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120040158</v>
+        <v>120040160</v>
       </c>
       <c r="B5" t="n">
         <v>57310</v>
@@ -1026,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477446</v>
+        <v>477440</v>
       </c>
       <c r="R5" t="n">
-        <v>7069039</v>
+        <v>7068958</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1061,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120040206</v>
+        <v>120040158</v>
       </c>
       <c r="B6" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477405</v>
+        <v>477446</v>
       </c>
       <c r="R6" t="n">
-        <v>7069105</v>
+        <v>7069039</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,6 +1164,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1837,10 +1837,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120040181</v>
+        <v>120040169</v>
       </c>
       <c r="B13" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1853,21 +1853,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1877,10 +1877,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>477437</v>
+        <v>477688</v>
       </c>
       <c r="R13" t="n">
-        <v>7068991</v>
+        <v>7069010</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1913,6 +1913,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1939,10 +1944,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120040191</v>
+        <v>120040181</v>
       </c>
       <c r="B14" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1951,25 +1956,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1979,10 +1984,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>477440</v>
+        <v>477437</v>
       </c>
       <c r="R14" t="n">
-        <v>7069251</v>
+        <v>7068991</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2041,7 +2046,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120040169</v>
+        <v>120040177</v>
       </c>
       <c r="B15" t="n">
         <v>57310</v>
@@ -2081,10 +2086,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>477688</v>
+        <v>477856</v>
       </c>
       <c r="R15" t="n">
-        <v>7069010</v>
+        <v>7069020</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2121,7 +2126,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2148,10 +2153,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120040177</v>
+        <v>120040191</v>
       </c>
       <c r="B16" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2160,25 +2165,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2188,10 +2193,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>477856</v>
+        <v>477440</v>
       </c>
       <c r="R16" t="n">
-        <v>7069020</v>
+        <v>7069251</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2224,11 +2229,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -4671,10 +4671,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120040187</v>
+        <v>120040138</v>
       </c>
       <c r="B40" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4683,25 +4683,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4711,10 +4711,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>477525</v>
+        <v>477726</v>
       </c>
       <c r="R40" t="n">
-        <v>7069106</v>
+        <v>7069062</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4747,6 +4747,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4773,10 +4778,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120040188</v>
+        <v>120040167</v>
       </c>
       <c r="B41" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4785,25 +4790,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4813,10 +4818,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>477454</v>
+        <v>477641</v>
       </c>
       <c r="R41" t="n">
-        <v>7069190</v>
+        <v>7068958</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4849,6 +4854,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack ganska färska</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4875,10 +4885,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120040138</v>
+        <v>120040187</v>
       </c>
       <c r="B42" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4887,25 +4897,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4915,10 +4925,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>477726</v>
+        <v>477525</v>
       </c>
       <c r="R42" t="n">
-        <v>7069062</v>
+        <v>7069106</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4951,11 +4961,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4982,10 +4987,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120040167</v>
+        <v>120040188</v>
       </c>
       <c r="B43" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4994,25 +4999,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5022,10 +5027,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>477641</v>
+        <v>477454</v>
       </c>
       <c r="R43" t="n">
-        <v>7068958</v>
+        <v>7069190</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5058,11 +5063,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack ganska färska</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5534,10 +5534,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120040183</v>
+        <v>120040174</v>
       </c>
       <c r="B48" t="n">
-        <v>57421</v>
+        <v>57310</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5546,20 +5546,20 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -5567,29 +5567,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>477821</v>
+        <v>477825</v>
       </c>
       <c r="R48" t="n">
-        <v>7069026</v>
+        <v>7069031</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5622,6 +5610,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5648,7 +5641,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120040174</v>
+        <v>120040144</v>
       </c>
       <c r="B49" t="n">
         <v>57310</v>
@@ -5688,10 +5681,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>477825</v>
+        <v>477644</v>
       </c>
       <c r="R49" t="n">
-        <v>7069031</v>
+        <v>7069114</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5755,7 +5748,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120040144</v>
+        <v>120040142</v>
       </c>
       <c r="B50" t="n">
         <v>57310</v>
@@ -5795,10 +5788,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>477644</v>
+        <v>477614</v>
       </c>
       <c r="R50" t="n">
-        <v>7069114</v>
+        <v>7069089</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5862,10 +5855,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120040142</v>
+        <v>120040183</v>
       </c>
       <c r="B51" t="n">
-        <v>57310</v>
+        <v>57421</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5874,20 +5867,20 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -5895,17 +5888,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>477614</v>
+        <v>477821</v>
       </c>
       <c r="R51" t="n">
-        <v>7069089</v>
+        <v>7069026</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5938,11 +5943,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6076,10 +6076,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120040190</v>
+        <v>120040159</v>
       </c>
       <c r="B53" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6088,25 +6088,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6116,10 +6116,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>477530</v>
+        <v>477444</v>
       </c>
       <c r="R53" t="n">
-        <v>7069276</v>
+        <v>7068963</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6152,6 +6152,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack ganska färska till äldre</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6178,10 +6183,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120040159</v>
+        <v>120040190</v>
       </c>
       <c r="B54" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6190,25 +6195,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6218,10 +6223,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>477444</v>
+        <v>477530</v>
       </c>
       <c r="R54" t="n">
-        <v>7068963</v>
+        <v>7069276</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6254,11 +6259,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack ganska färska till äldre</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6392,10 +6392,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120040152</v>
+        <v>120040205</v>
       </c>
       <c r="B56" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6408,21 +6408,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6432,10 +6432,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>477472</v>
+        <v>477382</v>
       </c>
       <c r="R56" t="n">
-        <v>7069168</v>
+        <v>7069247</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6468,11 +6468,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6499,7 +6494,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120040150</v>
+        <v>120040152</v>
       </c>
       <c r="B57" t="n">
         <v>57310</v>
@@ -6539,10 +6534,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>477457</v>
+        <v>477472</v>
       </c>
       <c r="R57" t="n">
-        <v>7069186</v>
+        <v>7069168</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6606,10 +6601,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120040205</v>
+        <v>120040150</v>
       </c>
       <c r="B58" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6622,21 +6617,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6646,10 +6641,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>477382</v>
+        <v>477457</v>
       </c>
       <c r="R58" t="n">
-        <v>7069247</v>
+        <v>7069186</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6682,6 +6677,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD58" t="b">

--- a/artfynd/A 36309-2024 artfynd.xlsx
+++ b/artfynd/A 36309-2024 artfynd.xlsx
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120040206</v>
+        <v>120040160</v>
       </c>
       <c r="B4" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477405</v>
+        <v>477440</v>
       </c>
       <c r="R4" t="n">
-        <v>7069105</v>
+        <v>7068958</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,6 +955,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,7 +986,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120040160</v>
+        <v>120040158</v>
       </c>
       <c r="B5" t="n">
         <v>57310</v>
@@ -1021,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477440</v>
+        <v>477446</v>
       </c>
       <c r="R5" t="n">
-        <v>7068958</v>
+        <v>7069039</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,7 +1066,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120040158</v>
+        <v>120040206</v>
       </c>
       <c r="B6" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477446</v>
+        <v>477405</v>
       </c>
       <c r="R6" t="n">
-        <v>7069039</v>
+        <v>7069105</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1164,11 +1169,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -3198,10 +3198,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120040189</v>
+        <v>120040140</v>
       </c>
       <c r="B26" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3210,25 +3210,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3238,10 +3238,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>477498</v>
+        <v>477472</v>
       </c>
       <c r="R26" t="n">
-        <v>7069206</v>
+        <v>7069006</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3274,6 +3274,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3300,7 +3305,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120040192</v>
+        <v>120040189</v>
       </c>
       <c r="B27" t="n">
         <v>97907</v>
@@ -3340,10 +3345,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>477445</v>
+        <v>477498</v>
       </c>
       <c r="R27" t="n">
-        <v>7068977</v>
+        <v>7069206</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3402,10 +3407,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120040161</v>
+        <v>120040192</v>
       </c>
       <c r="B28" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3414,25 +3419,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3442,10 +3447,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>477426</v>
+        <v>477445</v>
       </c>
       <c r="R28" t="n">
-        <v>7068947</v>
+        <v>7068977</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3478,11 +3483,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3509,7 +3509,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120040140</v>
+        <v>120040161</v>
       </c>
       <c r="B29" t="n">
         <v>57310</v>
@@ -3549,10 +3549,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>477472</v>
+        <v>477426</v>
       </c>
       <c r="R29" t="n">
-        <v>7069006</v>
+        <v>7068947</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -5534,10 +5534,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120040174</v>
+        <v>120040183</v>
       </c>
       <c r="B48" t="n">
-        <v>57310</v>
+        <v>57421</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5546,20 +5546,20 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -5567,17 +5567,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>477825</v>
+        <v>477821</v>
       </c>
       <c r="R48" t="n">
-        <v>7069031</v>
+        <v>7069026</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5610,11 +5622,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5641,7 +5648,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120040144</v>
+        <v>120040174</v>
       </c>
       <c r="B49" t="n">
         <v>57310</v>
@@ -5681,10 +5688,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>477644</v>
+        <v>477825</v>
       </c>
       <c r="R49" t="n">
-        <v>7069114</v>
+        <v>7069031</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5748,7 +5755,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120040142</v>
+        <v>120040144</v>
       </c>
       <c r="B50" t="n">
         <v>57310</v>
@@ -5788,10 +5795,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>477614</v>
+        <v>477644</v>
       </c>
       <c r="R50" t="n">
-        <v>7069089</v>
+        <v>7069114</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5855,10 +5862,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120040183</v>
+        <v>120040142</v>
       </c>
       <c r="B51" t="n">
-        <v>57421</v>
+        <v>57310</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5867,20 +5874,20 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -5888,29 +5895,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>477821</v>
+        <v>477614</v>
       </c>
       <c r="R51" t="n">
-        <v>7069026</v>
+        <v>7069089</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5943,6 +5938,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD51" t="b">

--- a/artfynd/A 36309-2024 artfynd.xlsx
+++ b/artfynd/A 36309-2024 artfynd.xlsx
@@ -4671,10 +4671,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120040138</v>
+        <v>120040187</v>
       </c>
       <c r="B40" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4683,25 +4683,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4711,10 +4711,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>477726</v>
+        <v>477525</v>
       </c>
       <c r="R40" t="n">
-        <v>7069062</v>
+        <v>7069106</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4747,11 +4747,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4778,10 +4773,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120040167</v>
+        <v>120040188</v>
       </c>
       <c r="B41" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4790,25 +4785,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4818,10 +4813,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>477641</v>
+        <v>477454</v>
       </c>
       <c r="R41" t="n">
-        <v>7068958</v>
+        <v>7069190</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4854,11 +4849,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack ganska färska</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4885,10 +4875,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120040187</v>
+        <v>120040138</v>
       </c>
       <c r="B42" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4897,25 +4887,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4925,10 +4915,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>477525</v>
+        <v>477726</v>
       </c>
       <c r="R42" t="n">
-        <v>7069106</v>
+        <v>7069062</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4961,6 +4951,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4987,10 +4982,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120040188</v>
+        <v>120040167</v>
       </c>
       <c r="B43" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4999,25 +4994,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5027,10 +5022,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>477454</v>
+        <v>477641</v>
       </c>
       <c r="R43" t="n">
-        <v>7069190</v>
+        <v>7068958</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5063,6 +5058,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack ganska färska</t>
         </is>
       </c>
       <c r="AD43" t="b">

--- a/artfynd/A 36309-2024 artfynd.xlsx
+++ b/artfynd/A 36309-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120040202</v>
+        <v>120040185</v>
       </c>
       <c r="B2" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477674</v>
+        <v>477507</v>
       </c>
       <c r="R2" t="n">
-        <v>7069000</v>
+        <v>7069056</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120040201</v>
+        <v>120040202</v>
       </c>
       <c r="B3" t="n">
-        <v>90580</v>
+        <v>90598</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477484</v>
+        <v>477674</v>
       </c>
       <c r="R3" t="n">
-        <v>7068927</v>
+        <v>7069000</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120040160</v>
+        <v>120040201</v>
       </c>
       <c r="B4" t="n">
-        <v>57310</v>
+        <v>90598</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477440</v>
+        <v>477484</v>
       </c>
       <c r="R4" t="n">
-        <v>7068958</v>
+        <v>7068927</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,11 +955,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120040158</v>
+        <v>120040172</v>
       </c>
       <c r="B5" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1026,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477446</v>
+        <v>477777</v>
       </c>
       <c r="R5" t="n">
-        <v>7069039</v>
+        <v>7069022</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1061,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120040206</v>
+        <v>120040160</v>
       </c>
       <c r="B6" t="n">
-        <v>78526</v>
+        <v>57320</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477405</v>
+        <v>477440</v>
       </c>
       <c r="R6" t="n">
-        <v>7069105</v>
+        <v>7068958</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,6 +1164,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120040146</v>
+        <v>120040154</v>
       </c>
       <c r="B7" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477599</v>
+        <v>477476</v>
       </c>
       <c r="R7" t="n">
-        <v>7069105</v>
+        <v>7069264</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1302,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120040153</v>
+        <v>120040171</v>
       </c>
       <c r="B8" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1342,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477547</v>
+        <v>477759</v>
       </c>
       <c r="R8" t="n">
-        <v>7069271</v>
+        <v>7069019</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1409,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120040165</v>
+        <v>120040204</v>
       </c>
       <c r="B9" t="n">
-        <v>57310</v>
+        <v>78542</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1425,21 +1425,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>477596</v>
+        <v>477534</v>
       </c>
       <c r="R9" t="n">
-        <v>7068950</v>
+        <v>7069288</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1485,11 +1485,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1516,10 +1511,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120040166</v>
+        <v>120040158</v>
       </c>
       <c r="B10" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1556,10 +1551,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>477622</v>
+        <v>477446</v>
       </c>
       <c r="R10" t="n">
-        <v>7068965</v>
+        <v>7069039</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1623,10 +1618,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120040176</v>
+        <v>120040184</v>
       </c>
       <c r="B11" t="n">
-        <v>57310</v>
+        <v>97930</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1635,25 +1630,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1663,10 +1658,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>477852</v>
+        <v>477481</v>
       </c>
       <c r="R11" t="n">
-        <v>7069022</v>
+        <v>7069004</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1699,11 +1694,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack ganska färska till äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1730,10 +1720,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120040145</v>
+        <v>120040152</v>
       </c>
       <c r="B12" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1770,10 +1760,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>477626</v>
+        <v>477472</v>
       </c>
       <c r="R12" t="n">
-        <v>7069105</v>
+        <v>7069168</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1837,10 +1827,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120040169</v>
+        <v>120040173</v>
       </c>
       <c r="B13" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1877,10 +1867,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>477688</v>
+        <v>477786</v>
       </c>
       <c r="R13" t="n">
-        <v>7069010</v>
+        <v>7069029</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1944,10 +1934,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120040181</v>
+        <v>120040177</v>
       </c>
       <c r="B14" t="n">
-        <v>79607</v>
+        <v>57320</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1960,21 +1950,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1984,10 +1974,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>477437</v>
+        <v>477856</v>
       </c>
       <c r="R14" t="n">
-        <v>7068991</v>
+        <v>7069020</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2020,6 +2010,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2046,10 +2041,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120040177</v>
+        <v>120040164</v>
       </c>
       <c r="B15" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2086,10 +2081,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>477856</v>
+        <v>477597</v>
       </c>
       <c r="R15" t="n">
-        <v>7069020</v>
+        <v>7068964</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2126,7 +2121,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2153,10 +2148,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120040191</v>
+        <v>120040176</v>
       </c>
       <c r="B16" t="n">
-        <v>97907</v>
+        <v>57320</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2165,25 +2160,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2193,10 +2188,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>477440</v>
+        <v>477852</v>
       </c>
       <c r="R16" t="n">
-        <v>7069251</v>
+        <v>7069022</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2229,6 +2224,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack ganska färska till äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2255,10 +2255,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120040162</v>
+        <v>120040167</v>
       </c>
       <c r="B17" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2295,10 +2295,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>477471</v>
+        <v>477641</v>
       </c>
       <c r="R17" t="n">
-        <v>7068928</v>
+        <v>7068958</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack ganska färska</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2362,10 +2362,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120040139</v>
+        <v>120040150</v>
       </c>
       <c r="B18" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2402,10 +2402,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>477517</v>
+        <v>477457</v>
       </c>
       <c r="R18" t="n">
-        <v>7068992</v>
+        <v>7069186</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2469,10 +2469,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120040134</v>
+        <v>120040149</v>
       </c>
       <c r="B19" t="n">
-        <v>90562</v>
+        <v>57320</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2485,21 +2485,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2509,10 +2509,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>477522</v>
+        <v>477423</v>
       </c>
       <c r="R19" t="n">
-        <v>7068987</v>
+        <v>7069180</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2545,6 +2545,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2571,10 +2576,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120040148</v>
+        <v>120040190</v>
       </c>
       <c r="B20" t="n">
-        <v>57310</v>
+        <v>97930</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2583,25 +2588,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2611,10 +2616,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>477438</v>
+        <v>477530</v>
       </c>
       <c r="R20" t="n">
-        <v>7069178</v>
+        <v>7069276</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2647,11 +2652,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2678,10 +2678,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120040185</v>
+        <v>120040191</v>
       </c>
       <c r="B21" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2718,10 +2718,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>477507</v>
+        <v>477440</v>
       </c>
       <c r="R21" t="n">
-        <v>7069056</v>
+        <v>7069251</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2780,10 +2780,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120040204</v>
+        <v>120040170</v>
       </c>
       <c r="B22" t="n">
-        <v>78526</v>
+        <v>57320</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2796,21 +2796,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2820,10 +2820,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>477534</v>
+        <v>477755</v>
       </c>
       <c r="R22" t="n">
-        <v>7069288</v>
+        <v>7069016</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2856,6 +2856,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2882,10 +2887,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120040163</v>
+        <v>120040203</v>
       </c>
       <c r="B23" t="n">
-        <v>57310</v>
+        <v>78542</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2898,21 +2903,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2922,10 +2927,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>477544</v>
+        <v>477472</v>
       </c>
       <c r="R23" t="n">
-        <v>7068952</v>
+        <v>7069087</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2958,11 +2963,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2989,10 +2989,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120040171</v>
+        <v>120040181</v>
       </c>
       <c r="B24" t="n">
-        <v>57310</v>
+        <v>79623</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3005,21 +3005,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3029,10 +3029,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>477759</v>
+        <v>477437</v>
       </c>
       <c r="R24" t="n">
-        <v>7069019</v>
+        <v>7068991</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3065,11 +3065,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3096,10 +3091,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120040200</v>
+        <v>120040180</v>
       </c>
       <c r="B25" t="n">
-        <v>90580</v>
+        <v>79623</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3112,21 +3107,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3136,10 +3131,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>477439</v>
+        <v>477415</v>
       </c>
       <c r="R25" t="n">
-        <v>7069086</v>
+        <v>7069070</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3198,10 +3193,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120040140</v>
+        <v>120040136</v>
       </c>
       <c r="B26" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3214,21 +3209,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3238,10 +3233,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>477472</v>
+        <v>477434</v>
       </c>
       <c r="R26" t="n">
-        <v>7069006</v>
+        <v>7069116</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3274,11 +3269,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3305,10 +3295,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120040189</v>
+        <v>120040155</v>
       </c>
       <c r="B27" t="n">
-        <v>97907</v>
+        <v>57320</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3317,25 +3307,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3345,10 +3335,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>477498</v>
+        <v>477377</v>
       </c>
       <c r="R27" t="n">
-        <v>7069206</v>
+        <v>7069208</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3381,6 +3371,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3407,10 +3402,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120040192</v>
+        <v>120040174</v>
       </c>
       <c r="B28" t="n">
-        <v>97907</v>
+        <v>57320</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3419,25 +3414,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3447,10 +3442,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>477445</v>
+        <v>477825</v>
       </c>
       <c r="R28" t="n">
-        <v>7068977</v>
+        <v>7069031</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3483,6 +3478,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3509,10 +3509,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120040161</v>
+        <v>120040207</v>
       </c>
       <c r="B29" t="n">
-        <v>57310</v>
+        <v>86895</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3525,21 +3525,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3549,10 +3549,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>477426</v>
+        <v>477473</v>
       </c>
       <c r="R29" t="n">
-        <v>7068947</v>
+        <v>7069007</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3585,11 +3585,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3616,10 +3611,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120040135</v>
+        <v>120040165</v>
       </c>
       <c r="B30" t="n">
-        <v>90562</v>
+        <v>57320</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3632,21 +3627,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3656,10 +3651,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>477507</v>
+        <v>477596</v>
       </c>
       <c r="R30" t="n">
-        <v>7069055</v>
+        <v>7068950</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3692,6 +3687,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3718,10 +3718,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120040156</v>
+        <v>120040159</v>
       </c>
       <c r="B31" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3758,10 +3758,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>477377</v>
+        <v>477444</v>
       </c>
       <c r="R31" t="n">
-        <v>7069208</v>
+        <v>7068963</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack ganska färska till äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3825,10 +3825,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120040173</v>
+        <v>120040157</v>
       </c>
       <c r="B32" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3865,10 +3865,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>477786</v>
+        <v>477397</v>
       </c>
       <c r="R32" t="n">
-        <v>7069029</v>
+        <v>7069068</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3932,10 +3932,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120040151</v>
+        <v>120040153</v>
       </c>
       <c r="B33" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3972,10 +3972,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>477460</v>
+        <v>477547</v>
       </c>
       <c r="R33" t="n">
-        <v>7069166</v>
+        <v>7069271</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4012,7 +4012,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack färska och något äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4039,10 +4039,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120040164</v>
+        <v>120040141</v>
       </c>
       <c r="B34" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4079,10 +4079,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>477597</v>
+        <v>477562</v>
       </c>
       <c r="R34" t="n">
-        <v>7068964</v>
+        <v>7069078</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4119,7 +4119,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4146,10 +4146,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120040168</v>
+        <v>120040145</v>
       </c>
       <c r="B35" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4186,10 +4186,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>477664</v>
+        <v>477626</v>
       </c>
       <c r="R35" t="n">
-        <v>7068971</v>
+        <v>7069105</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4226,7 +4226,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4253,10 +4253,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120040184</v>
+        <v>120040187</v>
       </c>
       <c r="B36" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>477481</v>
+        <v>477525</v>
       </c>
       <c r="R36" t="n">
-        <v>7069004</v>
+        <v>7069106</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4355,10 +4355,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120040157</v>
+        <v>120040166</v>
       </c>
       <c r="B37" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4395,10 +4395,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>477397</v>
+        <v>477622</v>
       </c>
       <c r="R37" t="n">
-        <v>7069068</v>
+        <v>7068965</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4462,10 +4462,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120040199</v>
+        <v>120040151</v>
       </c>
       <c r="B38" t="n">
-        <v>90558</v>
+        <v>57320</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4478,21 +4478,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4502,10 +4502,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>477671</v>
+        <v>477460</v>
       </c>
       <c r="R38" t="n">
-        <v>7068973</v>
+        <v>7069166</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4538,6 +4538,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack färska och något äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4564,10 +4569,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120040170</v>
+        <v>120040189</v>
       </c>
       <c r="B39" t="n">
-        <v>57310</v>
+        <v>97930</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4576,25 +4581,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4604,10 +4609,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>477755</v>
+        <v>477498</v>
       </c>
       <c r="R39" t="n">
-        <v>7069016</v>
+        <v>7069206</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4640,11 +4645,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4671,10 +4671,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120040187</v>
+        <v>120040140</v>
       </c>
       <c r="B40" t="n">
-        <v>97907</v>
+        <v>57320</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4683,25 +4683,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4711,10 +4711,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>477525</v>
+        <v>477472</v>
       </c>
       <c r="R40" t="n">
-        <v>7069106</v>
+        <v>7069006</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4747,6 +4747,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4773,10 +4778,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120040188</v>
+        <v>120040144</v>
       </c>
       <c r="B41" t="n">
-        <v>97907</v>
+        <v>57320</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4785,25 +4790,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4813,10 +4818,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>477454</v>
+        <v>477644</v>
       </c>
       <c r="R41" t="n">
-        <v>7069190</v>
+        <v>7069114</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4849,6 +4854,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4875,10 +4885,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120040138</v>
+        <v>120040161</v>
       </c>
       <c r="B42" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4915,10 +4925,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>477726</v>
+        <v>477426</v>
       </c>
       <c r="R42" t="n">
-        <v>7069062</v>
+        <v>7068947</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4982,10 +4992,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120040167</v>
+        <v>120040182</v>
       </c>
       <c r="B43" t="n">
-        <v>57310</v>
+        <v>57431</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4994,20 +5004,20 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -5015,17 +5025,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>477641</v>
+        <v>477760</v>
       </c>
       <c r="R43" t="n">
-        <v>7068958</v>
+        <v>7069037</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5058,11 +5080,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack ganska färska</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5089,10 +5106,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120040175</v>
+        <v>120040163</v>
       </c>
       <c r="B44" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5122,37 +5139,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>477822</v>
+        <v>477544</v>
       </c>
       <c r="R44" t="n">
-        <v>7069037</v>
+        <v>7068952</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5185,6 +5182,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5211,10 +5213,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120040207</v>
+        <v>120040148</v>
       </c>
       <c r="B45" t="n">
-        <v>86878</v>
+        <v>57320</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5227,21 +5229,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5251,10 +5253,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>477473</v>
+        <v>477438</v>
       </c>
       <c r="R45" t="n">
-        <v>7069007</v>
+        <v>7069178</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5287,6 +5289,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5313,10 +5320,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120040172</v>
+        <v>120040168</v>
       </c>
       <c r="B46" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5353,10 +5360,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>477777</v>
+        <v>477664</v>
       </c>
       <c r="R46" t="n">
-        <v>7069022</v>
+        <v>7068971</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5393,7 +5400,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5420,10 +5427,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120040182</v>
+        <v>120040206</v>
       </c>
       <c r="B47" t="n">
-        <v>57421</v>
+        <v>78542</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5432,50 +5439,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>477760</v>
+        <v>477405</v>
       </c>
       <c r="R47" t="n">
-        <v>7069037</v>
+        <v>7069105</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5534,10 +5529,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120040183</v>
+        <v>120040200</v>
       </c>
       <c r="B48" t="n">
-        <v>57421</v>
+        <v>90598</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5546,50 +5541,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103031</v>
+        <v>5432</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>477821</v>
+        <v>477439</v>
       </c>
       <c r="R48" t="n">
-        <v>7069026</v>
+        <v>7069086</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5648,10 +5631,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120040174</v>
+        <v>120040205</v>
       </c>
       <c r="B49" t="n">
-        <v>57310</v>
+        <v>78542</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5664,21 +5647,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5688,10 +5671,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>477825</v>
+        <v>477382</v>
       </c>
       <c r="R49" t="n">
-        <v>7069031</v>
+        <v>7069247</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5724,11 +5707,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5755,10 +5733,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120040144</v>
+        <v>120040188</v>
       </c>
       <c r="B50" t="n">
-        <v>57310</v>
+        <v>97930</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5767,25 +5745,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5795,10 +5773,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>477644</v>
+        <v>477454</v>
       </c>
       <c r="R50" t="n">
-        <v>7069114</v>
+        <v>7069190</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5831,11 +5809,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5862,10 +5835,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120040142</v>
+        <v>120040138</v>
       </c>
       <c r="B51" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5902,10 +5875,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>477614</v>
+        <v>477726</v>
       </c>
       <c r="R51" t="n">
-        <v>7069089</v>
+        <v>7069062</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5969,10 +5942,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120040149</v>
+        <v>120040139</v>
       </c>
       <c r="B52" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6009,10 +5982,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>477423</v>
+        <v>477517</v>
       </c>
       <c r="R52" t="n">
-        <v>7069180</v>
+        <v>7068992</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6076,10 +6049,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120040159</v>
+        <v>120040146</v>
       </c>
       <c r="B53" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6116,10 +6089,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>477444</v>
+        <v>477599</v>
       </c>
       <c r="R53" t="n">
-        <v>7068963</v>
+        <v>7069105</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6156,7 +6129,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack ganska färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6183,10 +6156,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120040190</v>
+        <v>120040147</v>
       </c>
       <c r="B54" t="n">
-        <v>97907</v>
+        <v>57320</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6195,25 +6168,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6223,10 +6196,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>477530</v>
+        <v>477581</v>
       </c>
       <c r="R54" t="n">
-        <v>7069276</v>
+        <v>7069095</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6259,6 +6232,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6285,10 +6263,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120040141</v>
+        <v>120040183</v>
       </c>
       <c r="B55" t="n">
-        <v>57310</v>
+        <v>57431</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6297,20 +6275,20 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -6318,17 +6296,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>477562</v>
+        <v>477821</v>
       </c>
       <c r="R55" t="n">
-        <v>7069078</v>
+        <v>7069026</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6361,11 +6351,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6392,10 +6377,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120040205</v>
+        <v>120040135</v>
       </c>
       <c r="B56" t="n">
-        <v>78526</v>
+        <v>90580</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6408,21 +6393,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6432,10 +6417,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>477382</v>
+        <v>477507</v>
       </c>
       <c r="R56" t="n">
-        <v>7069247</v>
+        <v>7069055</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6494,10 +6479,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120040152</v>
+        <v>120040179</v>
       </c>
       <c r="B57" t="n">
-        <v>57310</v>
+        <v>79624</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6510,21 +6495,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6534,10 +6519,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>477472</v>
+        <v>477437</v>
       </c>
       <c r="R57" t="n">
-        <v>7069168</v>
+        <v>7068991</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6570,11 +6555,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6601,10 +6581,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120040150</v>
+        <v>120040134</v>
       </c>
       <c r="B58" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6617,21 +6597,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6641,10 +6621,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>477457</v>
+        <v>477522</v>
       </c>
       <c r="R58" t="n">
-        <v>7069186</v>
+        <v>7068987</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6677,11 +6657,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6708,10 +6683,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120040180</v>
+        <v>120040142</v>
       </c>
       <c r="B59" t="n">
-        <v>79607</v>
+        <v>57320</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6724,21 +6699,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6748,10 +6723,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>477415</v>
+        <v>477614</v>
       </c>
       <c r="R59" t="n">
-        <v>7069070</v>
+        <v>7069089</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6784,6 +6759,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6810,10 +6790,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120040147</v>
+        <v>120040162</v>
       </c>
       <c r="B60" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6850,10 +6830,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>477581</v>
+        <v>477471</v>
       </c>
       <c r="R60" t="n">
-        <v>7069095</v>
+        <v>7068928</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6917,10 +6897,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120040179</v>
+        <v>120040175</v>
       </c>
       <c r="B61" t="n">
-        <v>79608</v>
+        <v>57320</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6933,34 +6913,54 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>477437</v>
+        <v>477822</v>
       </c>
       <c r="R61" t="n">
-        <v>7068991</v>
+        <v>7069037</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7019,10 +7019,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120040136</v>
+        <v>120040192</v>
       </c>
       <c r="B62" t="n">
-        <v>90562</v>
+        <v>97930</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7031,25 +7031,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7059,10 +7059,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>477434</v>
+        <v>477445</v>
       </c>
       <c r="R62" t="n">
-        <v>7069116</v>
+        <v>7068977</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7121,10 +7121,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120040203</v>
+        <v>120040199</v>
       </c>
       <c r="B63" t="n">
-        <v>78526</v>
+        <v>90576</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7137,21 +7137,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7161,10 +7161,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>477472</v>
+        <v>477671</v>
       </c>
       <c r="R63" t="n">
-        <v>7069087</v>
+        <v>7068973</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7223,10 +7223,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120040154</v>
+        <v>120040169</v>
       </c>
       <c r="B64" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7263,10 +7263,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>477476</v>
+        <v>477688</v>
       </c>
       <c r="R64" t="n">
-        <v>7069264</v>
+        <v>7069010</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>

--- a/artfynd/A 36309-2024 artfynd.xlsx
+++ b/artfynd/A 36309-2024 artfynd.xlsx
@@ -5835,10 +5835,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120040138</v>
+        <v>120040135</v>
       </c>
       <c r="B51" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5851,21 +5851,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5875,10 +5875,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>477726</v>
+        <v>477507</v>
       </c>
       <c r="R51" t="n">
-        <v>7069062</v>
+        <v>7069055</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5911,11 +5911,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5942,7 +5937,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120040139</v>
+        <v>120040138</v>
       </c>
       <c r="B52" t="n">
         <v>57320</v>
@@ -5982,10 +5977,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>477517</v>
+        <v>477726</v>
       </c>
       <c r="R52" t="n">
-        <v>7068992</v>
+        <v>7069062</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6049,7 +6044,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120040146</v>
+        <v>120040139</v>
       </c>
       <c r="B53" t="n">
         <v>57320</v>
@@ -6089,10 +6084,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>477599</v>
+        <v>477517</v>
       </c>
       <c r="R53" t="n">
-        <v>7069105</v>
+        <v>7068992</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6156,7 +6151,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120040147</v>
+        <v>120040146</v>
       </c>
       <c r="B54" t="n">
         <v>57320</v>
@@ -6196,10 +6191,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>477581</v>
+        <v>477599</v>
       </c>
       <c r="R54" t="n">
-        <v>7069095</v>
+        <v>7069105</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6263,10 +6258,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120040183</v>
+        <v>120040147</v>
       </c>
       <c r="B55" t="n">
-        <v>57431</v>
+        <v>57320</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6275,20 +6270,20 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -6296,29 +6291,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>477821</v>
+        <v>477581</v>
       </c>
       <c r="R55" t="n">
-        <v>7069026</v>
+        <v>7069095</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6351,6 +6334,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6377,10 +6365,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120040135</v>
+        <v>120040183</v>
       </c>
       <c r="B56" t="n">
-        <v>90580</v>
+        <v>57431</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6389,38 +6377,50 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>103031</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>477507</v>
+        <v>477821</v>
       </c>
       <c r="R56" t="n">
-        <v>7069055</v>
+        <v>7069026</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6479,10 +6479,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120040179</v>
+        <v>120040134</v>
       </c>
       <c r="B57" t="n">
-        <v>79624</v>
+        <v>90580</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6495,21 +6495,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>477437</v>
+        <v>477522</v>
       </c>
       <c r="R57" t="n">
-        <v>7068991</v>
+        <v>7068987</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6581,10 +6581,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120040134</v>
+        <v>120040142</v>
       </c>
       <c r="B58" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6597,21 +6597,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6621,10 +6621,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>477522</v>
+        <v>477614</v>
       </c>
       <c r="R58" t="n">
-        <v>7068987</v>
+        <v>7069089</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6657,6 +6657,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6683,10 +6688,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120040142</v>
+        <v>120040179</v>
       </c>
       <c r="B59" t="n">
-        <v>57320</v>
+        <v>79624</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6699,21 +6704,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6723,10 +6728,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>477614</v>
+        <v>477437</v>
       </c>
       <c r="R59" t="n">
-        <v>7069089</v>
+        <v>7068991</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6759,11 +6764,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD59" t="b">

--- a/artfynd/A 36309-2024 artfynd.xlsx
+++ b/artfynd/A 36309-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120040185</v>
+        <v>120040207</v>
       </c>
       <c r="B2" t="n">
-        <v>97930</v>
+        <v>86895</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477507</v>
+        <v>477473</v>
       </c>
       <c r="R2" t="n">
-        <v>7069056</v>
+        <v>7069007</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120040202</v>
+        <v>120040182</v>
       </c>
       <c r="B3" t="n">
-        <v>90598</v>
+        <v>57431</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +789,50 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>103031</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477674</v>
+        <v>477760</v>
       </c>
       <c r="R3" t="n">
-        <v>7069000</v>
+        <v>7069037</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120040201</v>
+        <v>120040157</v>
       </c>
       <c r="B4" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +907,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477484</v>
+        <v>477397</v>
       </c>
       <c r="R4" t="n">
-        <v>7068927</v>
+        <v>7069068</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,6 +967,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120040172</v>
+        <v>120040185</v>
       </c>
       <c r="B5" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +1010,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477777</v>
+        <v>477507</v>
       </c>
       <c r="R5" t="n">
-        <v>7069022</v>
+        <v>7069056</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1057,11 +1074,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,10 +1100,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120040160</v>
+        <v>120040200</v>
       </c>
       <c r="B6" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,21 +1116,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1140,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477440</v>
+        <v>477439</v>
       </c>
       <c r="R6" t="n">
-        <v>7068958</v>
+        <v>7069086</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1164,11 +1176,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,7 +1202,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120040154</v>
+        <v>120040177</v>
       </c>
       <c r="B7" t="n">
         <v>57320</v>
@@ -1235,10 +1242,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477476</v>
+        <v>477856</v>
       </c>
       <c r="R7" t="n">
-        <v>7069264</v>
+        <v>7069020</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1275,7 +1282,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1302,7 +1309,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120040171</v>
+        <v>120040146</v>
       </c>
       <c r="B8" t="n">
         <v>57320</v>
@@ -1342,10 +1349,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477759</v>
+        <v>477599</v>
       </c>
       <c r="R8" t="n">
-        <v>7069019</v>
+        <v>7069105</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1409,10 +1416,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120040204</v>
+        <v>120040173</v>
       </c>
       <c r="B9" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1425,21 +1432,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1449,10 +1456,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>477534</v>
+        <v>477786</v>
       </c>
       <c r="R9" t="n">
-        <v>7069288</v>
+        <v>7069029</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1485,6 +1492,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1511,7 +1523,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120040158</v>
+        <v>120040141</v>
       </c>
       <c r="B10" t="n">
         <v>57320</v>
@@ -1551,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>477446</v>
+        <v>477562</v>
       </c>
       <c r="R10" t="n">
-        <v>7069039</v>
+        <v>7069078</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1591,7 +1603,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1618,10 +1630,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120040184</v>
+        <v>120040203</v>
       </c>
       <c r="B11" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1630,25 +1642,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1658,10 +1670,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>477481</v>
+        <v>477472</v>
       </c>
       <c r="R11" t="n">
-        <v>7069004</v>
+        <v>7069087</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1720,10 +1732,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120040152</v>
+        <v>120040205</v>
       </c>
       <c r="B12" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1736,21 +1748,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1760,10 +1772,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>477472</v>
+        <v>477382</v>
       </c>
       <c r="R12" t="n">
-        <v>7069168</v>
+        <v>7069247</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1796,11 +1808,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1827,7 +1834,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120040173</v>
+        <v>120040163</v>
       </c>
       <c r="B13" t="n">
         <v>57320</v>
@@ -1867,10 +1874,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>477786</v>
+        <v>477544</v>
       </c>
       <c r="R13" t="n">
-        <v>7069029</v>
+        <v>7068952</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1907,7 +1914,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1934,10 +1941,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120040177</v>
+        <v>120040184</v>
       </c>
       <c r="B14" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1946,25 +1953,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1974,10 +1981,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>477856</v>
+        <v>477481</v>
       </c>
       <c r="R14" t="n">
-        <v>7069020</v>
+        <v>7069004</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2010,11 +2017,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2041,10 +2043,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120040164</v>
+        <v>120040183</v>
       </c>
       <c r="B15" t="n">
-        <v>57320</v>
+        <v>57431</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2053,20 +2055,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2074,17 +2076,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>477597</v>
+        <v>477821</v>
       </c>
       <c r="R15" t="n">
-        <v>7068964</v>
+        <v>7069026</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2117,11 +2131,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2148,7 +2157,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120040176</v>
+        <v>120040155</v>
       </c>
       <c r="B16" t="n">
         <v>57320</v>
@@ -2188,10 +2197,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>477852</v>
+        <v>477377</v>
       </c>
       <c r="R16" t="n">
-        <v>7069022</v>
+        <v>7069208</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2228,7 +2237,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack ganska färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2255,7 +2264,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120040167</v>
+        <v>120040164</v>
       </c>
       <c r="B17" t="n">
         <v>57320</v>
@@ -2295,10 +2304,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>477641</v>
+        <v>477597</v>
       </c>
       <c r="R17" t="n">
-        <v>7068958</v>
+        <v>7068964</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2335,7 +2344,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack ganska färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2362,10 +2371,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120040150</v>
+        <v>120040191</v>
       </c>
       <c r="B18" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2374,25 +2383,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2402,10 +2411,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>477457</v>
+        <v>477440</v>
       </c>
       <c r="R18" t="n">
-        <v>7069186</v>
+        <v>7069251</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2438,11 +2447,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2469,7 +2473,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120040149</v>
+        <v>120040138</v>
       </c>
       <c r="B19" t="n">
         <v>57320</v>
@@ -2509,10 +2513,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>477423</v>
+        <v>477726</v>
       </c>
       <c r="R19" t="n">
-        <v>7069180</v>
+        <v>7069062</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2576,10 +2580,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120040190</v>
+        <v>120040148</v>
       </c>
       <c r="B20" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2588,25 +2592,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2616,10 +2620,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>477530</v>
+        <v>477438</v>
       </c>
       <c r="R20" t="n">
-        <v>7069276</v>
+        <v>7069178</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2652,6 +2656,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2678,10 +2687,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120040191</v>
+        <v>120040167</v>
       </c>
       <c r="B21" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2690,25 +2699,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2718,10 +2727,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>477440</v>
+        <v>477641</v>
       </c>
       <c r="R21" t="n">
-        <v>7069251</v>
+        <v>7068958</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2754,6 +2763,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack ganska färska</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2780,10 +2794,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120040170</v>
+        <v>120040202</v>
       </c>
       <c r="B22" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2796,21 +2810,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2820,10 +2834,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>477755</v>
+        <v>477674</v>
       </c>
       <c r="R22" t="n">
-        <v>7069016</v>
+        <v>7069000</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2856,11 +2870,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2887,7 +2896,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120040203</v>
+        <v>120040206</v>
       </c>
       <c r="B23" t="n">
         <v>78542</v>
@@ -2927,10 +2936,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>477472</v>
+        <v>477405</v>
       </c>
       <c r="R23" t="n">
-        <v>7069087</v>
+        <v>7069105</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2989,10 +2998,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120040181</v>
+        <v>120040204</v>
       </c>
       <c r="B24" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3005,21 +3014,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3029,10 +3038,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>477437</v>
+        <v>477534</v>
       </c>
       <c r="R24" t="n">
-        <v>7068991</v>
+        <v>7069288</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3091,10 +3100,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120040180</v>
+        <v>120040142</v>
       </c>
       <c r="B25" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3107,21 +3116,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3131,10 +3140,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>477415</v>
+        <v>477614</v>
       </c>
       <c r="R25" t="n">
-        <v>7069070</v>
+        <v>7069089</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3167,6 +3176,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3193,10 +3207,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120040136</v>
+        <v>120040190</v>
       </c>
       <c r="B26" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3205,25 +3219,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3233,10 +3247,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>477434</v>
+        <v>477530</v>
       </c>
       <c r="R26" t="n">
-        <v>7069116</v>
+        <v>7069276</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3295,7 +3309,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120040155</v>
+        <v>120040150</v>
       </c>
       <c r="B27" t="n">
         <v>57320</v>
@@ -3335,10 +3349,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>477377</v>
+        <v>477457</v>
       </c>
       <c r="R27" t="n">
-        <v>7069208</v>
+        <v>7069186</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3402,7 +3416,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120040174</v>
+        <v>120040172</v>
       </c>
       <c r="B28" t="n">
         <v>57320</v>
@@ -3442,10 +3456,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>477825</v>
+        <v>477777</v>
       </c>
       <c r="R28" t="n">
-        <v>7069031</v>
+        <v>7069022</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3509,10 +3523,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120040207</v>
+        <v>120040162</v>
       </c>
       <c r="B29" t="n">
-        <v>86895</v>
+        <v>57320</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3525,21 +3539,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3549,10 +3563,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>477473</v>
+        <v>477471</v>
       </c>
       <c r="R29" t="n">
-        <v>7069007</v>
+        <v>7068928</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3585,6 +3599,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3611,7 +3630,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120040165</v>
+        <v>120040166</v>
       </c>
       <c r="B30" t="n">
         <v>57320</v>
@@ -3651,10 +3670,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>477596</v>
+        <v>477622</v>
       </c>
       <c r="R30" t="n">
-        <v>7068950</v>
+        <v>7068965</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3718,7 +3737,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120040159</v>
+        <v>120040171</v>
       </c>
       <c r="B31" t="n">
         <v>57320</v>
@@ -3758,10 +3777,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>477444</v>
+        <v>477759</v>
       </c>
       <c r="R31" t="n">
-        <v>7068963</v>
+        <v>7069019</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3798,7 +3817,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack ganska färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3825,7 +3844,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120040157</v>
+        <v>120040149</v>
       </c>
       <c r="B32" t="n">
         <v>57320</v>
@@ -3865,10 +3884,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>477397</v>
+        <v>477423</v>
       </c>
       <c r="R32" t="n">
-        <v>7069068</v>
+        <v>7069180</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3905,7 +3924,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3932,10 +3951,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120040153</v>
+        <v>120040179</v>
       </c>
       <c r="B33" t="n">
-        <v>57320</v>
+        <v>79624</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3948,21 +3967,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3972,10 +3991,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>477547</v>
+        <v>477437</v>
       </c>
       <c r="R33" t="n">
-        <v>7069271</v>
+        <v>7068991</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4008,11 +4027,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4039,7 +4053,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120040141</v>
+        <v>120040170</v>
       </c>
       <c r="B34" t="n">
         <v>57320</v>
@@ -4079,10 +4093,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>477562</v>
+        <v>477755</v>
       </c>
       <c r="R34" t="n">
-        <v>7069078</v>
+        <v>7069016</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4146,7 +4160,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120040145</v>
+        <v>120040144</v>
       </c>
       <c r="B35" t="n">
         <v>57320</v>
@@ -4186,10 +4200,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>477626</v>
+        <v>477644</v>
       </c>
       <c r="R35" t="n">
-        <v>7069105</v>
+        <v>7069114</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4253,10 +4267,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120040187</v>
+        <v>120040161</v>
       </c>
       <c r="B36" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4265,25 +4279,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4293,10 +4307,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>477525</v>
+        <v>477426</v>
       </c>
       <c r="R36" t="n">
-        <v>7069106</v>
+        <v>7068947</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4329,6 +4343,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4355,10 +4374,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120040166</v>
+        <v>120040181</v>
       </c>
       <c r="B37" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4371,21 +4390,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4395,10 +4414,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>477622</v>
+        <v>477437</v>
       </c>
       <c r="R37" t="n">
-        <v>7068965</v>
+        <v>7068991</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4431,11 +4450,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4462,7 +4476,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120040151</v>
+        <v>120040152</v>
       </c>
       <c r="B38" t="n">
         <v>57320</v>
@@ -4502,10 +4516,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>477460</v>
+        <v>477472</v>
       </c>
       <c r="R38" t="n">
-        <v>7069166</v>
+        <v>7069168</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4542,7 +4556,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack färska och något äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4569,10 +4583,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120040189</v>
+        <v>120040174</v>
       </c>
       <c r="B39" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4581,25 +4595,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4609,10 +4623,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>477498</v>
+        <v>477825</v>
       </c>
       <c r="R39" t="n">
-        <v>7069206</v>
+        <v>7069031</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4645,6 +4659,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4671,10 +4690,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120040140</v>
+        <v>120040134</v>
       </c>
       <c r="B40" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4687,21 +4706,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4711,10 +4730,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>477472</v>
+        <v>477522</v>
       </c>
       <c r="R40" t="n">
-        <v>7069006</v>
+        <v>7068987</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4747,11 +4766,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4778,10 +4792,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120040144</v>
+        <v>120040201</v>
       </c>
       <c r="B41" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4794,21 +4808,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4818,10 +4832,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>477644</v>
+        <v>477484</v>
       </c>
       <c r="R41" t="n">
-        <v>7069114</v>
+        <v>7068927</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4854,11 +4868,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4885,7 +4894,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120040161</v>
+        <v>120040158</v>
       </c>
       <c r="B42" t="n">
         <v>57320</v>
@@ -4925,10 +4934,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>477426</v>
+        <v>477446</v>
       </c>
       <c r="R42" t="n">
-        <v>7068947</v>
+        <v>7069039</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4965,7 +4974,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4992,10 +5001,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120040182</v>
+        <v>120040188</v>
       </c>
       <c r="B43" t="n">
-        <v>57431</v>
+        <v>97930</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5004,50 +5013,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103031</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>477760</v>
+        <v>477454</v>
       </c>
       <c r="R43" t="n">
-        <v>7069037</v>
+        <v>7069190</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5106,7 +5103,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120040163</v>
+        <v>120040169</v>
       </c>
       <c r="B44" t="n">
         <v>57320</v>
@@ -5146,10 +5143,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>477544</v>
+        <v>477688</v>
       </c>
       <c r="R44" t="n">
-        <v>7068952</v>
+        <v>7069010</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5186,7 +5183,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5213,10 +5210,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120040148</v>
+        <v>120040189</v>
       </c>
       <c r="B45" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5225,25 +5222,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5253,10 +5250,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>477438</v>
+        <v>477498</v>
       </c>
       <c r="R45" t="n">
-        <v>7069178</v>
+        <v>7069206</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5289,11 +5286,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5320,7 +5312,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120040168</v>
+        <v>120040140</v>
       </c>
       <c r="B46" t="n">
         <v>57320</v>
@@ -5360,10 +5352,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>477664</v>
+        <v>477472</v>
       </c>
       <c r="R46" t="n">
-        <v>7068971</v>
+        <v>7069006</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5400,7 +5392,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5427,10 +5419,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120040206</v>
+        <v>120040168</v>
       </c>
       <c r="B47" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5443,21 +5435,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5467,10 +5459,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>477405</v>
+        <v>477664</v>
       </c>
       <c r="R47" t="n">
-        <v>7069105</v>
+        <v>7068971</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5503,6 +5495,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5529,10 +5526,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120040200</v>
+        <v>120040187</v>
       </c>
       <c r="B48" t="n">
-        <v>90598</v>
+        <v>97930</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5541,25 +5538,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5569,10 +5566,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>477439</v>
+        <v>477525</v>
       </c>
       <c r="R48" t="n">
-        <v>7069086</v>
+        <v>7069106</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5631,10 +5628,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120040205</v>
+        <v>120040192</v>
       </c>
       <c r="B49" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5643,25 +5640,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5671,10 +5668,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>477382</v>
+        <v>477445</v>
       </c>
       <c r="R49" t="n">
-        <v>7069247</v>
+        <v>7068977</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5733,10 +5730,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120040188</v>
+        <v>120040199</v>
       </c>
       <c r="B50" t="n">
-        <v>97930</v>
+        <v>90576</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5745,25 +5742,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>1108</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5773,10 +5770,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>477454</v>
+        <v>477671</v>
       </c>
       <c r="R50" t="n">
-        <v>7069190</v>
+        <v>7068973</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5835,10 +5832,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120040135</v>
+        <v>120040180</v>
       </c>
       <c r="B51" t="n">
-        <v>90580</v>
+        <v>79623</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5851,21 +5848,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5875,10 +5872,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>477507</v>
+        <v>477415</v>
       </c>
       <c r="R51" t="n">
-        <v>7069055</v>
+        <v>7069070</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5937,7 +5934,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120040138</v>
+        <v>120040165</v>
       </c>
       <c r="B52" t="n">
         <v>57320</v>
@@ -5977,10 +5974,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>477726</v>
+        <v>477596</v>
       </c>
       <c r="R52" t="n">
-        <v>7069062</v>
+        <v>7068950</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6017,7 +6014,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6044,7 +6041,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120040139</v>
+        <v>120040159</v>
       </c>
       <c r="B53" t="n">
         <v>57320</v>
@@ -6084,10 +6081,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>477517</v>
+        <v>477444</v>
       </c>
       <c r="R53" t="n">
-        <v>7068992</v>
+        <v>7068963</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6124,7 +6121,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack ganska färska till äldre</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6151,7 +6148,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120040146</v>
+        <v>120040139</v>
       </c>
       <c r="B54" t="n">
         <v>57320</v>
@@ -6191,10 +6188,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>477599</v>
+        <v>477517</v>
       </c>
       <c r="R54" t="n">
-        <v>7069105</v>
+        <v>7068992</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6258,7 +6255,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120040147</v>
+        <v>120040176</v>
       </c>
       <c r="B55" t="n">
         <v>57320</v>
@@ -6298,10 +6295,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>477581</v>
+        <v>477852</v>
       </c>
       <c r="R55" t="n">
-        <v>7069095</v>
+        <v>7069022</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6338,7 +6335,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack ganska färska till äldre</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6365,10 +6362,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120040183</v>
+        <v>120040135</v>
       </c>
       <c r="B56" t="n">
-        <v>57431</v>
+        <v>90580</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6377,50 +6374,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103031</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>477821</v>
+        <v>477507</v>
       </c>
       <c r="R56" t="n">
-        <v>7069026</v>
+        <v>7069055</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6479,10 +6464,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120040134</v>
+        <v>120040175</v>
       </c>
       <c r="B57" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6495,34 +6480,54 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>477522</v>
+        <v>477822</v>
       </c>
       <c r="R57" t="n">
-        <v>7068987</v>
+        <v>7069037</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6581,7 +6586,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120040142</v>
+        <v>120040153</v>
       </c>
       <c r="B58" t="n">
         <v>57320</v>
@@ -6621,10 +6626,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>477614</v>
+        <v>477547</v>
       </c>
       <c r="R58" t="n">
-        <v>7069089</v>
+        <v>7069271</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6688,10 +6693,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120040179</v>
+        <v>120040151</v>
       </c>
       <c r="B59" t="n">
-        <v>79624</v>
+        <v>57320</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6704,21 +6709,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6728,10 +6733,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>477437</v>
+        <v>477460</v>
       </c>
       <c r="R59" t="n">
-        <v>7068991</v>
+        <v>7069166</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6764,6 +6769,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack färska och något äldre</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6790,10 +6800,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120040162</v>
+        <v>120040136</v>
       </c>
       <c r="B60" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6806,21 +6816,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6830,10 +6840,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>477471</v>
+        <v>477434</v>
       </c>
       <c r="R60" t="n">
-        <v>7068928</v>
+        <v>7069116</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6866,11 +6876,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6897,7 +6902,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120040175</v>
+        <v>120040147</v>
       </c>
       <c r="B61" t="n">
         <v>57320</v>
@@ -6930,37 +6935,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>477822</v>
+        <v>477581</v>
       </c>
       <c r="R61" t="n">
-        <v>7069037</v>
+        <v>7069095</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6993,6 +6978,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7019,10 +7009,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120040192</v>
+        <v>120040160</v>
       </c>
       <c r="B62" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7031,25 +7021,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7059,10 +7049,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>477445</v>
+        <v>477440</v>
       </c>
       <c r="R62" t="n">
-        <v>7068977</v>
+        <v>7068958</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7095,6 +7085,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7121,10 +7116,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120040199</v>
+        <v>120040154</v>
       </c>
       <c r="B63" t="n">
-        <v>90576</v>
+        <v>57320</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7137,21 +7132,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7161,10 +7156,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>477671</v>
+        <v>477476</v>
       </c>
       <c r="R63" t="n">
-        <v>7068973</v>
+        <v>7069264</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7197,6 +7192,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7223,7 +7223,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120040169</v>
+        <v>120040145</v>
       </c>
       <c r="B64" t="n">
         <v>57320</v>
@@ -7263,10 +7263,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>477688</v>
+        <v>477626</v>
       </c>
       <c r="R64" t="n">
-        <v>7069010</v>
+        <v>7069105</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>

--- a/artfynd/A 36309-2024 artfynd.xlsx
+++ b/artfynd/A 36309-2024 artfynd.xlsx
@@ -2157,7 +2157,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120040155</v>
+        <v>120040164</v>
       </c>
       <c r="B16" t="n">
         <v>57320</v>
@@ -2197,10 +2197,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>477377</v>
+        <v>477597</v>
       </c>
       <c r="R16" t="n">
-        <v>7069208</v>
+        <v>7068964</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2237,7 +2237,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2264,7 +2264,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120040164</v>
+        <v>120040155</v>
       </c>
       <c r="B17" t="n">
         <v>57320</v>
@@ -2304,10 +2304,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>477597</v>
+        <v>477377</v>
       </c>
       <c r="R17" t="n">
-        <v>7068964</v>
+        <v>7069208</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -6693,10 +6693,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120040151</v>
+        <v>120040136</v>
       </c>
       <c r="B59" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6709,21 +6709,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6733,10 +6733,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>477460</v>
+        <v>477434</v>
       </c>
       <c r="R59" t="n">
-        <v>7069166</v>
+        <v>7069116</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6769,11 +6769,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack färska och något äldre</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6800,10 +6795,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120040136</v>
+        <v>120040151</v>
       </c>
       <c r="B60" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6816,21 +6811,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6840,10 +6835,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>477434</v>
+        <v>477460</v>
       </c>
       <c r="R60" t="n">
-        <v>7069116</v>
+        <v>7069166</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6876,6 +6871,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack färska och något äldre</t>
         </is>
       </c>
       <c r="AD60" t="b">

--- a/artfynd/A 36309-2024 artfynd.xlsx
+++ b/artfynd/A 36309-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120040207</v>
+        <v>120040162</v>
       </c>
       <c r="B2" t="n">
-        <v>86895</v>
+        <v>57320</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477473</v>
+        <v>477471</v>
       </c>
       <c r="R2" t="n">
-        <v>7069007</v>
+        <v>7068928</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120040182</v>
+        <v>120040180</v>
       </c>
       <c r="B3" t="n">
-        <v>57431</v>
+        <v>79623</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,50 +794,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103031</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477760</v>
+        <v>477415</v>
       </c>
       <c r="R3" t="n">
-        <v>7069037</v>
+        <v>7069070</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -891,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120040157</v>
+        <v>120040183</v>
       </c>
       <c r="B4" t="n">
-        <v>57320</v>
+        <v>57431</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,20 +896,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -924,17 +917,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477397</v>
+        <v>477821</v>
       </c>
       <c r="R4" t="n">
-        <v>7069068</v>
+        <v>7069026</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -967,11 +972,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120040185</v>
+        <v>120040167</v>
       </c>
       <c r="B5" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1010,25 +1010,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1038,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477507</v>
+        <v>477641</v>
       </c>
       <c r="R5" t="n">
-        <v>7069056</v>
+        <v>7068958</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1074,6 +1074,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack ganska färska</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1100,10 +1105,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120040200</v>
+        <v>120040188</v>
       </c>
       <c r="B6" t="n">
-        <v>90598</v>
+        <v>97930</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1112,25 +1117,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1140,10 +1145,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477439</v>
+        <v>477454</v>
       </c>
       <c r="R6" t="n">
-        <v>7069086</v>
+        <v>7069190</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1202,7 +1207,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120040177</v>
+        <v>120040164</v>
       </c>
       <c r="B7" t="n">
         <v>57320</v>
@@ -1242,10 +1247,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477856</v>
+        <v>477597</v>
       </c>
       <c r="R7" t="n">
-        <v>7069020</v>
+        <v>7068964</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1282,7 +1287,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1309,7 +1314,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120040146</v>
+        <v>120040159</v>
       </c>
       <c r="B8" t="n">
         <v>57320</v>
@@ -1349,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477599</v>
+        <v>477444</v>
       </c>
       <c r="R8" t="n">
-        <v>7069105</v>
+        <v>7068963</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,7 +1394,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack ganska färska till äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1416,7 +1421,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120040173</v>
+        <v>120040158</v>
       </c>
       <c r="B9" t="n">
         <v>57320</v>
@@ -1456,10 +1461,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>477786</v>
+        <v>477446</v>
       </c>
       <c r="R9" t="n">
-        <v>7069029</v>
+        <v>7069039</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1496,7 +1501,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1523,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120040141</v>
+        <v>120040136</v>
       </c>
       <c r="B10" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1539,21 +1544,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,10 +1568,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>477562</v>
+        <v>477434</v>
       </c>
       <c r="R10" t="n">
-        <v>7069078</v>
+        <v>7069116</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1599,11 +1604,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1630,10 +1630,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120040203</v>
+        <v>120040139</v>
       </c>
       <c r="B11" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1646,21 +1646,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1670,10 +1670,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>477472</v>
+        <v>477517</v>
       </c>
       <c r="R11" t="n">
-        <v>7069087</v>
+        <v>7068992</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1706,6 +1706,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1732,10 +1737,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120040205</v>
+        <v>120040147</v>
       </c>
       <c r="B12" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1748,21 +1753,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1772,10 +1777,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>477382</v>
+        <v>477581</v>
       </c>
       <c r="R12" t="n">
-        <v>7069247</v>
+        <v>7069095</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1808,6 +1813,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1834,10 +1844,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120040163</v>
+        <v>120040182</v>
       </c>
       <c r="B13" t="n">
-        <v>57320</v>
+        <v>57431</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1846,20 +1856,20 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1867,17 +1877,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>477544</v>
+        <v>477760</v>
       </c>
       <c r="R13" t="n">
-        <v>7068952</v>
+        <v>7069037</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1910,11 +1932,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1941,10 +1958,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120040184</v>
+        <v>120040134</v>
       </c>
       <c r="B14" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1953,25 +1970,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1981,10 +1998,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>477481</v>
+        <v>477522</v>
       </c>
       <c r="R14" t="n">
-        <v>7069004</v>
+        <v>7068987</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2043,10 +2060,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120040183</v>
+        <v>120040142</v>
       </c>
       <c r="B15" t="n">
-        <v>57431</v>
+        <v>57320</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2055,20 +2072,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2076,29 +2093,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>477821</v>
+        <v>477614</v>
       </c>
       <c r="R15" t="n">
-        <v>7069026</v>
+        <v>7069089</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2131,6 +2136,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2157,7 +2167,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120040164</v>
+        <v>120040175</v>
       </c>
       <c r="B16" t="n">
         <v>57320</v>
@@ -2190,17 +2200,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>477597</v>
+        <v>477822</v>
       </c>
       <c r="R16" t="n">
-        <v>7068964</v>
+        <v>7069037</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2233,11 +2263,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2264,7 +2289,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120040155</v>
+        <v>120040174</v>
       </c>
       <c r="B17" t="n">
         <v>57320</v>
@@ -2304,10 +2329,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>477377</v>
+        <v>477825</v>
       </c>
       <c r="R17" t="n">
-        <v>7069208</v>
+        <v>7069031</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2371,10 +2396,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120040191</v>
+        <v>120040181</v>
       </c>
       <c r="B18" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2383,25 +2408,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2411,10 +2436,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>477440</v>
+        <v>477437</v>
       </c>
       <c r="R18" t="n">
-        <v>7069251</v>
+        <v>7068991</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2473,7 +2498,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120040138</v>
+        <v>120040145</v>
       </c>
       <c r="B19" t="n">
         <v>57320</v>
@@ -2513,10 +2538,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>477726</v>
+        <v>477626</v>
       </c>
       <c r="R19" t="n">
-        <v>7069062</v>
+        <v>7069105</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2580,7 +2605,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120040148</v>
+        <v>120040163</v>
       </c>
       <c r="B20" t="n">
         <v>57320</v>
@@ -2620,10 +2645,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>477438</v>
+        <v>477544</v>
       </c>
       <c r="R20" t="n">
-        <v>7069178</v>
+        <v>7068952</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2660,7 +2685,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2687,10 +2712,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120040167</v>
+        <v>120040185</v>
       </c>
       <c r="B21" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2699,25 +2724,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2727,10 +2752,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>477641</v>
+        <v>477507</v>
       </c>
       <c r="R21" t="n">
-        <v>7068958</v>
+        <v>7069056</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2763,11 +2788,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack ganska färska</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2794,10 +2814,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120040202</v>
+        <v>120040153</v>
       </c>
       <c r="B22" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2810,21 +2830,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2834,10 +2854,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>477674</v>
+        <v>477547</v>
       </c>
       <c r="R22" t="n">
-        <v>7069000</v>
+        <v>7069271</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2870,6 +2890,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2896,10 +2921,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120040206</v>
+        <v>120040201</v>
       </c>
       <c r="B23" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2912,21 +2937,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2936,10 +2961,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>477405</v>
+        <v>477484</v>
       </c>
       <c r="R23" t="n">
-        <v>7069105</v>
+        <v>7068927</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2998,10 +3023,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120040204</v>
+        <v>120040157</v>
       </c>
       <c r="B24" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3014,21 +3039,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3038,10 +3063,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>477534</v>
+        <v>477397</v>
       </c>
       <c r="R24" t="n">
-        <v>7069288</v>
+        <v>7069068</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3074,6 +3099,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3100,7 +3130,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120040142</v>
+        <v>120040156</v>
       </c>
       <c r="B25" t="n">
         <v>57320</v>
@@ -3140,10 +3170,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>477614</v>
+        <v>477377</v>
       </c>
       <c r="R25" t="n">
-        <v>7069089</v>
+        <v>7069208</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3180,7 +3210,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3207,10 +3237,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120040190</v>
+        <v>120040151</v>
       </c>
       <c r="B26" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3219,25 +3249,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3247,10 +3277,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>477530</v>
+        <v>477460</v>
       </c>
       <c r="R26" t="n">
-        <v>7069276</v>
+        <v>7069166</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3283,6 +3313,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack färska och något äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3309,10 +3344,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120040150</v>
+        <v>120040206</v>
       </c>
       <c r="B27" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3325,21 +3360,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3349,10 +3384,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>477457</v>
+        <v>477405</v>
       </c>
       <c r="R27" t="n">
-        <v>7069186</v>
+        <v>7069105</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3385,11 +3420,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3416,7 +3446,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120040172</v>
+        <v>120040169</v>
       </c>
       <c r="B28" t="n">
         <v>57320</v>
@@ -3456,10 +3486,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>477777</v>
+        <v>477688</v>
       </c>
       <c r="R28" t="n">
-        <v>7069022</v>
+        <v>7069010</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3523,10 +3553,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120040162</v>
+        <v>120040202</v>
       </c>
       <c r="B29" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3539,21 +3569,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3563,10 +3593,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>477471</v>
+        <v>477674</v>
       </c>
       <c r="R29" t="n">
-        <v>7068928</v>
+        <v>7069000</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3599,11 +3629,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3630,10 +3655,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120040166</v>
+        <v>120040203</v>
       </c>
       <c r="B30" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3646,21 +3671,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3670,10 +3695,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>477622</v>
+        <v>477472</v>
       </c>
       <c r="R30" t="n">
-        <v>7068965</v>
+        <v>7069087</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3706,11 +3731,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3737,7 +3757,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120040171</v>
+        <v>120040161</v>
       </c>
       <c r="B31" t="n">
         <v>57320</v>
@@ -3777,10 +3797,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>477759</v>
+        <v>477426</v>
       </c>
       <c r="R31" t="n">
-        <v>7069019</v>
+        <v>7068947</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3844,7 +3864,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120040149</v>
+        <v>120040170</v>
       </c>
       <c r="B32" t="n">
         <v>57320</v>
@@ -3884,10 +3904,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>477423</v>
+        <v>477755</v>
       </c>
       <c r="R32" t="n">
-        <v>7069180</v>
+        <v>7069016</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3951,10 +3971,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120040179</v>
+        <v>120040189</v>
       </c>
       <c r="B33" t="n">
-        <v>79624</v>
+        <v>97930</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3963,25 +3983,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3991,10 +4011,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>477437</v>
+        <v>477498</v>
       </c>
       <c r="R33" t="n">
-        <v>7068991</v>
+        <v>7069206</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4053,10 +4073,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120040170</v>
+        <v>120040184</v>
       </c>
       <c r="B34" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4065,25 +4085,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4093,10 +4113,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>477755</v>
+        <v>477481</v>
       </c>
       <c r="R34" t="n">
-        <v>7069016</v>
+        <v>7069004</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4129,11 +4149,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4160,7 +4175,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120040144</v>
+        <v>120040154</v>
       </c>
       <c r="B35" t="n">
         <v>57320</v>
@@ -4200,10 +4215,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>477644</v>
+        <v>477476</v>
       </c>
       <c r="R35" t="n">
-        <v>7069114</v>
+        <v>7069264</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4267,7 +4282,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120040161</v>
+        <v>120040140</v>
       </c>
       <c r="B36" t="n">
         <v>57320</v>
@@ -4307,10 +4322,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>477426</v>
+        <v>477472</v>
       </c>
       <c r="R36" t="n">
-        <v>7068947</v>
+        <v>7069006</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4374,10 +4389,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120040181</v>
+        <v>120040168</v>
       </c>
       <c r="B37" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4390,21 +4405,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4414,10 +4429,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>477437</v>
+        <v>477664</v>
       </c>
       <c r="R37" t="n">
-        <v>7068991</v>
+        <v>7068971</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4450,6 +4465,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4476,7 +4496,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120040152</v>
+        <v>120040160</v>
       </c>
       <c r="B38" t="n">
         <v>57320</v>
@@ -4516,10 +4536,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>477472</v>
+        <v>477440</v>
       </c>
       <c r="R38" t="n">
-        <v>7069168</v>
+        <v>7068958</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4583,7 +4603,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120040174</v>
+        <v>120040166</v>
       </c>
       <c r="B39" t="n">
         <v>57320</v>
@@ -4623,10 +4643,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>477825</v>
+        <v>477622</v>
       </c>
       <c r="R39" t="n">
-        <v>7069031</v>
+        <v>7068965</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4663,7 +4683,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4690,10 +4710,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120040134</v>
+        <v>120040173</v>
       </c>
       <c r="B40" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4706,21 +4726,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4730,10 +4750,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>477522</v>
+        <v>477786</v>
       </c>
       <c r="R40" t="n">
-        <v>7068987</v>
+        <v>7069029</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4766,6 +4786,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4792,10 +4817,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120040201</v>
+        <v>120040141</v>
       </c>
       <c r="B41" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4808,21 +4833,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4832,10 +4857,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>477484</v>
+        <v>477562</v>
       </c>
       <c r="R41" t="n">
-        <v>7068927</v>
+        <v>7069078</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4868,6 +4893,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4894,7 +4924,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120040158</v>
+        <v>120040171</v>
       </c>
       <c r="B42" t="n">
         <v>57320</v>
@@ -4934,10 +4964,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>477446</v>
+        <v>477759</v>
       </c>
       <c r="R42" t="n">
-        <v>7069039</v>
+        <v>7069019</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4974,7 +5004,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5001,10 +5031,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120040188</v>
+        <v>120040179</v>
       </c>
       <c r="B43" t="n">
-        <v>97930</v>
+        <v>79624</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5013,25 +5043,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5041,10 +5071,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>477454</v>
+        <v>477437</v>
       </c>
       <c r="R43" t="n">
-        <v>7069190</v>
+        <v>7068991</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5103,10 +5133,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120040169</v>
+        <v>120040135</v>
       </c>
       <c r="B44" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5119,21 +5149,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5143,10 +5173,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>477688</v>
+        <v>477507</v>
       </c>
       <c r="R44" t="n">
-        <v>7069010</v>
+        <v>7069055</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5179,11 +5209,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5210,10 +5235,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120040189</v>
+        <v>120040177</v>
       </c>
       <c r="B45" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5222,25 +5247,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5250,10 +5275,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>477498</v>
+        <v>477856</v>
       </c>
       <c r="R45" t="n">
-        <v>7069206</v>
+        <v>7069020</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5286,6 +5311,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5312,7 +5342,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120040140</v>
+        <v>120040165</v>
       </c>
       <c r="B46" t="n">
         <v>57320</v>
@@ -5352,10 +5382,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>477472</v>
+        <v>477596</v>
       </c>
       <c r="R46" t="n">
-        <v>7069006</v>
+        <v>7068950</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5392,7 +5422,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5419,7 +5449,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120040168</v>
+        <v>120040176</v>
       </c>
       <c r="B47" t="n">
         <v>57320</v>
@@ -5459,10 +5489,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>477664</v>
+        <v>477852</v>
       </c>
       <c r="R47" t="n">
-        <v>7068971</v>
+        <v>7069022</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5499,7 +5529,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack ganska färska till äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5526,10 +5556,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120040187</v>
+        <v>120040146</v>
       </c>
       <c r="B48" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5538,25 +5568,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5566,10 +5596,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>477525</v>
+        <v>477599</v>
       </c>
       <c r="R48" t="n">
-        <v>7069106</v>
+        <v>7069105</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5602,6 +5632,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5628,10 +5663,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120040192</v>
+        <v>120040172</v>
       </c>
       <c r="B49" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5640,25 +5675,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5668,10 +5703,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>477445</v>
+        <v>477777</v>
       </c>
       <c r="R49" t="n">
-        <v>7068977</v>
+        <v>7069022</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5704,6 +5739,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5730,10 +5770,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120040199</v>
+        <v>120040200</v>
       </c>
       <c r="B50" t="n">
-        <v>90576</v>
+        <v>90598</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5746,21 +5786,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5770,10 +5810,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>477671</v>
+        <v>477439</v>
       </c>
       <c r="R50" t="n">
-        <v>7068973</v>
+        <v>7069086</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5832,10 +5872,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120040180</v>
+        <v>120040150</v>
       </c>
       <c r="B51" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5848,21 +5888,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5872,10 +5912,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>477415</v>
+        <v>477457</v>
       </c>
       <c r="R51" t="n">
-        <v>7069070</v>
+        <v>7069186</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5908,6 +5948,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5934,7 +5979,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120040165</v>
+        <v>120040148</v>
       </c>
       <c r="B52" t="n">
         <v>57320</v>
@@ -5974,10 +6019,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>477596</v>
+        <v>477438</v>
       </c>
       <c r="R52" t="n">
-        <v>7068950</v>
+        <v>7069178</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6014,7 +6059,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6041,7 +6086,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120040159</v>
+        <v>120040144</v>
       </c>
       <c r="B53" t="n">
         <v>57320</v>
@@ -6081,10 +6126,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>477444</v>
+        <v>477644</v>
       </c>
       <c r="R53" t="n">
-        <v>7068963</v>
+        <v>7069114</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6121,7 +6166,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack ganska färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6148,10 +6193,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120040139</v>
+        <v>120040205</v>
       </c>
       <c r="B54" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6164,21 +6209,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6188,10 +6233,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>477517</v>
+        <v>477382</v>
       </c>
       <c r="R54" t="n">
-        <v>7068992</v>
+        <v>7069247</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6224,11 +6269,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6255,10 +6295,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120040176</v>
+        <v>120040204</v>
       </c>
       <c r="B55" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6271,21 +6311,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6295,10 +6335,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>477852</v>
+        <v>477534</v>
       </c>
       <c r="R55" t="n">
-        <v>7069022</v>
+        <v>7069288</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6331,11 +6371,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack ganska färska till äldre</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6362,10 +6397,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120040135</v>
+        <v>120040149</v>
       </c>
       <c r="B56" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6378,21 +6413,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6402,10 +6437,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>477507</v>
+        <v>477423</v>
       </c>
       <c r="R56" t="n">
-        <v>7069055</v>
+        <v>7069180</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6438,6 +6473,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6464,7 +6504,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120040175</v>
+        <v>120040152</v>
       </c>
       <c r="B57" t="n">
         <v>57320</v>
@@ -6497,37 +6537,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>477822</v>
+        <v>477472</v>
       </c>
       <c r="R57" t="n">
-        <v>7069037</v>
+        <v>7069168</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6560,6 +6580,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6586,10 +6611,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120040153</v>
+        <v>120040187</v>
       </c>
       <c r="B58" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6598,25 +6623,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6626,10 +6651,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>477547</v>
+        <v>477525</v>
       </c>
       <c r="R58" t="n">
-        <v>7069271</v>
+        <v>7069106</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6662,11 +6687,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6693,10 +6713,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120040136</v>
+        <v>120040191</v>
       </c>
       <c r="B59" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6705,25 +6725,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6733,10 +6753,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>477434</v>
+        <v>477440</v>
       </c>
       <c r="R59" t="n">
-        <v>7069116</v>
+        <v>7069251</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6795,10 +6815,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120040151</v>
+        <v>120040199</v>
       </c>
       <c r="B60" t="n">
-        <v>57320</v>
+        <v>90576</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6811,21 +6831,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6835,10 +6855,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>477460</v>
+        <v>477671</v>
       </c>
       <c r="R60" t="n">
-        <v>7069166</v>
+        <v>7068973</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6871,11 +6891,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Ringhack färska och något äldre</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6902,10 +6917,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120040147</v>
+        <v>120040192</v>
       </c>
       <c r="B61" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6914,25 +6929,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6942,10 +6957,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>477581</v>
+        <v>477445</v>
       </c>
       <c r="R61" t="n">
-        <v>7069095</v>
+        <v>7068977</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6978,11 +6993,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7009,10 +7019,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120040160</v>
+        <v>120040190</v>
       </c>
       <c r="B62" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7021,25 +7031,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7049,10 +7059,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>477440</v>
+        <v>477530</v>
       </c>
       <c r="R62" t="n">
-        <v>7068958</v>
+        <v>7069276</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7085,11 +7095,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7116,7 +7121,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120040154</v>
+        <v>120040138</v>
       </c>
       <c r="B63" t="n">
         <v>57320</v>
@@ -7156,10 +7161,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>477476</v>
+        <v>477726</v>
       </c>
       <c r="R63" t="n">
-        <v>7069264</v>
+        <v>7069062</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7223,10 +7228,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120040145</v>
+        <v>120040207</v>
       </c>
       <c r="B64" t="n">
-        <v>57320</v>
+        <v>86895</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7239,21 +7244,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7263,10 +7268,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>477626</v>
+        <v>477473</v>
       </c>
       <c r="R64" t="n">
-        <v>7069105</v>
+        <v>7069007</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7299,11 +7304,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD64" t="b">

--- a/artfynd/A 36309-2024 artfynd.xlsx
+++ b/artfynd/A 36309-2024 artfynd.xlsx
@@ -1958,10 +1958,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120040134</v>
+        <v>120040142</v>
       </c>
       <c r="B14" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1974,21 +1974,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1998,10 +1998,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>477522</v>
+        <v>477614</v>
       </c>
       <c r="R14" t="n">
-        <v>7068987</v>
+        <v>7069089</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2034,6 +2034,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2060,7 +2065,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120040142</v>
+        <v>120040175</v>
       </c>
       <c r="B15" t="n">
         <v>57320</v>
@@ -2093,17 +2098,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>477614</v>
+        <v>477822</v>
       </c>
       <c r="R15" t="n">
-        <v>7069089</v>
+        <v>7069037</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2136,11 +2161,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2167,7 +2187,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120040175</v>
+        <v>120040174</v>
       </c>
       <c r="B16" t="n">
         <v>57320</v>
@@ -2200,37 +2220,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>477822</v>
+        <v>477825</v>
       </c>
       <c r="R16" t="n">
-        <v>7069037</v>
+        <v>7069031</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2263,6 +2263,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2289,10 +2294,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120040174</v>
+        <v>120040134</v>
       </c>
       <c r="B17" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2305,21 +2310,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2329,10 +2334,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>477825</v>
+        <v>477522</v>
       </c>
       <c r="R17" t="n">
-        <v>7069031</v>
+        <v>7068987</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2365,11 +2370,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2396,10 +2396,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120040181</v>
+        <v>120040145</v>
       </c>
       <c r="B18" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2412,21 +2412,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2436,10 +2436,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>477437</v>
+        <v>477626</v>
       </c>
       <c r="R18" t="n">
-        <v>7068991</v>
+        <v>7069105</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2472,6 +2472,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2498,7 +2503,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120040145</v>
+        <v>120040163</v>
       </c>
       <c r="B19" t="n">
         <v>57320</v>
@@ -2538,10 +2543,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>477626</v>
+        <v>477544</v>
       </c>
       <c r="R19" t="n">
-        <v>7069105</v>
+        <v>7068952</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2578,7 +2583,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2605,10 +2610,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120040163</v>
+        <v>120040185</v>
       </c>
       <c r="B20" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2617,25 +2622,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2645,10 +2650,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>477544</v>
+        <v>477507</v>
       </c>
       <c r="R20" t="n">
-        <v>7068952</v>
+        <v>7069056</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2681,11 +2686,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2712,10 +2712,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120040185</v>
+        <v>120040181</v>
       </c>
       <c r="B21" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2724,25 +2724,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2752,10 +2752,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>477507</v>
+        <v>477437</v>
       </c>
       <c r="R21" t="n">
-        <v>7069056</v>
+        <v>7068991</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2921,10 +2921,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120040201</v>
+        <v>120040157</v>
       </c>
       <c r="B23" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2937,21 +2937,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2961,10 +2961,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>477484</v>
+        <v>477397</v>
       </c>
       <c r="R23" t="n">
-        <v>7068927</v>
+        <v>7069068</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2997,6 +2997,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3023,7 +3028,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120040157</v>
+        <v>120040156</v>
       </c>
       <c r="B24" t="n">
         <v>57320</v>
@@ -3063,10 +3068,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>477397</v>
+        <v>477377</v>
       </c>
       <c r="R24" t="n">
-        <v>7069068</v>
+        <v>7069208</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3103,7 +3108,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3130,7 +3135,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120040156</v>
+        <v>120040151</v>
       </c>
       <c r="B25" t="n">
         <v>57320</v>
@@ -3170,10 +3175,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>477377</v>
+        <v>477460</v>
       </c>
       <c r="R25" t="n">
-        <v>7069208</v>
+        <v>7069166</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3210,7 +3215,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack färska och något äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3237,10 +3242,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120040151</v>
+        <v>120040201</v>
       </c>
       <c r="B26" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3253,21 +3258,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3277,10 +3282,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>477460</v>
+        <v>477484</v>
       </c>
       <c r="R26" t="n">
-        <v>7069166</v>
+        <v>7068927</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3313,11 +3318,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack färska och något äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3344,10 +3344,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120040206</v>
+        <v>120040169</v>
       </c>
       <c r="B27" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3360,21 +3360,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3384,10 +3384,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>477405</v>
+        <v>477688</v>
       </c>
       <c r="R27" t="n">
-        <v>7069105</v>
+        <v>7069010</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3420,6 +3420,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3446,10 +3451,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120040169</v>
+        <v>120040206</v>
       </c>
       <c r="B28" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3462,21 +3467,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3486,10 +3491,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>477688</v>
+        <v>477405</v>
       </c>
       <c r="R28" t="n">
-        <v>7069010</v>
+        <v>7069105</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3522,11 +3527,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4073,10 +4073,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120040184</v>
+        <v>120040154</v>
       </c>
       <c r="B34" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4085,25 +4085,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4113,10 +4113,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>477481</v>
+        <v>477476</v>
       </c>
       <c r="R34" t="n">
-        <v>7069004</v>
+        <v>7069264</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4149,6 +4149,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4175,7 +4180,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120040154</v>
+        <v>120040140</v>
       </c>
       <c r="B35" t="n">
         <v>57320</v>
@@ -4215,10 +4220,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>477476</v>
+        <v>477472</v>
       </c>
       <c r="R35" t="n">
-        <v>7069264</v>
+        <v>7069006</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4282,7 +4287,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120040140</v>
+        <v>120040168</v>
       </c>
       <c r="B36" t="n">
         <v>57320</v>
@@ -4322,10 +4327,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>477472</v>
+        <v>477664</v>
       </c>
       <c r="R36" t="n">
-        <v>7069006</v>
+        <v>7068971</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4362,7 +4367,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4389,7 +4394,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120040168</v>
+        <v>120040160</v>
       </c>
       <c r="B37" t="n">
         <v>57320</v>
@@ -4429,10 +4434,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>477664</v>
+        <v>477440</v>
       </c>
       <c r="R37" t="n">
-        <v>7068971</v>
+        <v>7068958</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4469,7 +4474,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4496,7 +4501,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120040160</v>
+        <v>120040166</v>
       </c>
       <c r="B38" t="n">
         <v>57320</v>
@@ -4536,10 +4541,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>477440</v>
+        <v>477622</v>
       </c>
       <c r="R38" t="n">
-        <v>7068958</v>
+        <v>7068965</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4576,7 +4581,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4603,10 +4608,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120040166</v>
+        <v>120040184</v>
       </c>
       <c r="B39" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4615,25 +4620,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4643,10 +4648,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>477622</v>
+        <v>477481</v>
       </c>
       <c r="R39" t="n">
-        <v>7068965</v>
+        <v>7069004</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4679,11 +4684,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5031,10 +5031,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120040179</v>
+        <v>120040177</v>
       </c>
       <c r="B43" t="n">
-        <v>79624</v>
+        <v>57320</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5047,21 +5047,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5071,10 +5071,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>477437</v>
+        <v>477856</v>
       </c>
       <c r="R43" t="n">
-        <v>7068991</v>
+        <v>7069020</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5107,6 +5107,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5133,10 +5138,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120040135</v>
+        <v>120040146</v>
       </c>
       <c r="B44" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5149,21 +5154,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5173,10 +5178,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>477507</v>
+        <v>477599</v>
       </c>
       <c r="R44" t="n">
-        <v>7069055</v>
+        <v>7069105</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5209,6 +5214,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5235,7 +5245,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120040177</v>
+        <v>120040165</v>
       </c>
       <c r="B45" t="n">
         <v>57320</v>
@@ -5275,10 +5285,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>477856</v>
+        <v>477596</v>
       </c>
       <c r="R45" t="n">
-        <v>7069020</v>
+        <v>7068950</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5315,7 +5325,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5342,7 +5352,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120040165</v>
+        <v>120040176</v>
       </c>
       <c r="B46" t="n">
         <v>57320</v>
@@ -5382,10 +5392,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>477596</v>
+        <v>477852</v>
       </c>
       <c r="R46" t="n">
-        <v>7068950</v>
+        <v>7069022</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5422,7 +5432,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack ganska färska till äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5449,10 +5459,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120040176</v>
+        <v>120040135</v>
       </c>
       <c r="B47" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5465,21 +5475,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5489,10 +5499,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>477852</v>
+        <v>477507</v>
       </c>
       <c r="R47" t="n">
-        <v>7069022</v>
+        <v>7069055</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5525,11 +5535,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack ganska färska till äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5556,10 +5561,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120040146</v>
+        <v>120040179</v>
       </c>
       <c r="B48" t="n">
-        <v>57320</v>
+        <v>79624</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5572,21 +5577,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5596,10 +5601,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>477599</v>
+        <v>477437</v>
       </c>
       <c r="R48" t="n">
-        <v>7069105</v>
+        <v>7068991</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5632,11 +5637,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -7019,10 +7019,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120040190</v>
+        <v>120040138</v>
       </c>
       <c r="B62" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7031,25 +7031,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7059,10 +7059,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>477530</v>
+        <v>477726</v>
       </c>
       <c r="R62" t="n">
-        <v>7069276</v>
+        <v>7069062</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7095,6 +7095,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7121,10 +7126,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120040138</v>
+        <v>120040207</v>
       </c>
       <c r="B63" t="n">
-        <v>57320</v>
+        <v>86895</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7137,21 +7142,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7161,10 +7166,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>477726</v>
+        <v>477473</v>
       </c>
       <c r="R63" t="n">
-        <v>7069062</v>
+        <v>7069007</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7197,11 +7202,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7228,10 +7228,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120040207</v>
+        <v>120040190</v>
       </c>
       <c r="B64" t="n">
-        <v>86895</v>
+        <v>97930</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7240,25 +7240,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>510</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7268,10 +7268,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>477473</v>
+        <v>477530</v>
       </c>
       <c r="R64" t="n">
-        <v>7069007</v>
+        <v>7069276</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>

--- a/artfynd/A 36309-2024 artfynd.xlsx
+++ b/artfynd/A 36309-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120040162</v>
+        <v>120040191</v>
       </c>
       <c r="B2" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477471</v>
+        <v>477440</v>
       </c>
       <c r="R2" t="n">
-        <v>7068928</v>
+        <v>7069251</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120040180</v>
+        <v>120040200</v>
       </c>
       <c r="B3" t="n">
-        <v>79623</v>
+        <v>90598</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477415</v>
+        <v>477439</v>
       </c>
       <c r="R3" t="n">
-        <v>7069070</v>
+        <v>7069086</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120040183</v>
+        <v>120040199</v>
       </c>
       <c r="B4" t="n">
-        <v>57431</v>
+        <v>90576</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,50 +891,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103031</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477821</v>
+        <v>477671</v>
       </c>
       <c r="R4" t="n">
-        <v>7069026</v>
+        <v>7068973</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120040167</v>
+        <v>120040188</v>
       </c>
       <c r="B5" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1010,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1038,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477641</v>
+        <v>477454</v>
       </c>
       <c r="R5" t="n">
-        <v>7068958</v>
+        <v>7069190</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1074,11 +1057,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack ganska färska</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1105,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120040188</v>
+        <v>120040162</v>
       </c>
       <c r="B6" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1117,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1145,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477454</v>
+        <v>477471</v>
       </c>
       <c r="R6" t="n">
-        <v>7069190</v>
+        <v>7068928</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1181,6 +1159,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1207,7 +1190,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120040164</v>
+        <v>120040169</v>
       </c>
       <c r="B7" t="n">
         <v>57320</v>
@@ -1247,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477597</v>
+        <v>477688</v>
       </c>
       <c r="R7" t="n">
-        <v>7068964</v>
+        <v>7069010</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,7 +1270,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1314,7 +1297,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120040159</v>
+        <v>120040156</v>
       </c>
       <c r="B8" t="n">
         <v>57320</v>
@@ -1354,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477444</v>
+        <v>477377</v>
       </c>
       <c r="R8" t="n">
-        <v>7068963</v>
+        <v>7069208</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1394,7 +1377,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack ganska färska till äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1421,7 +1404,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120040158</v>
+        <v>120040144</v>
       </c>
       <c r="B9" t="n">
         <v>57320</v>
@@ -1461,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>477446</v>
+        <v>477644</v>
       </c>
       <c r="R9" t="n">
-        <v>7069039</v>
+        <v>7069114</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1501,7 +1484,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1528,10 +1511,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120040136</v>
+        <v>120040203</v>
       </c>
       <c r="B10" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1544,21 +1527,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1568,10 +1551,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>477434</v>
+        <v>477472</v>
       </c>
       <c r="R10" t="n">
-        <v>7069116</v>
+        <v>7069087</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1630,10 +1613,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120040139</v>
+        <v>120040179</v>
       </c>
       <c r="B11" t="n">
-        <v>57320</v>
+        <v>79624</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1646,21 +1629,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1670,10 +1653,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>477517</v>
+        <v>477437</v>
       </c>
       <c r="R11" t="n">
-        <v>7068992</v>
+        <v>7068991</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1706,11 +1689,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1737,10 +1715,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120040147</v>
+        <v>120040206</v>
       </c>
       <c r="B12" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1753,21 +1731,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1777,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>477581</v>
+        <v>477405</v>
       </c>
       <c r="R12" t="n">
-        <v>7069095</v>
+        <v>7069105</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1813,11 +1791,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1844,10 +1817,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120040182</v>
+        <v>120040147</v>
       </c>
       <c r="B13" t="n">
-        <v>57431</v>
+        <v>57320</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1856,20 +1829,20 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1877,29 +1850,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>477760</v>
+        <v>477581</v>
       </c>
       <c r="R13" t="n">
-        <v>7069037</v>
+        <v>7069095</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1932,6 +1893,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1958,7 +1924,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120040142</v>
+        <v>120040145</v>
       </c>
       <c r="B14" t="n">
         <v>57320</v>
@@ -1998,10 +1964,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>477614</v>
+        <v>477626</v>
       </c>
       <c r="R14" t="n">
-        <v>7069089</v>
+        <v>7069105</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2065,10 +2031,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120040175</v>
+        <v>120040189</v>
       </c>
       <c r="B15" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2077,58 +2043,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>477822</v>
+        <v>477498</v>
       </c>
       <c r="R15" t="n">
-        <v>7069037</v>
+        <v>7069206</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2187,10 +2133,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120040174</v>
+        <v>120040184</v>
       </c>
       <c r="B16" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2199,25 +2145,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2227,10 +2173,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>477825</v>
+        <v>477481</v>
       </c>
       <c r="R16" t="n">
-        <v>7069031</v>
+        <v>7069004</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2263,11 +2209,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2294,10 +2235,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120040134</v>
+        <v>120040138</v>
       </c>
       <c r="B17" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2310,21 +2251,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2334,10 +2275,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>477522</v>
+        <v>477726</v>
       </c>
       <c r="R17" t="n">
-        <v>7068987</v>
+        <v>7069062</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2370,6 +2311,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2396,7 +2342,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120040145</v>
+        <v>120040177</v>
       </c>
       <c r="B18" t="n">
         <v>57320</v>
@@ -2436,10 +2382,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>477626</v>
+        <v>477856</v>
       </c>
       <c r="R18" t="n">
-        <v>7069105</v>
+        <v>7069020</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2476,7 +2422,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2503,7 +2449,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120040163</v>
+        <v>120040154</v>
       </c>
       <c r="B19" t="n">
         <v>57320</v>
@@ -2543,10 +2489,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>477544</v>
+        <v>477476</v>
       </c>
       <c r="R19" t="n">
-        <v>7068952</v>
+        <v>7069264</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2583,7 +2529,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2610,10 +2556,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120040185</v>
+        <v>120040168</v>
       </c>
       <c r="B20" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2622,25 +2568,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2650,10 +2596,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>477507</v>
+        <v>477664</v>
       </c>
       <c r="R20" t="n">
-        <v>7069056</v>
+        <v>7068971</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2686,6 +2632,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2712,10 +2663,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120040181</v>
+        <v>120040205</v>
       </c>
       <c r="B21" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2728,21 +2679,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2752,10 +2703,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>477437</v>
+        <v>477382</v>
       </c>
       <c r="R21" t="n">
-        <v>7068991</v>
+        <v>7069247</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2814,7 +2765,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120040153</v>
+        <v>120040139</v>
       </c>
       <c r="B22" t="n">
         <v>57320</v>
@@ -2854,10 +2805,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>477547</v>
+        <v>477517</v>
       </c>
       <c r="R22" t="n">
-        <v>7069271</v>
+        <v>7068992</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2921,7 +2872,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120040157</v>
+        <v>120040153</v>
       </c>
       <c r="B23" t="n">
         <v>57320</v>
@@ -2961,10 +2912,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>477397</v>
+        <v>477547</v>
       </c>
       <c r="R23" t="n">
-        <v>7069068</v>
+        <v>7069271</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3001,7 +2952,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3028,7 +2979,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120040156</v>
+        <v>120040157</v>
       </c>
       <c r="B24" t="n">
         <v>57320</v>
@@ -3068,10 +3019,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>477377</v>
+        <v>477397</v>
       </c>
       <c r="R24" t="n">
-        <v>7069208</v>
+        <v>7069068</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3108,7 +3059,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3135,10 +3086,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120040151</v>
+        <v>120040185</v>
       </c>
       <c r="B25" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3147,25 +3098,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3175,10 +3126,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>477460</v>
+        <v>477507</v>
       </c>
       <c r="R25" t="n">
-        <v>7069166</v>
+        <v>7069056</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3211,11 +3162,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack färska och något äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3242,10 +3188,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120040201</v>
+        <v>120040171</v>
       </c>
       <c r="B26" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3258,21 +3204,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3282,10 +3228,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>477484</v>
+        <v>477759</v>
       </c>
       <c r="R26" t="n">
-        <v>7068927</v>
+        <v>7069019</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3318,6 +3264,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3344,10 +3295,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120040169</v>
+        <v>120040183</v>
       </c>
       <c r="B27" t="n">
-        <v>57320</v>
+        <v>57431</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3356,20 +3307,20 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3377,17 +3328,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>477688</v>
+        <v>477821</v>
       </c>
       <c r="R27" t="n">
-        <v>7069010</v>
+        <v>7069026</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3420,11 +3383,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3451,10 +3409,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120040206</v>
+        <v>120040202</v>
       </c>
       <c r="B28" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3467,21 +3425,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3491,10 +3449,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>477405</v>
+        <v>477674</v>
       </c>
       <c r="R28" t="n">
-        <v>7069105</v>
+        <v>7069000</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3553,10 +3511,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120040202</v>
+        <v>120040204</v>
       </c>
       <c r="B29" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3569,21 +3527,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3593,10 +3551,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>477674</v>
+        <v>477534</v>
       </c>
       <c r="R29" t="n">
-        <v>7069000</v>
+        <v>7069288</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3655,10 +3613,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120040203</v>
+        <v>120040180</v>
       </c>
       <c r="B30" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3671,21 +3629,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3695,10 +3653,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>477472</v>
+        <v>477415</v>
       </c>
       <c r="R30" t="n">
-        <v>7069087</v>
+        <v>7069070</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3757,10 +3715,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120040161</v>
+        <v>120040201</v>
       </c>
       <c r="B31" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3773,21 +3731,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3797,10 +3755,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>477426</v>
+        <v>477484</v>
       </c>
       <c r="R31" t="n">
-        <v>7068947</v>
+        <v>7068927</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3833,11 +3791,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3864,7 +3817,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120040170</v>
+        <v>120040152</v>
       </c>
       <c r="B32" t="n">
         <v>57320</v>
@@ -3904,10 +3857,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>477755</v>
+        <v>477472</v>
       </c>
       <c r="R32" t="n">
-        <v>7069016</v>
+        <v>7069168</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3971,10 +3924,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120040189</v>
+        <v>120040150</v>
       </c>
       <c r="B33" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3983,25 +3936,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4011,10 +3964,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>477498</v>
+        <v>477457</v>
       </c>
       <c r="R33" t="n">
-        <v>7069206</v>
+        <v>7069186</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4047,6 +4000,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4073,7 +4031,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120040154</v>
+        <v>120040148</v>
       </c>
       <c r="B34" t="n">
         <v>57320</v>
@@ -4113,10 +4071,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>477476</v>
+        <v>477438</v>
       </c>
       <c r="R34" t="n">
-        <v>7069264</v>
+        <v>7069178</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4180,7 +4138,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120040140</v>
+        <v>120040158</v>
       </c>
       <c r="B35" t="n">
         <v>57320</v>
@@ -4220,10 +4178,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>477472</v>
+        <v>477446</v>
       </c>
       <c r="R35" t="n">
-        <v>7069006</v>
+        <v>7069039</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4260,7 +4218,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4287,10 +4245,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120040168</v>
+        <v>120040181</v>
       </c>
       <c r="B36" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4303,21 +4261,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4327,10 +4285,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>477664</v>
+        <v>477437</v>
       </c>
       <c r="R36" t="n">
-        <v>7068971</v>
+        <v>7068991</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4363,11 +4321,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4501,7 +4454,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120040166</v>
+        <v>120040161</v>
       </c>
       <c r="B38" t="n">
         <v>57320</v>
@@ -4541,10 +4494,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>477622</v>
+        <v>477426</v>
       </c>
       <c r="R38" t="n">
-        <v>7068965</v>
+        <v>7068947</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4581,7 +4534,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4608,10 +4561,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120040184</v>
+        <v>120040136</v>
       </c>
       <c r="B39" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4620,25 +4573,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4648,10 +4601,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>477481</v>
+        <v>477434</v>
       </c>
       <c r="R39" t="n">
-        <v>7069004</v>
+        <v>7069116</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4710,7 +4663,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120040173</v>
+        <v>120040140</v>
       </c>
       <c r="B40" t="n">
         <v>57320</v>
@@ -4750,10 +4703,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>477786</v>
+        <v>477472</v>
       </c>
       <c r="R40" t="n">
-        <v>7069029</v>
+        <v>7069006</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4817,7 +4770,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120040141</v>
+        <v>120040159</v>
       </c>
       <c r="B41" t="n">
         <v>57320</v>
@@ -4857,10 +4810,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>477562</v>
+        <v>477444</v>
       </c>
       <c r="R41" t="n">
-        <v>7069078</v>
+        <v>7068963</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4897,7 +4850,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack ganska färska till äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4924,7 +4877,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120040171</v>
+        <v>120040173</v>
       </c>
       <c r="B42" t="n">
         <v>57320</v>
@@ -4964,10 +4917,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>477759</v>
+        <v>477786</v>
       </c>
       <c r="R42" t="n">
-        <v>7069019</v>
+        <v>7069029</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5031,7 +4984,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120040177</v>
+        <v>120040174</v>
       </c>
       <c r="B43" t="n">
         <v>57320</v>
@@ -5071,10 +5024,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>477856</v>
+        <v>477825</v>
       </c>
       <c r="R43" t="n">
-        <v>7069020</v>
+        <v>7069031</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5111,7 +5064,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5138,10 +5091,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120040146</v>
+        <v>120040135</v>
       </c>
       <c r="B44" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5154,21 +5107,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5178,10 +5131,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>477599</v>
+        <v>477507</v>
       </c>
       <c r="R44" t="n">
-        <v>7069105</v>
+        <v>7069055</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5214,11 +5167,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5245,10 +5193,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120040165</v>
+        <v>120040182</v>
       </c>
       <c r="B45" t="n">
-        <v>57320</v>
+        <v>57431</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5257,20 +5205,20 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5278,17 +5226,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>477596</v>
+        <v>477760</v>
       </c>
       <c r="R45" t="n">
-        <v>7068950</v>
+        <v>7069037</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5321,11 +5281,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5352,10 +5307,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120040176</v>
+        <v>120040187</v>
       </c>
       <c r="B46" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5364,25 +5319,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5392,10 +5347,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>477852</v>
+        <v>477525</v>
       </c>
       <c r="R46" t="n">
-        <v>7069022</v>
+        <v>7069106</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5428,11 +5383,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack ganska färska till äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5459,10 +5409,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120040135</v>
+        <v>120040207</v>
       </c>
       <c r="B47" t="n">
-        <v>90580</v>
+        <v>86895</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5475,21 +5425,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5499,10 +5449,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>477507</v>
+        <v>477473</v>
       </c>
       <c r="R47" t="n">
-        <v>7069055</v>
+        <v>7069007</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5561,10 +5511,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120040179</v>
+        <v>120040146</v>
       </c>
       <c r="B48" t="n">
-        <v>79624</v>
+        <v>57320</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5577,21 +5527,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5601,10 +5551,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>477437</v>
+        <v>477599</v>
       </c>
       <c r="R48" t="n">
-        <v>7068991</v>
+        <v>7069105</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5637,6 +5587,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5663,7 +5618,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120040172</v>
+        <v>120040142</v>
       </c>
       <c r="B49" t="n">
         <v>57320</v>
@@ -5703,10 +5658,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>477777</v>
+        <v>477614</v>
       </c>
       <c r="R49" t="n">
-        <v>7069022</v>
+        <v>7069089</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5770,10 +5725,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120040200</v>
+        <v>120040165</v>
       </c>
       <c r="B50" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5786,21 +5741,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5810,10 +5765,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>477439</v>
+        <v>477596</v>
       </c>
       <c r="R50" t="n">
-        <v>7069086</v>
+        <v>7068950</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5846,6 +5801,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5872,7 +5832,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120040150</v>
+        <v>120040166</v>
       </c>
       <c r="B51" t="n">
         <v>57320</v>
@@ -5912,10 +5872,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>477457</v>
+        <v>477622</v>
       </c>
       <c r="R51" t="n">
-        <v>7069186</v>
+        <v>7068965</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5952,7 +5912,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5979,7 +5939,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120040148</v>
+        <v>120040163</v>
       </c>
       <c r="B52" t="n">
         <v>57320</v>
@@ -6019,10 +5979,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>477438</v>
+        <v>477544</v>
       </c>
       <c r="R52" t="n">
-        <v>7069178</v>
+        <v>7068952</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6059,7 +6019,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6086,7 +6046,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120040144</v>
+        <v>120040141</v>
       </c>
       <c r="B53" t="n">
         <v>57320</v>
@@ -6126,10 +6086,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>477644</v>
+        <v>477562</v>
       </c>
       <c r="R53" t="n">
-        <v>7069114</v>
+        <v>7069078</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6193,10 +6153,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120040205</v>
+        <v>120040172</v>
       </c>
       <c r="B54" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6209,21 +6169,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6233,10 +6193,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>477382</v>
+        <v>477777</v>
       </c>
       <c r="R54" t="n">
-        <v>7069247</v>
+        <v>7069022</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6269,6 +6229,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6295,10 +6260,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120040204</v>
+        <v>120040167</v>
       </c>
       <c r="B55" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6311,21 +6276,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6335,10 +6300,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>477534</v>
+        <v>477641</v>
       </c>
       <c r="R55" t="n">
-        <v>7069288</v>
+        <v>7068958</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6371,6 +6336,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack ganska färska</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6397,10 +6367,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120040149</v>
+        <v>120040192</v>
       </c>
       <c r="B56" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6409,25 +6379,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6437,10 +6407,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>477423</v>
+        <v>477445</v>
       </c>
       <c r="R56" t="n">
-        <v>7069180</v>
+        <v>7068977</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6473,11 +6443,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6504,7 +6469,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120040152</v>
+        <v>120040164</v>
       </c>
       <c r="B57" t="n">
         <v>57320</v>
@@ -6544,10 +6509,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>477472</v>
+        <v>477597</v>
       </c>
       <c r="R57" t="n">
-        <v>7069168</v>
+        <v>7068964</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6584,7 +6549,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6611,10 +6576,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120040187</v>
+        <v>120040175</v>
       </c>
       <c r="B58" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6623,38 +6588,58 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>477525</v>
+        <v>477822</v>
       </c>
       <c r="R58" t="n">
-        <v>7069106</v>
+        <v>7069037</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6713,10 +6698,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120040191</v>
+        <v>120040149</v>
       </c>
       <c r="B59" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6725,25 +6710,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6753,10 +6738,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>477440</v>
+        <v>477423</v>
       </c>
       <c r="R59" t="n">
-        <v>7069251</v>
+        <v>7069180</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6789,6 +6774,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6815,10 +6805,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120040199</v>
+        <v>120040134</v>
       </c>
       <c r="B60" t="n">
-        <v>90576</v>
+        <v>90580</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6831,21 +6821,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6855,10 +6845,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>477671</v>
+        <v>477522</v>
       </c>
       <c r="R60" t="n">
-        <v>7068973</v>
+        <v>7068987</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6917,10 +6907,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120040192</v>
+        <v>120040176</v>
       </c>
       <c r="B61" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6929,25 +6919,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6957,10 +6947,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>477445</v>
+        <v>477852</v>
       </c>
       <c r="R61" t="n">
-        <v>7068977</v>
+        <v>7069022</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6993,6 +6983,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Ringhack ganska färska till äldre</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7019,7 +7014,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120040138</v>
+        <v>120040151</v>
       </c>
       <c r="B62" t="n">
         <v>57320</v>
@@ -7059,10 +7054,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>477726</v>
+        <v>477460</v>
       </c>
       <c r="R62" t="n">
-        <v>7069062</v>
+        <v>7069166</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7099,7 +7094,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och något äldre</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7126,10 +7121,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120040207</v>
+        <v>120040190</v>
       </c>
       <c r="B63" t="n">
-        <v>86895</v>
+        <v>97930</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7138,25 +7133,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>510</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7166,10 +7161,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>477473</v>
+        <v>477530</v>
       </c>
       <c r="R63" t="n">
-        <v>7069007</v>
+        <v>7069276</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7228,10 +7223,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120040190</v>
+        <v>120040170</v>
       </c>
       <c r="B64" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7240,25 +7235,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7268,10 +7263,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>477530</v>
+        <v>477755</v>
       </c>
       <c r="R64" t="n">
-        <v>7069276</v>
+        <v>7069016</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7304,6 +7299,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD64" t="b">

--- a/artfynd/A 36309-2024 artfynd.xlsx
+++ b/artfynd/A 36309-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120040191</v>
+        <v>120040154</v>
       </c>
       <c r="B2" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477440</v>
+        <v>477476</v>
       </c>
       <c r="R2" t="n">
-        <v>7069251</v>
+        <v>7069264</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120040200</v>
+        <v>120040170</v>
       </c>
       <c r="B3" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477439</v>
+        <v>477755</v>
       </c>
       <c r="R3" t="n">
-        <v>7069086</v>
+        <v>7069016</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,6 +858,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120040199</v>
+        <v>120040201</v>
       </c>
       <c r="B4" t="n">
-        <v>90576</v>
+        <v>90598</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477671</v>
+        <v>477484</v>
       </c>
       <c r="R4" t="n">
-        <v>7068973</v>
+        <v>7068927</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120040188</v>
+        <v>120040163</v>
       </c>
       <c r="B5" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +1003,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477454</v>
+        <v>477544</v>
       </c>
       <c r="R5" t="n">
-        <v>7069190</v>
+        <v>7068952</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1057,6 +1067,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1083,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120040162</v>
+        <v>120040182</v>
       </c>
       <c r="B6" t="n">
-        <v>57320</v>
+        <v>57431</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,20 +1110,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1116,17 +1131,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477471</v>
+        <v>477760</v>
       </c>
       <c r="R6" t="n">
-        <v>7068928</v>
+        <v>7069037</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1159,11 +1186,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1190,7 +1212,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120040169</v>
+        <v>120040159</v>
       </c>
       <c r="B7" t="n">
         <v>57320</v>
@@ -1230,10 +1252,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477688</v>
+        <v>477444</v>
       </c>
       <c r="R7" t="n">
-        <v>7069010</v>
+        <v>7068963</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1270,7 +1292,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack ganska färska till äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1297,7 +1319,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120040156</v>
+        <v>120040155</v>
       </c>
       <c r="B8" t="n">
         <v>57320</v>
@@ -1377,7 +1399,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1404,10 +1426,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120040144</v>
+        <v>120040180</v>
       </c>
       <c r="B9" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1420,21 +1442,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1444,10 +1466,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>477644</v>
+        <v>477415</v>
       </c>
       <c r="R9" t="n">
-        <v>7069114</v>
+        <v>7069070</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1480,11 +1502,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1511,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120040203</v>
+        <v>120040166</v>
       </c>
       <c r="B10" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1527,21 +1544,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1551,10 +1568,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>477472</v>
+        <v>477622</v>
       </c>
       <c r="R10" t="n">
-        <v>7069087</v>
+        <v>7068965</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1587,6 +1604,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1613,10 +1635,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120040179</v>
+        <v>120040162</v>
       </c>
       <c r="B11" t="n">
-        <v>79624</v>
+        <v>57320</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1629,21 +1651,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1653,10 +1675,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>477437</v>
+        <v>477471</v>
       </c>
       <c r="R11" t="n">
-        <v>7068991</v>
+        <v>7068928</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1689,6 +1711,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1715,10 +1742,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120040206</v>
+        <v>120040171</v>
       </c>
       <c r="B12" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1731,21 +1758,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1755,10 +1782,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>477405</v>
+        <v>477759</v>
       </c>
       <c r="R12" t="n">
-        <v>7069105</v>
+        <v>7069019</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1791,6 +1818,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1817,10 +1849,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120040147</v>
+        <v>120040203</v>
       </c>
       <c r="B13" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1833,21 +1865,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1857,10 +1889,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>477581</v>
+        <v>477472</v>
       </c>
       <c r="R13" t="n">
-        <v>7069095</v>
+        <v>7069087</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1893,11 +1925,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1924,10 +1951,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120040145</v>
+        <v>120040181</v>
       </c>
       <c r="B14" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1940,21 +1967,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1964,10 +1991,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>477626</v>
+        <v>477437</v>
       </c>
       <c r="R14" t="n">
-        <v>7069105</v>
+        <v>7068991</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2000,11 +2027,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2031,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120040189</v>
+        <v>120040138</v>
       </c>
       <c r="B15" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2043,25 +2065,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2071,10 +2093,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>477498</v>
+        <v>477726</v>
       </c>
       <c r="R15" t="n">
-        <v>7069206</v>
+        <v>7069062</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2107,6 +2129,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2133,10 +2160,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120040184</v>
+        <v>120040168</v>
       </c>
       <c r="B16" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2145,25 +2172,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2173,10 +2200,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>477481</v>
+        <v>477664</v>
       </c>
       <c r="R16" t="n">
-        <v>7069004</v>
+        <v>7068971</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2209,6 +2236,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2235,7 +2267,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120040138</v>
+        <v>120040157</v>
       </c>
       <c r="B17" t="n">
         <v>57320</v>
@@ -2275,10 +2307,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>477726</v>
+        <v>477397</v>
       </c>
       <c r="R17" t="n">
-        <v>7069062</v>
+        <v>7069068</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2315,7 +2347,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2342,10 +2374,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120040177</v>
+        <v>120040135</v>
       </c>
       <c r="B18" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2358,21 +2390,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2382,10 +2414,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>477856</v>
+        <v>477507</v>
       </c>
       <c r="R18" t="n">
-        <v>7069020</v>
+        <v>7069055</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2418,11 +2450,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2449,10 +2476,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120040154</v>
+        <v>120040184</v>
       </c>
       <c r="B19" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2461,25 +2488,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2489,10 +2516,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>477476</v>
+        <v>477481</v>
       </c>
       <c r="R19" t="n">
-        <v>7069264</v>
+        <v>7069004</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2525,11 +2552,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2556,10 +2578,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120040168</v>
+        <v>120040199</v>
       </c>
       <c r="B20" t="n">
-        <v>57320</v>
+        <v>90576</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2572,21 +2594,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2596,10 +2618,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>477664</v>
+        <v>477671</v>
       </c>
       <c r="R20" t="n">
-        <v>7068971</v>
+        <v>7068973</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2632,11 +2654,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2663,10 +2680,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120040205</v>
+        <v>120040147</v>
       </c>
       <c r="B21" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2679,21 +2696,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2703,10 +2720,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>477382</v>
+        <v>477581</v>
       </c>
       <c r="R21" t="n">
-        <v>7069247</v>
+        <v>7069095</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2739,6 +2756,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2765,10 +2787,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120040139</v>
+        <v>120040206</v>
       </c>
       <c r="B22" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2781,21 +2803,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2805,10 +2827,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>477517</v>
+        <v>477405</v>
       </c>
       <c r="R22" t="n">
-        <v>7068992</v>
+        <v>7069105</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2841,11 +2863,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2872,7 +2889,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120040153</v>
+        <v>120040172</v>
       </c>
       <c r="B23" t="n">
         <v>57320</v>
@@ -2912,10 +2929,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>477547</v>
+        <v>477777</v>
       </c>
       <c r="R23" t="n">
-        <v>7069271</v>
+        <v>7069022</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2979,7 +2996,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120040157</v>
+        <v>120040141</v>
       </c>
       <c r="B24" t="n">
         <v>57320</v>
@@ -3019,10 +3036,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>477397</v>
+        <v>477562</v>
       </c>
       <c r="R24" t="n">
-        <v>7069068</v>
+        <v>7069078</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3059,7 +3076,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3086,7 +3103,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120040185</v>
+        <v>120040187</v>
       </c>
       <c r="B25" t="n">
         <v>97930</v>
@@ -3126,10 +3143,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>477507</v>
+        <v>477525</v>
       </c>
       <c r="R25" t="n">
-        <v>7069056</v>
+        <v>7069106</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3188,10 +3205,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120040171</v>
+        <v>120040192</v>
       </c>
       <c r="B26" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3200,25 +3217,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3228,10 +3245,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>477759</v>
+        <v>477445</v>
       </c>
       <c r="R26" t="n">
-        <v>7069019</v>
+        <v>7068977</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3264,11 +3281,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3295,10 +3307,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120040183</v>
+        <v>120040151</v>
       </c>
       <c r="B27" t="n">
-        <v>57431</v>
+        <v>57320</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3307,20 +3319,20 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3328,29 +3340,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>477821</v>
+        <v>477460</v>
       </c>
       <c r="R27" t="n">
-        <v>7069026</v>
+        <v>7069166</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3383,6 +3383,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack färska och något äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3409,10 +3414,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120040202</v>
+        <v>120040148</v>
       </c>
       <c r="B28" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3425,21 +3430,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3449,10 +3454,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>477674</v>
+        <v>477438</v>
       </c>
       <c r="R28" t="n">
-        <v>7069000</v>
+        <v>7069178</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3485,6 +3490,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3511,10 +3521,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120040204</v>
+        <v>120040140</v>
       </c>
       <c r="B29" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3527,21 +3537,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3551,10 +3561,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>477534</v>
+        <v>477472</v>
       </c>
       <c r="R29" t="n">
-        <v>7069288</v>
+        <v>7069006</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3587,6 +3597,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3613,10 +3628,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120040180</v>
+        <v>120040185</v>
       </c>
       <c r="B30" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3625,25 +3640,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3653,10 +3668,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>477415</v>
+        <v>477507</v>
       </c>
       <c r="R30" t="n">
-        <v>7069070</v>
+        <v>7069056</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3715,10 +3730,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120040201</v>
+        <v>120040190</v>
       </c>
       <c r="B31" t="n">
-        <v>90598</v>
+        <v>97930</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3727,25 +3742,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3755,10 +3770,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>477484</v>
+        <v>477530</v>
       </c>
       <c r="R31" t="n">
-        <v>7068927</v>
+        <v>7069276</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3817,7 +3832,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120040152</v>
+        <v>120040142</v>
       </c>
       <c r="B32" t="n">
         <v>57320</v>
@@ -3857,10 +3872,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>477472</v>
+        <v>477614</v>
       </c>
       <c r="R32" t="n">
-        <v>7069168</v>
+        <v>7069089</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3924,10 +3939,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120040150</v>
+        <v>120040136</v>
       </c>
       <c r="B33" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3940,21 +3955,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3964,10 +3979,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>477457</v>
+        <v>477434</v>
       </c>
       <c r="R33" t="n">
-        <v>7069186</v>
+        <v>7069116</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4000,11 +4015,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4031,10 +4041,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120040148</v>
+        <v>120040202</v>
       </c>
       <c r="B34" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4047,21 +4057,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4071,10 +4081,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>477438</v>
+        <v>477674</v>
       </c>
       <c r="R34" t="n">
-        <v>7069178</v>
+        <v>7069000</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4107,11 +4117,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4138,7 +4143,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120040158</v>
+        <v>120040160</v>
       </c>
       <c r="B35" t="n">
         <v>57320</v>
@@ -4178,10 +4183,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>477446</v>
+        <v>477440</v>
       </c>
       <c r="R35" t="n">
-        <v>7069039</v>
+        <v>7068958</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4218,7 +4223,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4245,10 +4250,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120040181</v>
+        <v>120040173</v>
       </c>
       <c r="B36" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4261,21 +4266,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4285,10 +4290,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>477437</v>
+        <v>477786</v>
       </c>
       <c r="R36" t="n">
-        <v>7068991</v>
+        <v>7069029</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4321,6 +4326,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4347,7 +4357,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120040160</v>
+        <v>120040153</v>
       </c>
       <c r="B37" t="n">
         <v>57320</v>
@@ -4387,10 +4397,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>477440</v>
+        <v>477547</v>
       </c>
       <c r="R37" t="n">
-        <v>7068958</v>
+        <v>7069271</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4454,10 +4464,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120040161</v>
+        <v>120040205</v>
       </c>
       <c r="B38" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4470,21 +4480,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4494,10 +4504,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>477426</v>
+        <v>477382</v>
       </c>
       <c r="R38" t="n">
-        <v>7068947</v>
+        <v>7069247</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4530,11 +4540,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4561,10 +4566,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120040136</v>
+        <v>120040149</v>
       </c>
       <c r="B39" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4577,21 +4582,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4601,10 +4606,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>477434</v>
+        <v>477423</v>
       </c>
       <c r="R39" t="n">
-        <v>7069116</v>
+        <v>7069180</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4637,6 +4642,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4663,10 +4673,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120040140</v>
+        <v>120040179</v>
       </c>
       <c r="B40" t="n">
-        <v>57320</v>
+        <v>79624</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4679,21 +4689,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4703,10 +4713,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>477472</v>
+        <v>477437</v>
       </c>
       <c r="R40" t="n">
-        <v>7069006</v>
+        <v>7068991</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4739,11 +4749,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4770,7 +4775,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120040159</v>
+        <v>120040139</v>
       </c>
       <c r="B41" t="n">
         <v>57320</v>
@@ -4810,10 +4815,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>477444</v>
+        <v>477517</v>
       </c>
       <c r="R41" t="n">
-        <v>7068963</v>
+        <v>7068992</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4850,7 +4855,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack ganska färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4877,7 +4882,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120040173</v>
+        <v>120040158</v>
       </c>
       <c r="B42" t="n">
         <v>57320</v>
@@ -4917,10 +4922,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>477786</v>
+        <v>477446</v>
       </c>
       <c r="R42" t="n">
-        <v>7069029</v>
+        <v>7069039</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4957,7 +4962,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4984,10 +4989,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120040174</v>
+        <v>120040207</v>
       </c>
       <c r="B43" t="n">
-        <v>57320</v>
+        <v>86895</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5000,21 +5005,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5024,10 +5029,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>477825</v>
+        <v>477473</v>
       </c>
       <c r="R43" t="n">
-        <v>7069031</v>
+        <v>7069007</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5060,11 +5065,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5091,10 +5091,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120040135</v>
+        <v>120040200</v>
       </c>
       <c r="B44" t="n">
-        <v>90580</v>
+        <v>90598</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5107,21 +5107,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5131,10 +5131,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>477507</v>
+        <v>477439</v>
       </c>
       <c r="R44" t="n">
-        <v>7069055</v>
+        <v>7069086</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5193,10 +5193,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120040182</v>
+        <v>120040176</v>
       </c>
       <c r="B45" t="n">
-        <v>57431</v>
+        <v>57320</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5205,20 +5205,20 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5226,29 +5226,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>477760</v>
+        <v>477852</v>
       </c>
       <c r="R45" t="n">
-        <v>7069037</v>
+        <v>7069022</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5281,6 +5269,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack ganska färska till äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5307,10 +5300,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120040187</v>
+        <v>120040175</v>
       </c>
       <c r="B46" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5319,38 +5312,58 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>477525</v>
+        <v>477822</v>
       </c>
       <c r="R46" t="n">
-        <v>7069106</v>
+        <v>7069037</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5409,10 +5422,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120040207</v>
+        <v>120040161</v>
       </c>
       <c r="B47" t="n">
-        <v>86895</v>
+        <v>57320</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5425,21 +5438,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5449,10 +5462,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>477473</v>
+        <v>477426</v>
       </c>
       <c r="R47" t="n">
-        <v>7069007</v>
+        <v>7068947</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5485,6 +5498,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5511,7 +5529,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120040146</v>
+        <v>120040144</v>
       </c>
       <c r="B48" t="n">
         <v>57320</v>
@@ -5551,10 +5569,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>477599</v>
+        <v>477644</v>
       </c>
       <c r="R48" t="n">
-        <v>7069105</v>
+        <v>7069114</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5618,10 +5636,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120040142</v>
+        <v>120040191</v>
       </c>
       <c r="B49" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5630,25 +5648,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5658,10 +5676,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>477614</v>
+        <v>477440</v>
       </c>
       <c r="R49" t="n">
-        <v>7069089</v>
+        <v>7069251</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5694,11 +5712,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5725,7 +5738,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120040165</v>
+        <v>120040145</v>
       </c>
       <c r="B50" t="n">
         <v>57320</v>
@@ -5765,10 +5778,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>477596</v>
+        <v>477626</v>
       </c>
       <c r="R50" t="n">
-        <v>7068950</v>
+        <v>7069105</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5805,7 +5818,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5832,7 +5845,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120040166</v>
+        <v>120040174</v>
       </c>
       <c r="B51" t="n">
         <v>57320</v>
@@ -5872,10 +5885,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>477622</v>
+        <v>477825</v>
       </c>
       <c r="R51" t="n">
-        <v>7068965</v>
+        <v>7069031</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5912,7 +5925,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5939,7 +5952,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120040163</v>
+        <v>120040164</v>
       </c>
       <c r="B52" t="n">
         <v>57320</v>
@@ -5979,10 +5992,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>477544</v>
+        <v>477597</v>
       </c>
       <c r="R52" t="n">
-        <v>7068952</v>
+        <v>7068964</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6046,10 +6059,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120040141</v>
+        <v>120040189</v>
       </c>
       <c r="B53" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6058,25 +6071,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6086,10 +6099,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>477562</v>
+        <v>477498</v>
       </c>
       <c r="R53" t="n">
-        <v>7069078</v>
+        <v>7069206</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6122,11 +6135,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6153,7 +6161,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120040172</v>
+        <v>120040167</v>
       </c>
       <c r="B54" t="n">
         <v>57320</v>
@@ -6193,10 +6201,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>477777</v>
+        <v>477641</v>
       </c>
       <c r="R54" t="n">
-        <v>7069022</v>
+        <v>7068958</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6233,7 +6241,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack ganska färska</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6260,7 +6268,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120040167</v>
+        <v>120040165</v>
       </c>
       <c r="B55" t="n">
         <v>57320</v>
@@ -6300,10 +6308,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>477641</v>
+        <v>477596</v>
       </c>
       <c r="R55" t="n">
-        <v>7068958</v>
+        <v>7068950</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6340,7 +6348,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ringhack ganska färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6367,10 +6375,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120040192</v>
+        <v>120040146</v>
       </c>
       <c r="B56" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6379,25 +6387,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6407,10 +6415,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>477445</v>
+        <v>477599</v>
       </c>
       <c r="R56" t="n">
-        <v>7068977</v>
+        <v>7069105</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6443,6 +6451,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6469,10 +6482,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120040164</v>
+        <v>120040134</v>
       </c>
       <c r="B57" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6485,21 +6498,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6509,10 +6522,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>477597</v>
+        <v>477522</v>
       </c>
       <c r="R57" t="n">
-        <v>7068964</v>
+        <v>7068987</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6545,11 +6558,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6576,7 +6584,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120040175</v>
+        <v>120040177</v>
       </c>
       <c r="B58" t="n">
         <v>57320</v>
@@ -6609,37 +6617,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>477822</v>
+        <v>477856</v>
       </c>
       <c r="R58" t="n">
-        <v>7069037</v>
+        <v>7069020</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6672,6 +6660,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6698,7 +6691,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120040149</v>
+        <v>120040150</v>
       </c>
       <c r="B59" t="n">
         <v>57320</v>
@@ -6738,10 +6731,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>477423</v>
+        <v>477457</v>
       </c>
       <c r="R59" t="n">
-        <v>7069180</v>
+        <v>7069186</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6805,10 +6798,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120040134</v>
+        <v>120040169</v>
       </c>
       <c r="B60" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6821,21 +6814,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6845,10 +6838,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>477522</v>
+        <v>477688</v>
       </c>
       <c r="R60" t="n">
-        <v>7068987</v>
+        <v>7069010</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6881,6 +6874,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6907,7 +6905,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120040176</v>
+        <v>120040152</v>
       </c>
       <c r="B61" t="n">
         <v>57320</v>
@@ -6947,10 +6945,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>477852</v>
+        <v>477472</v>
       </c>
       <c r="R61" t="n">
-        <v>7069022</v>
+        <v>7069168</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6987,7 +6985,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Ringhack ganska färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7014,10 +7012,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120040151</v>
+        <v>120040188</v>
       </c>
       <c r="B62" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7026,25 +7024,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7054,10 +7052,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>477460</v>
+        <v>477454</v>
       </c>
       <c r="R62" t="n">
-        <v>7069166</v>
+        <v>7069190</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7090,11 +7088,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Ringhack färska och något äldre</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7121,10 +7114,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120040190</v>
+        <v>120040204</v>
       </c>
       <c r="B63" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7133,25 +7126,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7161,10 +7154,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>477530</v>
+        <v>477534</v>
       </c>
       <c r="R63" t="n">
-        <v>7069276</v>
+        <v>7069288</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7223,10 +7216,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120040170</v>
+        <v>120040183</v>
       </c>
       <c r="B64" t="n">
-        <v>57320</v>
+        <v>57431</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7235,20 +7228,20 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -7256,17 +7249,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>477755</v>
+        <v>477821</v>
       </c>
       <c r="R64" t="n">
-        <v>7069016</v>
+        <v>7069026</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7299,11 +7304,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD64" t="b">

--- a/artfynd/A 36309-2024 artfynd.xlsx
+++ b/artfynd/A 36309-2024 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120040170</v>
+        <v>120040201</v>
       </c>
       <c r="B3" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477755</v>
+        <v>477484</v>
       </c>
       <c r="R3" t="n">
-        <v>7069016</v>
+        <v>7068927</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120040201</v>
+        <v>120040182</v>
       </c>
       <c r="B4" t="n">
-        <v>90598</v>
+        <v>57431</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,38 +896,50 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>103031</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477484</v>
+        <v>477760</v>
       </c>
       <c r="R4" t="n">
-        <v>7068927</v>
+        <v>7069037</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1098,10 +1105,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120040182</v>
+        <v>120040170</v>
       </c>
       <c r="B6" t="n">
-        <v>57431</v>
+        <v>57320</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1110,20 +1117,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1131,29 +1138,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477760</v>
+        <v>477755</v>
       </c>
       <c r="R6" t="n">
-        <v>7069037</v>
+        <v>7069016</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1186,6 +1181,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -2267,10 +2267,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120040157</v>
+        <v>120040135</v>
       </c>
       <c r="B17" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2283,21 +2283,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2307,10 +2307,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>477397</v>
+        <v>477507</v>
       </c>
       <c r="R17" t="n">
-        <v>7069068</v>
+        <v>7069055</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2343,11 +2343,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2374,10 +2369,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120040135</v>
+        <v>120040157</v>
       </c>
       <c r="B18" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2390,21 +2385,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2414,10 +2409,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>477507</v>
+        <v>477397</v>
       </c>
       <c r="R18" t="n">
-        <v>7069055</v>
+        <v>7069068</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2450,6 +2445,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3521,7 +3521,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120040140</v>
+        <v>120040142</v>
       </c>
       <c r="B29" t="n">
         <v>57320</v>
@@ -3561,10 +3561,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>477472</v>
+        <v>477614</v>
       </c>
       <c r="R29" t="n">
-        <v>7069006</v>
+        <v>7069089</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3628,10 +3628,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120040185</v>
+        <v>120040140</v>
       </c>
       <c r="B30" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3640,25 +3640,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3668,10 +3668,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>477507</v>
+        <v>477472</v>
       </c>
       <c r="R30" t="n">
-        <v>7069056</v>
+        <v>7069006</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3704,6 +3704,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3730,7 +3735,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120040190</v>
+        <v>120040185</v>
       </c>
       <c r="B31" t="n">
         <v>97930</v>
@@ -3770,10 +3775,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>477530</v>
+        <v>477507</v>
       </c>
       <c r="R31" t="n">
-        <v>7069276</v>
+        <v>7069056</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3832,10 +3837,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120040142</v>
+        <v>120040190</v>
       </c>
       <c r="B32" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3844,25 +3849,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3872,10 +3877,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>477614</v>
+        <v>477530</v>
       </c>
       <c r="R32" t="n">
-        <v>7069089</v>
+        <v>7069276</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3908,11 +3913,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3939,10 +3939,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120040136</v>
+        <v>120040173</v>
       </c>
       <c r="B33" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3955,21 +3955,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3979,10 +3979,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>477434</v>
+        <v>477786</v>
       </c>
       <c r="R33" t="n">
-        <v>7069116</v>
+        <v>7069029</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4015,6 +4015,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4041,10 +4046,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120040202</v>
+        <v>120040153</v>
       </c>
       <c r="B34" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4057,21 +4062,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4081,10 +4086,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>477674</v>
+        <v>477547</v>
       </c>
       <c r="R34" t="n">
-        <v>7069000</v>
+        <v>7069271</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4117,6 +4122,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4250,10 +4260,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120040173</v>
+        <v>120040136</v>
       </c>
       <c r="B36" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4266,21 +4276,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4290,10 +4300,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>477786</v>
+        <v>477434</v>
       </c>
       <c r="R36" t="n">
-        <v>7069029</v>
+        <v>7069116</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4326,11 +4336,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4357,10 +4362,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120040153</v>
+        <v>120040202</v>
       </c>
       <c r="B37" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4373,21 +4378,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4397,10 +4402,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>477547</v>
+        <v>477674</v>
       </c>
       <c r="R37" t="n">
-        <v>7069271</v>
+        <v>7069000</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4433,11 +4438,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4464,10 +4464,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120040205</v>
+        <v>120040149</v>
       </c>
       <c r="B38" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4480,21 +4480,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4504,10 +4504,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>477382</v>
+        <v>477423</v>
       </c>
       <c r="R38" t="n">
-        <v>7069247</v>
+        <v>7069180</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4540,6 +4540,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4566,10 +4571,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120040149</v>
+        <v>120040205</v>
       </c>
       <c r="B39" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4582,21 +4587,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4606,10 +4611,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>477423</v>
+        <v>477382</v>
       </c>
       <c r="R39" t="n">
-        <v>7069180</v>
+        <v>7069247</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4642,11 +4647,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">

--- a/artfynd/A 36309-2024 artfynd.xlsx
+++ b/artfynd/A 36309-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120040154</v>
+        <v>120040140</v>
       </c>
       <c r="B2" t="n">
         <v>57320</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477476</v>
+        <v>477472</v>
       </c>
       <c r="R2" t="n">
-        <v>7069264</v>
+        <v>7069006</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120040201</v>
+        <v>120040138</v>
       </c>
       <c r="B3" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477484</v>
+        <v>477726</v>
       </c>
       <c r="R3" t="n">
-        <v>7068927</v>
+        <v>7069062</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,6 +858,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120040182</v>
+        <v>120040190</v>
       </c>
       <c r="B4" t="n">
-        <v>57431</v>
+        <v>97930</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,50 +901,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103031</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477760</v>
+        <v>477530</v>
       </c>
       <c r="R4" t="n">
-        <v>7069037</v>
+        <v>7069276</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120040163</v>
+        <v>120040150</v>
       </c>
       <c r="B5" t="n">
         <v>57320</v>
@@ -1038,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477544</v>
+        <v>477457</v>
       </c>
       <c r="R5" t="n">
-        <v>7068952</v>
+        <v>7069186</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1078,7 +1071,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1105,7 +1098,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120040170</v>
+        <v>120040171</v>
       </c>
       <c r="B6" t="n">
         <v>57320</v>
@@ -1145,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477755</v>
+        <v>477759</v>
       </c>
       <c r="R6" t="n">
-        <v>7069016</v>
+        <v>7069019</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120040159</v>
+        <v>120040181</v>
       </c>
       <c r="B7" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1228,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1252,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477444</v>
+        <v>477437</v>
       </c>
       <c r="R7" t="n">
-        <v>7068963</v>
+        <v>7068991</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1288,11 +1281,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack ganska färska till äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1319,7 +1307,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120040155</v>
+        <v>120040139</v>
       </c>
       <c r="B8" t="n">
         <v>57320</v>
@@ -1359,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477377</v>
+        <v>477517</v>
       </c>
       <c r="R8" t="n">
-        <v>7069208</v>
+        <v>7068992</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1426,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120040180</v>
+        <v>120040176</v>
       </c>
       <c r="B9" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1442,21 +1430,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1466,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>477415</v>
+        <v>477852</v>
       </c>
       <c r="R9" t="n">
-        <v>7069070</v>
+        <v>7069022</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1502,6 +1490,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack ganska färska till äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1528,7 +1521,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120040166</v>
+        <v>120040170</v>
       </c>
       <c r="B10" t="n">
         <v>57320</v>
@@ -1568,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>477622</v>
+        <v>477755</v>
       </c>
       <c r="R10" t="n">
-        <v>7068965</v>
+        <v>7069016</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1608,7 +1601,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1635,7 +1628,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120040162</v>
+        <v>120040168</v>
       </c>
       <c r="B11" t="n">
         <v>57320</v>
@@ -1675,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>477471</v>
+        <v>477664</v>
       </c>
       <c r="R11" t="n">
-        <v>7068928</v>
+        <v>7068971</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1715,7 +1708,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1742,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120040171</v>
+        <v>120040204</v>
       </c>
       <c r="B12" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1758,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1782,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>477759</v>
+        <v>477534</v>
       </c>
       <c r="R12" t="n">
-        <v>7069019</v>
+        <v>7069288</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1818,11 +1811,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1849,10 +1837,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120040203</v>
+        <v>120040146</v>
       </c>
       <c r="B13" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1865,21 +1853,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1889,10 +1877,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>477472</v>
+        <v>477599</v>
       </c>
       <c r="R13" t="n">
-        <v>7069087</v>
+        <v>7069105</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1925,6 +1913,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1951,10 +1944,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120040181</v>
+        <v>120040167</v>
       </c>
       <c r="B14" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1967,21 +1960,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1991,10 +1984,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>477437</v>
+        <v>477641</v>
       </c>
       <c r="R14" t="n">
-        <v>7068991</v>
+        <v>7068958</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2027,6 +2020,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack ganska färska</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2053,10 +2051,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120040138</v>
+        <v>120040135</v>
       </c>
       <c r="B15" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2069,21 +2067,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2093,10 +2091,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>477726</v>
+        <v>477507</v>
       </c>
       <c r="R15" t="n">
-        <v>7069062</v>
+        <v>7069055</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2129,11 +2127,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2160,10 +2153,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120040168</v>
+        <v>120040185</v>
       </c>
       <c r="B16" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2172,25 +2165,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2200,10 +2193,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>477664</v>
+        <v>477507</v>
       </c>
       <c r="R16" t="n">
-        <v>7068971</v>
+        <v>7069056</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2236,11 +2229,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2267,10 +2255,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120040135</v>
+        <v>120040203</v>
       </c>
       <c r="B17" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2283,21 +2271,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2307,10 +2295,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>477507</v>
+        <v>477472</v>
       </c>
       <c r="R17" t="n">
-        <v>7069055</v>
+        <v>7069087</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2369,7 +2357,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120040157</v>
+        <v>120040166</v>
       </c>
       <c r="B18" t="n">
         <v>57320</v>
@@ -2409,10 +2397,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>477397</v>
+        <v>477622</v>
       </c>
       <c r="R18" t="n">
-        <v>7069068</v>
+        <v>7068965</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2476,10 +2464,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120040184</v>
+        <v>120040207</v>
       </c>
       <c r="B19" t="n">
-        <v>97930</v>
+        <v>86895</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2488,25 +2476,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>510</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2516,10 +2504,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>477481</v>
+        <v>477473</v>
       </c>
       <c r="R19" t="n">
-        <v>7069004</v>
+        <v>7069007</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2578,10 +2566,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120040199</v>
+        <v>120040182</v>
       </c>
       <c r="B20" t="n">
-        <v>90576</v>
+        <v>57431</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2590,38 +2578,50 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>103031</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>477671</v>
+        <v>477760</v>
       </c>
       <c r="R20" t="n">
-        <v>7068973</v>
+        <v>7069037</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2680,10 +2680,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120040147</v>
+        <v>120040199</v>
       </c>
       <c r="B21" t="n">
-        <v>57320</v>
+        <v>90576</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2696,21 +2696,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2720,10 +2720,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>477581</v>
+        <v>477671</v>
       </c>
       <c r="R21" t="n">
-        <v>7069095</v>
+        <v>7068973</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2756,11 +2756,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2787,10 +2782,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120040206</v>
+        <v>120040200</v>
       </c>
       <c r="B22" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2803,21 +2798,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2827,10 +2822,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>477405</v>
+        <v>477439</v>
       </c>
       <c r="R22" t="n">
-        <v>7069105</v>
+        <v>7069086</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2889,10 +2884,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120040172</v>
+        <v>120040183</v>
       </c>
       <c r="B23" t="n">
-        <v>57320</v>
+        <v>57431</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2901,20 +2896,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2922,17 +2917,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>477777</v>
+        <v>477821</v>
       </c>
       <c r="R23" t="n">
-        <v>7069022</v>
+        <v>7069026</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2965,11 +2972,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2996,10 +2998,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120040141</v>
+        <v>120040206</v>
       </c>
       <c r="B24" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3012,21 +3014,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3036,10 +3038,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>477562</v>
+        <v>477405</v>
       </c>
       <c r="R24" t="n">
-        <v>7069078</v>
+        <v>7069105</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3072,11 +3074,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3103,10 +3100,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120040187</v>
+        <v>120040155</v>
       </c>
       <c r="B25" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3115,25 +3112,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3143,10 +3140,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>477525</v>
+        <v>477377</v>
       </c>
       <c r="R25" t="n">
-        <v>7069106</v>
+        <v>7069208</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3179,6 +3176,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3205,10 +3207,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120040192</v>
+        <v>120040142</v>
       </c>
       <c r="B26" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3217,25 +3219,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3245,10 +3247,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>477445</v>
+        <v>477614</v>
       </c>
       <c r="R26" t="n">
-        <v>7068977</v>
+        <v>7069089</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3281,6 +3283,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3307,10 +3314,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120040151</v>
+        <v>120040202</v>
       </c>
       <c r="B27" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3323,21 +3330,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3347,10 +3354,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>477460</v>
+        <v>477674</v>
       </c>
       <c r="R27" t="n">
-        <v>7069166</v>
+        <v>7069000</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3383,11 +3390,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack färska och något äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3414,10 +3416,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120040148</v>
+        <v>120040201</v>
       </c>
       <c r="B28" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3430,21 +3432,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3454,10 +3456,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>477438</v>
+        <v>477484</v>
       </c>
       <c r="R28" t="n">
-        <v>7069178</v>
+        <v>7068927</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3490,11 +3492,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3521,7 +3518,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120040142</v>
+        <v>120040154</v>
       </c>
       <c r="B29" t="n">
         <v>57320</v>
@@ -3561,10 +3558,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>477614</v>
+        <v>477476</v>
       </c>
       <c r="R29" t="n">
-        <v>7069089</v>
+        <v>7069264</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3628,10 +3625,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120040140</v>
+        <v>120040191</v>
       </c>
       <c r="B30" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3640,25 +3637,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3668,10 +3665,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>477472</v>
+        <v>477440</v>
       </c>
       <c r="R30" t="n">
-        <v>7069006</v>
+        <v>7069251</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3704,11 +3701,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3735,10 +3727,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120040185</v>
+        <v>120040172</v>
       </c>
       <c r="B31" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3747,25 +3739,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3775,10 +3767,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>477507</v>
+        <v>477777</v>
       </c>
       <c r="R31" t="n">
-        <v>7069056</v>
+        <v>7069022</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3811,6 +3803,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3837,10 +3834,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120040190</v>
+        <v>120040160</v>
       </c>
       <c r="B32" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3849,25 +3846,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3877,10 +3874,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>477530</v>
+        <v>477440</v>
       </c>
       <c r="R32" t="n">
-        <v>7069276</v>
+        <v>7068958</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3913,6 +3910,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3939,7 +3941,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120040173</v>
+        <v>120040149</v>
       </c>
       <c r="B33" t="n">
         <v>57320</v>
@@ -3979,10 +3981,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>477786</v>
+        <v>477423</v>
       </c>
       <c r="R33" t="n">
-        <v>7069029</v>
+        <v>7069180</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4046,7 +4048,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120040153</v>
+        <v>120040151</v>
       </c>
       <c r="B34" t="n">
         <v>57320</v>
@@ -4086,10 +4088,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>477547</v>
+        <v>477460</v>
       </c>
       <c r="R34" t="n">
-        <v>7069271</v>
+        <v>7069166</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4126,7 +4128,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och något äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4153,7 +4155,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120040160</v>
+        <v>120040147</v>
       </c>
       <c r="B35" t="n">
         <v>57320</v>
@@ -4193,10 +4195,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>477440</v>
+        <v>477581</v>
       </c>
       <c r="R35" t="n">
-        <v>7068958</v>
+        <v>7069095</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4260,10 +4262,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120040136</v>
+        <v>120040148</v>
       </c>
       <c r="B36" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4276,21 +4278,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4300,10 +4302,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>477434</v>
+        <v>477438</v>
       </c>
       <c r="R36" t="n">
-        <v>7069116</v>
+        <v>7069178</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4336,6 +4338,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4362,10 +4369,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120040202</v>
+        <v>120040134</v>
       </c>
       <c r="B37" t="n">
-        <v>90598</v>
+        <v>90580</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4378,21 +4385,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4402,10 +4409,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>477674</v>
+        <v>477522</v>
       </c>
       <c r="R37" t="n">
-        <v>7069000</v>
+        <v>7068987</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4464,7 +4471,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120040149</v>
+        <v>120040165</v>
       </c>
       <c r="B38" t="n">
         <v>57320</v>
@@ -4504,10 +4511,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>477423</v>
+        <v>477596</v>
       </c>
       <c r="R38" t="n">
-        <v>7069180</v>
+        <v>7068950</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4544,7 +4551,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4571,10 +4578,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120040205</v>
+        <v>120040159</v>
       </c>
       <c r="B39" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4587,21 +4594,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4611,10 +4618,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>477382</v>
+        <v>477444</v>
       </c>
       <c r="R39" t="n">
-        <v>7069247</v>
+        <v>7068963</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4647,6 +4654,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack ganska färska till äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4673,10 +4685,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120040179</v>
+        <v>120040169</v>
       </c>
       <c r="B40" t="n">
-        <v>79624</v>
+        <v>57320</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4689,21 +4701,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4713,10 +4725,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>477437</v>
+        <v>477688</v>
       </c>
       <c r="R40" t="n">
-        <v>7068991</v>
+        <v>7069010</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4749,6 +4761,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4775,7 +4792,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120040139</v>
+        <v>120040173</v>
       </c>
       <c r="B41" t="n">
         <v>57320</v>
@@ -4815,10 +4832,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>477517</v>
+        <v>477786</v>
       </c>
       <c r="R41" t="n">
-        <v>7068992</v>
+        <v>7069029</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4989,10 +5006,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120040207</v>
+        <v>120040187</v>
       </c>
       <c r="B43" t="n">
-        <v>86895</v>
+        <v>97930</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5001,25 +5018,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>510</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5029,10 +5046,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>477473</v>
+        <v>477525</v>
       </c>
       <c r="R43" t="n">
-        <v>7069007</v>
+        <v>7069106</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5091,10 +5108,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120040200</v>
+        <v>120040189</v>
       </c>
       <c r="B44" t="n">
-        <v>90598</v>
+        <v>97930</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5103,25 +5120,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5131,10 +5148,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>477439</v>
+        <v>477498</v>
       </c>
       <c r="R44" t="n">
-        <v>7069086</v>
+        <v>7069206</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5193,10 +5210,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120040176</v>
+        <v>120040179</v>
       </c>
       <c r="B45" t="n">
-        <v>57320</v>
+        <v>79624</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5209,21 +5226,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5233,10 +5250,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>477852</v>
+        <v>477437</v>
       </c>
       <c r="R45" t="n">
-        <v>7069022</v>
+        <v>7068991</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5269,11 +5286,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack ganska färska till äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5300,10 +5312,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120040175</v>
+        <v>120040180</v>
       </c>
       <c r="B46" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5316,54 +5328,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>477822</v>
+        <v>477415</v>
       </c>
       <c r="R46" t="n">
-        <v>7069037</v>
+        <v>7069070</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5422,7 +5414,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120040161</v>
+        <v>120040177</v>
       </c>
       <c r="B47" t="n">
         <v>57320</v>
@@ -5462,10 +5454,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>477426</v>
+        <v>477856</v>
       </c>
       <c r="R47" t="n">
-        <v>7068947</v>
+        <v>7069020</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5502,7 +5494,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5529,7 +5521,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120040144</v>
+        <v>120040153</v>
       </c>
       <c r="B48" t="n">
         <v>57320</v>
@@ -5569,10 +5561,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>477644</v>
+        <v>477547</v>
       </c>
       <c r="R48" t="n">
-        <v>7069114</v>
+        <v>7069271</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5636,10 +5628,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120040191</v>
+        <v>120040145</v>
       </c>
       <c r="B49" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5648,25 +5640,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5676,10 +5668,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>477440</v>
+        <v>477626</v>
       </c>
       <c r="R49" t="n">
-        <v>7069251</v>
+        <v>7069105</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5712,6 +5704,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5738,7 +5735,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120040145</v>
+        <v>120040157</v>
       </c>
       <c r="B50" t="n">
         <v>57320</v>
@@ -5778,10 +5775,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>477626</v>
+        <v>477397</v>
       </c>
       <c r="R50" t="n">
-        <v>7069105</v>
+        <v>7069068</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5818,7 +5815,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5845,7 +5842,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120040174</v>
+        <v>120040141</v>
       </c>
       <c r="B51" t="n">
         <v>57320</v>
@@ -5885,10 +5882,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>477825</v>
+        <v>477562</v>
       </c>
       <c r="R51" t="n">
-        <v>7069031</v>
+        <v>7069078</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5952,7 +5949,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120040164</v>
+        <v>120040162</v>
       </c>
       <c r="B52" t="n">
         <v>57320</v>
@@ -5992,10 +5989,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>477597</v>
+        <v>477471</v>
       </c>
       <c r="R52" t="n">
-        <v>7068964</v>
+        <v>7068928</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6032,7 +6029,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6059,10 +6056,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120040189</v>
+        <v>120040163</v>
       </c>
       <c r="B53" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6071,25 +6068,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6099,10 +6096,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>477498</v>
+        <v>477544</v>
       </c>
       <c r="R53" t="n">
-        <v>7069206</v>
+        <v>7068952</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6135,6 +6132,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6161,10 +6163,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120040167</v>
+        <v>120040188</v>
       </c>
       <c r="B54" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6173,25 +6175,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6201,10 +6203,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>477641</v>
+        <v>477454</v>
       </c>
       <c r="R54" t="n">
-        <v>7068958</v>
+        <v>7069190</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6237,11 +6239,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack ganska färska</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6268,10 +6265,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120040165</v>
+        <v>120040205</v>
       </c>
       <c r="B55" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6284,21 +6281,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6308,10 +6305,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>477596</v>
+        <v>477382</v>
       </c>
       <c r="R55" t="n">
-        <v>7068950</v>
+        <v>7069247</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6344,11 +6341,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6375,7 +6367,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120040146</v>
+        <v>120040164</v>
       </c>
       <c r="B56" t="n">
         <v>57320</v>
@@ -6415,10 +6407,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>477599</v>
+        <v>477597</v>
       </c>
       <c r="R56" t="n">
-        <v>7069105</v>
+        <v>7068964</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6455,7 +6447,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6482,10 +6474,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120040134</v>
+        <v>120040152</v>
       </c>
       <c r="B57" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6498,21 +6490,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6522,10 +6514,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>477522</v>
+        <v>477472</v>
       </c>
       <c r="R57" t="n">
-        <v>7068987</v>
+        <v>7069168</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6558,6 +6550,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6584,7 +6581,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120040177</v>
+        <v>120040144</v>
       </c>
       <c r="B58" t="n">
         <v>57320</v>
@@ -6624,10 +6621,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>477856</v>
+        <v>477644</v>
       </c>
       <c r="R58" t="n">
-        <v>7069020</v>
+        <v>7069114</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6664,7 +6661,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6691,10 +6688,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120040150</v>
+        <v>120040192</v>
       </c>
       <c r="B59" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6703,25 +6700,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6731,10 +6728,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>477457</v>
+        <v>477445</v>
       </c>
       <c r="R59" t="n">
-        <v>7069186</v>
+        <v>7068977</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6767,11 +6764,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6798,10 +6790,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120040169</v>
+        <v>120040184</v>
       </c>
       <c r="B60" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6810,25 +6802,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6838,10 +6830,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>477688</v>
+        <v>477481</v>
       </c>
       <c r="R60" t="n">
-        <v>7069010</v>
+        <v>7069004</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6874,11 +6866,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6905,7 +6892,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120040152</v>
+        <v>120040175</v>
       </c>
       <c r="B61" t="n">
         <v>57320</v>
@@ -6938,17 +6925,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>477472</v>
+        <v>477822</v>
       </c>
       <c r="R61" t="n">
-        <v>7069168</v>
+        <v>7069037</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6981,11 +6988,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7012,10 +7014,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120040188</v>
+        <v>120040174</v>
       </c>
       <c r="B62" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7024,25 +7026,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7052,10 +7054,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>477454</v>
+        <v>477825</v>
       </c>
       <c r="R62" t="n">
-        <v>7069190</v>
+        <v>7069031</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7088,6 +7090,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7114,10 +7121,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120040204</v>
+        <v>120040161</v>
       </c>
       <c r="B63" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7130,21 +7137,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7154,10 +7161,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>477534</v>
+        <v>477426</v>
       </c>
       <c r="R63" t="n">
-        <v>7069288</v>
+        <v>7068947</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7190,6 +7197,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7216,10 +7228,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120040183</v>
+        <v>120040136</v>
       </c>
       <c r="B64" t="n">
-        <v>57431</v>
+        <v>90580</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7228,50 +7240,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>103031</v>
+        <v>1202</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>477821</v>
+        <v>477434</v>
       </c>
       <c r="R64" t="n">
-        <v>7069026</v>
+        <v>7069116</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>

--- a/artfynd/A 36309-2024 artfynd.xlsx
+++ b/artfynd/A 36309-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120040140</v>
+        <v>120040182</v>
       </c>
       <c r="B2" t="n">
-        <v>57320</v>
+        <v>57431</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,17 +708,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477472</v>
+        <v>477760</v>
       </c>
       <c r="R2" t="n">
-        <v>7069006</v>
+        <v>7069037</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +763,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120040138</v>
+        <v>120040188</v>
       </c>
       <c r="B3" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +801,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477726</v>
+        <v>477454</v>
       </c>
       <c r="R3" t="n">
-        <v>7069062</v>
+        <v>7069190</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +865,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120040190</v>
+        <v>120040168</v>
       </c>
       <c r="B4" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,25 +903,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477530</v>
+        <v>477664</v>
       </c>
       <c r="R4" t="n">
-        <v>7069276</v>
+        <v>7068971</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,6 +967,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120040150</v>
+        <v>120040205</v>
       </c>
       <c r="B5" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,21 +1014,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477457</v>
+        <v>477382</v>
       </c>
       <c r="R5" t="n">
-        <v>7069186</v>
+        <v>7069247</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,11 +1074,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,10 +1100,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120040171</v>
+        <v>120040184</v>
       </c>
       <c r="B6" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1110,25 +1112,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1140,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477759</v>
+        <v>477481</v>
       </c>
       <c r="R6" t="n">
-        <v>7069019</v>
+        <v>7069004</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1174,11 +1176,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1202,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120040181</v>
+        <v>120040185</v>
       </c>
       <c r="B7" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,25 +1214,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1242,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477437</v>
+        <v>477507</v>
       </c>
       <c r="R7" t="n">
-        <v>7068991</v>
+        <v>7069056</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1307,7 +1304,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120040139</v>
+        <v>120040138</v>
       </c>
       <c r="B8" t="n">
         <v>57320</v>
@@ -1347,10 +1344,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477517</v>
+        <v>477726</v>
       </c>
       <c r="R8" t="n">
-        <v>7068992</v>
+        <v>7069062</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1414,7 +1411,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120040176</v>
+        <v>120040172</v>
       </c>
       <c r="B9" t="n">
         <v>57320</v>
@@ -1454,7 +1451,7 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>477852</v>
+        <v>477777</v>
       </c>
       <c r="R9" t="n">
         <v>7069022</v>
@@ -1494,7 +1491,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack ganska färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,7 +1518,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120040170</v>
+        <v>120040142</v>
       </c>
       <c r="B10" t="n">
         <v>57320</v>
@@ -1561,10 +1558,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>477755</v>
+        <v>477614</v>
       </c>
       <c r="R10" t="n">
-        <v>7069016</v>
+        <v>7069089</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1628,10 +1625,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120040168</v>
+        <v>120040187</v>
       </c>
       <c r="B11" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1640,25 +1637,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1668,10 +1665,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>477664</v>
+        <v>477525</v>
       </c>
       <c r="R11" t="n">
-        <v>7068971</v>
+        <v>7069106</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1704,11 +1701,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,10 +1727,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120040204</v>
+        <v>120040159</v>
       </c>
       <c r="B12" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,21 +1743,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1767,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>477534</v>
+        <v>477444</v>
       </c>
       <c r="R12" t="n">
-        <v>7069288</v>
+        <v>7068963</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1811,6 +1803,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack ganska färska till äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1837,7 +1834,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120040146</v>
+        <v>120040157</v>
       </c>
       <c r="B13" t="n">
         <v>57320</v>
@@ -1877,10 +1874,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>477599</v>
+        <v>477397</v>
       </c>
       <c r="R13" t="n">
-        <v>7069105</v>
+        <v>7069068</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1917,7 +1914,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1944,7 +1941,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120040167</v>
+        <v>120040145</v>
       </c>
       <c r="B14" t="n">
         <v>57320</v>
@@ -1984,10 +1981,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>477641</v>
+        <v>477626</v>
       </c>
       <c r="R14" t="n">
-        <v>7068958</v>
+        <v>7069105</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2024,7 +2021,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack ganska färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2153,10 +2150,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120040185</v>
+        <v>120040152</v>
       </c>
       <c r="B16" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2165,25 +2162,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2193,10 +2190,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>477507</v>
+        <v>477472</v>
       </c>
       <c r="R16" t="n">
-        <v>7069056</v>
+        <v>7069168</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2229,6 +2226,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2255,10 +2257,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120040203</v>
+        <v>120040154</v>
       </c>
       <c r="B17" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2271,21 +2273,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2295,10 +2297,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>477472</v>
+        <v>477476</v>
       </c>
       <c r="R17" t="n">
-        <v>7069087</v>
+        <v>7069264</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2331,6 +2333,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2357,7 +2364,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120040166</v>
+        <v>120040177</v>
       </c>
       <c r="B18" t="n">
         <v>57320</v>
@@ -2397,10 +2404,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>477622</v>
+        <v>477856</v>
       </c>
       <c r="R18" t="n">
-        <v>7068965</v>
+        <v>7069020</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2437,7 +2444,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2464,10 +2471,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120040207</v>
+        <v>120040153</v>
       </c>
       <c r="B19" t="n">
-        <v>86895</v>
+        <v>57320</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2480,21 +2487,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2504,10 +2511,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>477473</v>
+        <v>477547</v>
       </c>
       <c r="R19" t="n">
-        <v>7069007</v>
+        <v>7069271</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2540,6 +2547,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2566,10 +2578,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120040182</v>
+        <v>120040161</v>
       </c>
       <c r="B20" t="n">
-        <v>57431</v>
+        <v>57320</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2578,20 +2590,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2599,29 +2611,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>477760</v>
+        <v>477426</v>
       </c>
       <c r="R20" t="n">
-        <v>7069037</v>
+        <v>7068947</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2654,6 +2654,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2680,10 +2685,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120040199</v>
+        <v>120040201</v>
       </c>
       <c r="B21" t="n">
-        <v>90576</v>
+        <v>90598</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2696,21 +2701,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2720,10 +2725,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>477671</v>
+        <v>477484</v>
       </c>
       <c r="R21" t="n">
-        <v>7068973</v>
+        <v>7068927</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2782,10 +2787,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120040200</v>
+        <v>120040189</v>
       </c>
       <c r="B22" t="n">
-        <v>90598</v>
+        <v>97930</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2794,25 +2799,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2822,10 +2827,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>477439</v>
+        <v>477498</v>
       </c>
       <c r="R22" t="n">
-        <v>7069086</v>
+        <v>7069206</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2884,10 +2889,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120040183</v>
+        <v>120040155</v>
       </c>
       <c r="B23" t="n">
-        <v>57431</v>
+        <v>57320</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2896,20 +2901,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2917,29 +2922,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>477821</v>
+        <v>477377</v>
       </c>
       <c r="R23" t="n">
-        <v>7069026</v>
+        <v>7069208</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2972,6 +2965,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2998,10 +2996,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120040206</v>
+        <v>120040139</v>
       </c>
       <c r="B24" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3014,21 +3012,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3038,10 +3036,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>477405</v>
+        <v>477517</v>
       </c>
       <c r="R24" t="n">
-        <v>7069105</v>
+        <v>7068992</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3074,6 +3072,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3100,7 +3103,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120040155</v>
+        <v>120040166</v>
       </c>
       <c r="B25" t="n">
         <v>57320</v>
@@ -3140,10 +3143,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>477377</v>
+        <v>477622</v>
       </c>
       <c r="R25" t="n">
-        <v>7069208</v>
+        <v>7068965</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3180,7 +3183,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3207,10 +3210,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120040142</v>
+        <v>120040200</v>
       </c>
       <c r="B26" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3223,21 +3226,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3247,10 +3250,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>477614</v>
+        <v>477439</v>
       </c>
       <c r="R26" t="n">
-        <v>7069089</v>
+        <v>7069086</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3283,11 +3286,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3314,10 +3312,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120040202</v>
+        <v>120040180</v>
       </c>
       <c r="B27" t="n">
-        <v>90598</v>
+        <v>79623</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3330,21 +3328,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3354,10 +3352,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>477674</v>
+        <v>477415</v>
       </c>
       <c r="R27" t="n">
-        <v>7069000</v>
+        <v>7069070</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3416,10 +3414,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120040201</v>
+        <v>120040136</v>
       </c>
       <c r="B28" t="n">
-        <v>90598</v>
+        <v>90580</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3432,21 +3430,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3456,10 +3454,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>477484</v>
+        <v>477434</v>
       </c>
       <c r="R28" t="n">
-        <v>7068927</v>
+        <v>7069116</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3518,7 +3516,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120040154</v>
+        <v>120040164</v>
       </c>
       <c r="B29" t="n">
         <v>57320</v>
@@ -3558,10 +3556,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>477476</v>
+        <v>477597</v>
       </c>
       <c r="R29" t="n">
-        <v>7069264</v>
+        <v>7068964</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3598,7 +3596,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3625,10 +3623,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120040191</v>
+        <v>120040149</v>
       </c>
       <c r="B30" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3637,25 +3635,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3665,10 +3663,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>477440</v>
+        <v>477423</v>
       </c>
       <c r="R30" t="n">
-        <v>7069251</v>
+        <v>7069180</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3701,6 +3699,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3727,7 +3730,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120040172</v>
+        <v>120040175</v>
       </c>
       <c r="B31" t="n">
         <v>57320</v>
@@ -3760,17 +3763,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>477777</v>
+        <v>477822</v>
       </c>
       <c r="R31" t="n">
-        <v>7069022</v>
+        <v>7069037</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3803,11 +3826,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3834,7 +3852,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120040160</v>
+        <v>120040163</v>
       </c>
       <c r="B32" t="n">
         <v>57320</v>
@@ -3874,10 +3892,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>477440</v>
+        <v>477544</v>
       </c>
       <c r="R32" t="n">
-        <v>7068958</v>
+        <v>7068952</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3914,7 +3932,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3941,7 +3959,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120040149</v>
+        <v>120040158</v>
       </c>
       <c r="B33" t="n">
         <v>57320</v>
@@ -3981,10 +3999,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>477423</v>
+        <v>477446</v>
       </c>
       <c r="R33" t="n">
-        <v>7069180</v>
+        <v>7069039</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4021,7 +4039,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4048,10 +4066,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120040151</v>
+        <v>120040134</v>
       </c>
       <c r="B34" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4064,21 +4082,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4088,10 +4106,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>477460</v>
+        <v>477522</v>
       </c>
       <c r="R34" t="n">
-        <v>7069166</v>
+        <v>7068987</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4124,11 +4142,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack färska och något äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4155,7 +4168,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120040147</v>
+        <v>120040169</v>
       </c>
       <c r="B35" t="n">
         <v>57320</v>
@@ -4195,10 +4208,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>477581</v>
+        <v>477688</v>
       </c>
       <c r="R35" t="n">
-        <v>7069095</v>
+        <v>7069010</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4262,7 +4275,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120040148</v>
+        <v>120040170</v>
       </c>
       <c r="B36" t="n">
         <v>57320</v>
@@ -4302,10 +4315,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>477438</v>
+        <v>477755</v>
       </c>
       <c r="R36" t="n">
-        <v>7069178</v>
+        <v>7069016</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4369,10 +4382,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120040134</v>
+        <v>120040199</v>
       </c>
       <c r="B37" t="n">
-        <v>90580</v>
+        <v>90576</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4385,21 +4398,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4409,10 +4422,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>477522</v>
+        <v>477671</v>
       </c>
       <c r="R37" t="n">
-        <v>7068987</v>
+        <v>7068973</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4471,7 +4484,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120040165</v>
+        <v>120040146</v>
       </c>
       <c r="B38" t="n">
         <v>57320</v>
@@ -4511,10 +4524,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>477596</v>
+        <v>477599</v>
       </c>
       <c r="R38" t="n">
-        <v>7068950</v>
+        <v>7069105</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4551,7 +4564,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4578,7 +4591,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120040159</v>
+        <v>120040165</v>
       </c>
       <c r="B39" t="n">
         <v>57320</v>
@@ -4618,10 +4631,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>477444</v>
+        <v>477596</v>
       </c>
       <c r="R39" t="n">
-        <v>7068963</v>
+        <v>7068950</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4658,7 +4671,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack ganska färska till äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4685,7 +4698,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120040169</v>
+        <v>120040173</v>
       </c>
       <c r="B40" t="n">
         <v>57320</v>
@@ -4725,10 +4738,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>477688</v>
+        <v>477786</v>
       </c>
       <c r="R40" t="n">
-        <v>7069010</v>
+        <v>7069029</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4792,10 +4805,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120040173</v>
+        <v>120040202</v>
       </c>
       <c r="B41" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4808,21 +4821,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4832,10 +4845,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>477786</v>
+        <v>477674</v>
       </c>
       <c r="R41" t="n">
-        <v>7069029</v>
+        <v>7069000</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4868,11 +4881,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4899,10 +4907,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120040158</v>
+        <v>120040179</v>
       </c>
       <c r="B42" t="n">
-        <v>57320</v>
+        <v>79624</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4915,21 +4923,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4939,10 +4947,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>477446</v>
+        <v>477437</v>
       </c>
       <c r="R42" t="n">
-        <v>7069039</v>
+        <v>7068991</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4975,11 +4983,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5006,10 +5009,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120040187</v>
+        <v>120040167</v>
       </c>
       <c r="B43" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5018,25 +5021,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5046,10 +5049,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>477525</v>
+        <v>477641</v>
       </c>
       <c r="R43" t="n">
-        <v>7069106</v>
+        <v>7068958</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5082,6 +5085,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack ganska färska</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5108,10 +5116,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120040189</v>
+        <v>120040171</v>
       </c>
       <c r="B44" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5120,25 +5128,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5148,10 +5156,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>477498</v>
+        <v>477759</v>
       </c>
       <c r="R44" t="n">
-        <v>7069206</v>
+        <v>7069019</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5184,6 +5192,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5210,10 +5223,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120040179</v>
+        <v>120040151</v>
       </c>
       <c r="B45" t="n">
-        <v>79624</v>
+        <v>57320</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5226,21 +5239,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5250,10 +5263,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>477437</v>
+        <v>477460</v>
       </c>
       <c r="R45" t="n">
-        <v>7068991</v>
+        <v>7069166</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5286,6 +5299,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack färska och något äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5312,10 +5330,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120040180</v>
+        <v>120040162</v>
       </c>
       <c r="B46" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5328,21 +5346,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5352,10 +5370,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>477415</v>
+        <v>477471</v>
       </c>
       <c r="R46" t="n">
-        <v>7069070</v>
+        <v>7068928</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5388,6 +5406,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5414,10 +5437,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120040177</v>
+        <v>120040192</v>
       </c>
       <c r="B47" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5426,25 +5449,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5454,10 +5477,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>477856</v>
+        <v>477445</v>
       </c>
       <c r="R47" t="n">
-        <v>7069020</v>
+        <v>7068977</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5490,11 +5513,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5521,7 +5539,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120040153</v>
+        <v>120040150</v>
       </c>
       <c r="B48" t="n">
         <v>57320</v>
@@ -5561,10 +5579,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>477547</v>
+        <v>477457</v>
       </c>
       <c r="R48" t="n">
-        <v>7069271</v>
+        <v>7069186</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5628,7 +5646,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120040145</v>
+        <v>120040160</v>
       </c>
       <c r="B49" t="n">
         <v>57320</v>
@@ -5668,10 +5686,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>477626</v>
+        <v>477440</v>
       </c>
       <c r="R49" t="n">
-        <v>7069105</v>
+        <v>7068958</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5735,7 +5753,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120040157</v>
+        <v>120040174</v>
       </c>
       <c r="B50" t="n">
         <v>57320</v>
@@ -5775,10 +5793,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>477397</v>
+        <v>477825</v>
       </c>
       <c r="R50" t="n">
-        <v>7069068</v>
+        <v>7069031</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5815,7 +5833,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5842,7 +5860,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120040141</v>
+        <v>120040140</v>
       </c>
       <c r="B51" t="n">
         <v>57320</v>
@@ -5882,10 +5900,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>477562</v>
+        <v>477472</v>
       </c>
       <c r="R51" t="n">
-        <v>7069078</v>
+        <v>7069006</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5949,10 +5967,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120040162</v>
+        <v>120040181</v>
       </c>
       <c r="B52" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5965,21 +5983,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5989,10 +6007,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>477471</v>
+        <v>477437</v>
       </c>
       <c r="R52" t="n">
-        <v>7068928</v>
+        <v>7068991</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6025,11 +6043,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6056,10 +6069,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120040163</v>
+        <v>120040191</v>
       </c>
       <c r="B53" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6068,25 +6081,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6096,10 +6109,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>477544</v>
+        <v>477440</v>
       </c>
       <c r="R53" t="n">
-        <v>7068952</v>
+        <v>7069251</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6132,11 +6145,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6163,10 +6171,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120040188</v>
+        <v>120040206</v>
       </c>
       <c r="B54" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6175,25 +6183,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6203,10 +6211,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>477454</v>
+        <v>477405</v>
       </c>
       <c r="R54" t="n">
-        <v>7069190</v>
+        <v>7069105</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6265,10 +6273,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120040205</v>
+        <v>120040141</v>
       </c>
       <c r="B55" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6281,21 +6289,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6305,10 +6313,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>477382</v>
+        <v>477562</v>
       </c>
       <c r="R55" t="n">
-        <v>7069247</v>
+        <v>7069078</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6341,6 +6349,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6367,10 +6380,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120040164</v>
+        <v>120040183</v>
       </c>
       <c r="B56" t="n">
-        <v>57320</v>
+        <v>57431</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6379,20 +6392,20 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -6400,17 +6413,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>477597</v>
+        <v>477821</v>
       </c>
       <c r="R56" t="n">
-        <v>7068964</v>
+        <v>7069026</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6443,11 +6468,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6474,10 +6494,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120040152</v>
+        <v>120040203</v>
       </c>
       <c r="B57" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6490,21 +6510,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6517,7 +6537,7 @@
         <v>477472</v>
       </c>
       <c r="R57" t="n">
-        <v>7069168</v>
+        <v>7069087</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6550,11 +6570,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6581,7 +6596,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120040144</v>
+        <v>120040176</v>
       </c>
       <c r="B58" t="n">
         <v>57320</v>
@@ -6621,10 +6636,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>477644</v>
+        <v>477852</v>
       </c>
       <c r="R58" t="n">
-        <v>7069114</v>
+        <v>7069022</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6661,7 +6676,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack ganska färska till äldre</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6688,10 +6703,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120040192</v>
+        <v>120040144</v>
       </c>
       <c r="B59" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6700,25 +6715,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6728,10 +6743,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>477445</v>
+        <v>477644</v>
       </c>
       <c r="R59" t="n">
-        <v>7068977</v>
+        <v>7069114</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6764,6 +6779,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6790,10 +6810,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120040184</v>
+        <v>120040148</v>
       </c>
       <c r="B60" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6802,25 +6822,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6830,10 +6850,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>477481</v>
+        <v>477438</v>
       </c>
       <c r="R60" t="n">
-        <v>7069004</v>
+        <v>7069178</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6866,6 +6886,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6892,10 +6917,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120040175</v>
+        <v>120040190</v>
       </c>
       <c r="B61" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6904,58 +6929,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>477822</v>
+        <v>477530</v>
       </c>
       <c r="R61" t="n">
-        <v>7069037</v>
+        <v>7069276</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7014,7 +7019,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120040174</v>
+        <v>120040147</v>
       </c>
       <c r="B62" t="n">
         <v>57320</v>
@@ -7054,10 +7059,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>477825</v>
+        <v>477581</v>
       </c>
       <c r="R62" t="n">
-        <v>7069031</v>
+        <v>7069095</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7121,10 +7126,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120040161</v>
+        <v>120040204</v>
       </c>
       <c r="B63" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7137,21 +7142,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7161,10 +7166,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>477426</v>
+        <v>477534</v>
       </c>
       <c r="R63" t="n">
-        <v>7068947</v>
+        <v>7069288</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7197,11 +7202,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7228,10 +7228,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120040136</v>
+        <v>120040207</v>
       </c>
       <c r="B64" t="n">
-        <v>90580</v>
+        <v>86895</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7244,21 +7244,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7268,10 +7268,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>477434</v>
+        <v>477473</v>
       </c>
       <c r="R64" t="n">
-        <v>7069116</v>
+        <v>7069007</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>

--- a/artfynd/A 36309-2024 artfynd.xlsx
+++ b/artfynd/A 36309-2024 artfynd.xlsx
@@ -4382,10 +4382,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120040199</v>
+        <v>120040146</v>
       </c>
       <c r="B37" t="n">
-        <v>90576</v>
+        <v>57320</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4398,21 +4398,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4422,10 +4422,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>477671</v>
+        <v>477599</v>
       </c>
       <c r="R37" t="n">
-        <v>7068973</v>
+        <v>7069105</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4458,6 +4458,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4484,10 +4489,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120040146</v>
+        <v>120040199</v>
       </c>
       <c r="B38" t="n">
-        <v>57320</v>
+        <v>90576</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4500,21 +4505,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4524,10 +4529,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>477599</v>
+        <v>477671</v>
       </c>
       <c r="R38" t="n">
-        <v>7069105</v>
+        <v>7068973</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4560,11 +4565,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">

--- a/artfynd/A 36309-2024 artfynd.xlsx
+++ b/artfynd/A 36309-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY64"/>
+  <dimension ref="A1:AY72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7328,6 +7328,822 @@
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>129443108</v>
+      </c>
+      <c r="B65" t="n">
+        <v>79043</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Naturskog vid Svarttjärnen, ca 8,5 km norr om Föllinge, Jmt</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>477451</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7068947</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>Stamtät och självgallrande grannaturskog, sannolikt uppkommen efter brand långt tillbaks i historien</t>
+        </is>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>129443105</v>
+      </c>
+      <c r="B66" t="n">
+        <v>88943</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>510</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Naturskog vid Svarttjärnen, ca 8,5 km norr om Föllinge, Jmt</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>477510</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7068988</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>Stamtät och självgallrande grannaturskog, sannolikt uppkommen efter brand långt tillbaks i historien</t>
+        </is>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>129443102</v>
+      </c>
+      <c r="B67" t="n">
+        <v>92266</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>67</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Sprickporing</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Diplomitoporus crustulinus</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Bres.) Domański</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Naturskog vid Svarttjärnen, ca 8,5 km norr om Föllinge, Jmt</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>477562</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7069004</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>Stamtät och självgallrande grannaturskog, sannolikt uppkommen efter brand långt tillbaks i historien</t>
+        </is>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>129443107</v>
+      </c>
+      <c r="B68" t="n">
+        <v>98710</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Naturskog vid Svarttjärnen, ca 8,5 km norr om Föllinge, Jmt</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>477463</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7068940</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>Stamtät och självgallrande grannaturskog, sannolikt uppkommen efter brand långt tillbaks i historien</t>
+        </is>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>129443106</v>
+      </c>
+      <c r="B69" t="n">
+        <v>80108</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Naturskog vid Svarttjärnen, ca 8,5 km norr om Föllinge, Jmt</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>477518</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7069261</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>Stamtät och självgallrande grannaturskog, sannolikt uppkommen efter brand långt tillbaks i historien</t>
+        </is>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>129443110</v>
+      </c>
+      <c r="B70" t="n">
+        <v>88794</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>4405</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Diskvaxskivling</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Hygrophorus discoideus</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Pers.) Fr.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Naturskog vid Svarttjärnen, ca 8,5 km norr om Föllinge, Jmt</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>477490</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7068993</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI70" t="inlineStr">
+        <is>
+          <t>Stamtät grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>129443104</v>
+      </c>
+      <c r="B71" t="n">
+        <v>91543</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Naturskog vid Svarttjärnen, ca 8,5 km norr om Föllinge, Jmt</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>477551</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7068998</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI71" t="inlineStr">
+        <is>
+          <t>Stamtät och självgallrande grannaturskog, sannolikt uppkommen efter brand långt tillbaks i historien</t>
+        </is>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>129443103</v>
+      </c>
+      <c r="B72" t="n">
+        <v>92363</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>2014</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Koralltaggsvamp</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Hericium coralloides</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Scop.) Pers.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Naturskog vid Svarttjärnen, ca 8,5 km norr om Föllinge, Jmt</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>477498</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7069244</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI72" t="inlineStr">
+        <is>
+          <t>Stamtät och självgallrande grannaturskog, sannolikt uppkommen efter brand långt tillbaks i historien</t>
+        </is>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 36309-2024 artfynd.xlsx
+++ b/artfynd/A 36309-2024 artfynd.xlsx
@@ -7333,7 +7333,7 @@
         <v>129443108</v>
       </c>
       <c r="B65" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7435,7 +7435,7 @@
         <v>129443105</v>
       </c>
       <c r="B66" t="n">
-        <v>88943</v>
+        <v>88945</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7537,7 +7537,7 @@
         <v>129443102</v>
       </c>
       <c r="B67" t="n">
-        <v>92266</v>
+        <v>92268</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         <v>129443107</v>
       </c>
       <c r="B68" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7741,7 +7741,7 @@
         <v>129443106</v>
       </c>
       <c r="B69" t="n">
-        <v>80108</v>
+        <v>80109</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7843,7 +7843,7 @@
         <v>129443110</v>
       </c>
       <c r="B70" t="n">
-        <v>88794</v>
+        <v>88796</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7945,7 +7945,7 @@
         <v>129443104</v>
       </c>
       <c r="B71" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8047,7 +8047,7 @@
         <v>129443103</v>
       </c>
       <c r="B72" t="n">
-        <v>92363</v>
+        <v>92365</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 36309-2024 artfynd.xlsx
+++ b/artfynd/A 36309-2024 artfynd.xlsx
@@ -7435,7 +7435,7 @@
         <v>129443105</v>
       </c>
       <c r="B66" t="n">
-        <v>88945</v>
+        <v>88949</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7537,7 +7537,7 @@
         <v>129443102</v>
       </c>
       <c r="B67" t="n">
-        <v>92268</v>
+        <v>92272</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         <v>129443107</v>
       </c>
       <c r="B68" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7843,7 +7843,7 @@
         <v>129443110</v>
       </c>
       <c r="B70" t="n">
-        <v>88796</v>
+        <v>88800</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7945,7 +7945,7 @@
         <v>129443104</v>
       </c>
       <c r="B71" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8047,7 +8047,7 @@
         <v>129443103</v>
       </c>
       <c r="B72" t="n">
-        <v>92365</v>
+        <v>92369</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 36309-2024 artfynd.xlsx
+++ b/artfynd/A 36309-2024 artfynd.xlsx
@@ -7435,7 +7435,7 @@
         <v>129443105</v>
       </c>
       <c r="B66" t="n">
-        <v>88949</v>
+        <v>88950</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7537,7 +7537,7 @@
         <v>129443102</v>
       </c>
       <c r="B67" t="n">
-        <v>92272</v>
+        <v>92273</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         <v>129443107</v>
       </c>
       <c r="B68" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7843,7 +7843,7 @@
         <v>129443110</v>
       </c>
       <c r="B70" t="n">
-        <v>88800</v>
+        <v>88801</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7945,7 +7945,7 @@
         <v>129443104</v>
       </c>
       <c r="B71" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8047,7 +8047,7 @@
         <v>129443103</v>
       </c>
       <c r="B72" t="n">
-        <v>92369</v>
+        <v>92370</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 36309-2024 artfynd.xlsx
+++ b/artfynd/A 36309-2024 artfynd.xlsx
@@ -7435,7 +7435,7 @@
         <v>129443105</v>
       </c>
       <c r="B66" t="n">
-        <v>88950</v>
+        <v>88952</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7537,7 +7537,7 @@
         <v>129443102</v>
       </c>
       <c r="B67" t="n">
-        <v>92273</v>
+        <v>92276</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         <v>129443107</v>
       </c>
       <c r="B68" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7945,7 +7945,7 @@
         <v>129443104</v>
       </c>
       <c r="B71" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8047,7 +8047,7 @@
         <v>129443103</v>
       </c>
       <c r="B72" t="n">
-        <v>92370</v>
+        <v>92373</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 36309-2024 artfynd.xlsx
+++ b/artfynd/A 36309-2024 artfynd.xlsx
@@ -7333,7 +7333,7 @@
         <v>129443108</v>
       </c>
       <c r="B65" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7435,7 +7435,7 @@
         <v>129443105</v>
       </c>
       <c r="B66" t="n">
-        <v>88952</v>
+        <v>88980</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7537,7 +7537,7 @@
         <v>129443102</v>
       </c>
       <c r="B67" t="n">
-        <v>92276</v>
+        <v>92304</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         <v>129443107</v>
       </c>
       <c r="B68" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7741,7 +7741,7 @@
         <v>129443106</v>
       </c>
       <c r="B69" t="n">
-        <v>80109</v>
+        <v>80135</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7843,7 +7843,7 @@
         <v>129443110</v>
       </c>
       <c r="B70" t="n">
-        <v>88801</v>
+        <v>88829</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7945,7 +7945,7 @@
         <v>129443104</v>
       </c>
       <c r="B71" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8047,7 +8047,7 @@
         <v>129443103</v>
       </c>
       <c r="B72" t="n">
-        <v>92373</v>
+        <v>92401</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 36309-2024 artfynd.xlsx
+++ b/artfynd/A 36309-2024 artfynd.xlsx
@@ -7333,7 +7333,7 @@
         <v>129443108</v>
       </c>
       <c r="B65" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7435,7 +7435,7 @@
         <v>129443105</v>
       </c>
       <c r="B66" t="n">
-        <v>88980</v>
+        <v>88986</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7537,7 +7537,7 @@
         <v>129443102</v>
       </c>
       <c r="B67" t="n">
-        <v>92304</v>
+        <v>92310</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         <v>129443107</v>
       </c>
       <c r="B68" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7741,7 +7741,7 @@
         <v>129443106</v>
       </c>
       <c r="B69" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7843,7 +7843,7 @@
         <v>129443110</v>
       </c>
       <c r="B70" t="n">
-        <v>88829</v>
+        <v>88835</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7945,7 +7945,7 @@
         <v>129443104</v>
       </c>
       <c r="B71" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8047,7 +8047,7 @@
         <v>129443103</v>
       </c>
       <c r="B72" t="n">
-        <v>92401</v>
+        <v>92407</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 36309-2024 artfynd.xlsx
+++ b/artfynd/A 36309-2024 artfynd.xlsx
@@ -7333,7 +7333,7 @@
         <v>129443108</v>
       </c>
       <c r="B65" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7435,7 +7435,7 @@
         <v>129443105</v>
       </c>
       <c r="B66" t="n">
-        <v>88986</v>
+        <v>88987</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7537,7 +7537,7 @@
         <v>129443102</v>
       </c>
       <c r="B67" t="n">
-        <v>92310</v>
+        <v>92311</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         <v>129443107</v>
       </c>
       <c r="B68" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7741,7 +7741,7 @@
         <v>129443106</v>
       </c>
       <c r="B69" t="n">
-        <v>80140</v>
+        <v>80141</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7843,7 +7843,7 @@
         <v>129443110</v>
       </c>
       <c r="B70" t="n">
-        <v>88835</v>
+        <v>88836</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7945,7 +7945,7 @@
         <v>129443104</v>
       </c>
       <c r="B71" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8047,7 +8047,7 @@
         <v>129443103</v>
       </c>
       <c r="B72" t="n">
-        <v>92407</v>
+        <v>92408</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 36309-2024 artfynd.xlsx
+++ b/artfynd/A 36309-2024 artfynd.xlsx
@@ -7333,7 +7333,7 @@
         <v>129443108</v>
       </c>
       <c r="B65" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7435,7 +7435,7 @@
         <v>129443105</v>
       </c>
       <c r="B66" t="n">
-        <v>88987</v>
+        <v>88992</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7537,7 +7537,7 @@
         <v>129443102</v>
       </c>
       <c r="B67" t="n">
-        <v>92311</v>
+        <v>92316</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         <v>129443107</v>
       </c>
       <c r="B68" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7741,7 +7741,7 @@
         <v>129443106</v>
       </c>
       <c r="B69" t="n">
-        <v>80141</v>
+        <v>80146</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7843,7 +7843,7 @@
         <v>129443110</v>
       </c>
       <c r="B70" t="n">
-        <v>88836</v>
+        <v>88841</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7945,7 +7945,7 @@
         <v>129443104</v>
       </c>
       <c r="B71" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8047,7 +8047,7 @@
         <v>129443103</v>
       </c>
       <c r="B72" t="n">
-        <v>92408</v>
+        <v>92413</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 36309-2024 artfynd.xlsx
+++ b/artfynd/A 36309-2024 artfynd.xlsx
@@ -7435,7 +7435,7 @@
         <v>129443105</v>
       </c>
       <c r="B66" t="n">
-        <v>88992</v>
+        <v>88996</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7537,7 +7537,7 @@
         <v>129443102</v>
       </c>
       <c r="B67" t="n">
-        <v>92316</v>
+        <v>92320</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         <v>129443107</v>
       </c>
       <c r="B68" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7843,7 +7843,7 @@
         <v>129443110</v>
       </c>
       <c r="B70" t="n">
-        <v>88841</v>
+        <v>88845</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7945,7 +7945,7 @@
         <v>129443104</v>
       </c>
       <c r="B71" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8047,7 +8047,7 @@
         <v>129443103</v>
       </c>
       <c r="B72" t="n">
-        <v>92413</v>
+        <v>92417</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 36309-2024 artfynd.xlsx
+++ b/artfynd/A 36309-2024 artfynd.xlsx
@@ -7435,7 +7435,7 @@
         <v>129443105</v>
       </c>
       <c r="B66" t="n">
-        <v>88996</v>
+        <v>88998</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7537,7 +7537,7 @@
         <v>129443102</v>
       </c>
       <c r="B67" t="n">
-        <v>92320</v>
+        <v>92322</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         <v>129443107</v>
       </c>
       <c r="B68" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7843,7 +7843,7 @@
         <v>129443110</v>
       </c>
       <c r="B70" t="n">
-        <v>88845</v>
+        <v>88847</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7945,7 +7945,7 @@
         <v>129443104</v>
       </c>
       <c r="B71" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8047,7 +8047,7 @@
         <v>129443103</v>
       </c>
       <c r="B72" t="n">
-        <v>92417</v>
+        <v>92419</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 36309-2024 artfynd.xlsx
+++ b/artfynd/A 36309-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY72"/>
+  <dimension ref="A1:AY69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120040152</v>
+        <v>129443102</v>
       </c>
       <c r="B2" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92637</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>67</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Jmt</t>
+          <t>Naturskog vid Svarttjärnen, ca 8,5 km norr om Föllinge, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477472</v>
+        <v>477562</v>
       </c>
       <c r="R2" t="n">
-        <v>7069168</v>
+        <v>7069004</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,17 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -766,31 +756,31 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Stamtät och självgallrande grannaturskog, sannolikt uppkommen efter brand långt tillbaks i historien</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120040175</v>
+        <v>120040207</v>
       </c>
       <c r="B3" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,54 +788,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477822</v>
+        <v>477473</v>
       </c>
       <c r="R3" t="n">
-        <v>7069037</v>
+        <v>7069007</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -904,15 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120040145</v>
+        <v>129443105</v>
       </c>
       <c r="B4" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,34 +885,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Jmt</t>
+          <t>Naturskog vid Svarttjärnen, ca 8,5 km norr om Föllinge, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477626</v>
+        <v>477510</v>
       </c>
       <c r="R4" t="n">
-        <v>7069105</v>
+        <v>7068988</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,17 +939,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -995,31 +955,31 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Stamtät och självgallrande grannaturskog, sannolikt uppkommen efter brand långt tillbaks i historien</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120040136</v>
+        <v>120040199</v>
       </c>
       <c r="B5" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,21 +987,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477434</v>
+        <v>477671</v>
       </c>
       <c r="R5" t="n">
-        <v>7069116</v>
+        <v>7068973</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1113,15 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120040199</v>
+        <v>120040134</v>
       </c>
       <c r="B6" t="n">
-        <v>90576</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1129,21 +1084,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1153,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477671</v>
+        <v>477522</v>
       </c>
       <c r="R6" t="n">
-        <v>7068973</v>
+        <v>7068987</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,15 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120040139</v>
+        <v>120040135</v>
       </c>
       <c r="B7" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1231,21 +1181,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1255,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477517</v>
+        <v>477507</v>
       </c>
       <c r="R7" t="n">
-        <v>7068992</v>
+        <v>7069055</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1291,11 +1241,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1322,15 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120040146</v>
+        <v>120040136</v>
       </c>
       <c r="B8" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1338,21 +1278,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1362,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477599</v>
+        <v>477434</v>
       </c>
       <c r="R8" t="n">
-        <v>7069105</v>
+        <v>7069116</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1398,11 +1338,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1429,15 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120040202</v>
+        <v>129443104</v>
       </c>
       <c r="B9" t="n">
-        <v>90598</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1445,34 +1375,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Jmt</t>
+          <t>Naturskog vid Svarttjärnen, ca 8,5 km norr om Föllinge, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>477674</v>
+        <v>477551</v>
       </c>
       <c r="R9" t="n">
-        <v>7069000</v>
+        <v>7068998</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,12 +1429,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1515,31 +1445,31 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Stamtät och självgallrande grannaturskog, sannolikt uppkommen efter brand långt tillbaks i historien</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120040180</v>
+        <v>129443103</v>
       </c>
       <c r="B10" t="n">
-        <v>79623</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92732</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1547,34 +1477,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>2014</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Jmt</t>
+          <t>Naturskog vid Svarttjärnen, ca 8,5 km norr om Föllinge, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>477415</v>
+        <v>477498</v>
       </c>
       <c r="R10" t="n">
-        <v>7069070</v>
+        <v>7069244</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,12 +1531,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1617,31 +1547,31 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Stamtät och självgallrande grannaturskog, sannolikt uppkommen efter brand långt tillbaks i historien</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120040176</v>
+        <v>120040179</v>
       </c>
       <c r="B11" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1649,21 +1579,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1603,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>477852</v>
+        <v>477437</v>
       </c>
       <c r="R11" t="n">
-        <v>7069022</v>
+        <v>7068991</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,11 +1639,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack ganska färska till äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1740,50 +1665,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120040201</v>
+        <v>129443110</v>
       </c>
       <c r="B12" t="n">
-        <v>90598</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89143</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>4405</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Jmt</t>
+          <t>Naturskog vid Svarttjärnen, ca 8,5 km norr om Föllinge, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>477484</v>
+        <v>477490</v>
       </c>
       <c r="R12" t="n">
-        <v>7068927</v>
+        <v>7068993</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1810,12 +1730,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1826,31 +1746,31 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Stamtät grannaturskog</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120040188</v>
+        <v>120040203</v>
       </c>
       <c r="B13" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1858,21 +1778,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1882,10 +1802,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>477454</v>
+        <v>477472</v>
       </c>
       <c r="R13" t="n">
-        <v>7069190</v>
+        <v>7069087</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1944,37 +1864,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120040160</v>
+        <v>120040204</v>
       </c>
       <c r="B14" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1984,10 +1899,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>477440</v>
+        <v>477534</v>
       </c>
       <c r="R14" t="n">
-        <v>7068958</v>
+        <v>7069288</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2020,11 +1935,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2051,62 +1961,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120040183</v>
+        <v>120040205</v>
       </c>
       <c r="B15" t="n">
-        <v>57431</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>477821</v>
+        <v>477382</v>
       </c>
       <c r="R15" t="n">
-        <v>7069026</v>
+        <v>7069247</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2165,15 +2058,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120040187</v>
+        <v>120040206</v>
       </c>
       <c r="B16" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2181,21 +2069,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2205,10 +2093,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>477525</v>
+        <v>477405</v>
       </c>
       <c r="R16" t="n">
-        <v>7069106</v>
+        <v>7069105</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2267,50 +2155,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120040207</v>
+        <v>129443108</v>
       </c>
       <c r="B17" t="n">
-        <v>86895</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Jmt</t>
+          <t>Naturskog vid Svarttjärnen, ca 8,5 km norr om Föllinge, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>477473</v>
+        <v>477451</v>
       </c>
       <c r="R17" t="n">
-        <v>7069007</v>
+        <v>7068947</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2337,12 +2220,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2353,31 +2236,31 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Stamtät och självgallrande grannaturskog, sannolikt uppkommen efter brand långt tillbaks i historien</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120040164</v>
+        <v>120040180</v>
       </c>
       <c r="B18" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2385,21 +2268,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2409,10 +2292,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>477597</v>
+        <v>477415</v>
       </c>
       <c r="R18" t="n">
-        <v>7068964</v>
+        <v>7069070</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2445,11 +2328,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2476,15 +2354,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120040149</v>
+        <v>120040181</v>
       </c>
       <c r="B19" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2492,21 +2365,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2516,10 +2389,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>477423</v>
+        <v>477437</v>
       </c>
       <c r="R19" t="n">
-        <v>7069180</v>
+        <v>7068991</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2552,11 +2425,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2583,15 +2451,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120040203</v>
+        <v>120040138</v>
       </c>
       <c r="B20" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2599,21 +2462,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2623,10 +2486,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>477472</v>
+        <v>477726</v>
       </c>
       <c r="R20" t="n">
-        <v>7069087</v>
+        <v>7069062</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2659,6 +2522,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2685,37 +2553,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120040191</v>
+        <v>120040139</v>
       </c>
       <c r="B21" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2725,10 +2588,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>477440</v>
+        <v>477517</v>
       </c>
       <c r="R21" t="n">
-        <v>7069251</v>
+        <v>7068992</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2761,6 +2624,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2787,15 +2655,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120040173</v>
+        <v>120040140</v>
       </c>
       <c r="B22" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2827,10 +2690,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>477786</v>
+        <v>477472</v>
       </c>
       <c r="R22" t="n">
-        <v>7069029</v>
+        <v>7069006</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2894,15 +2757,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120040140</v>
+        <v>120040141</v>
       </c>
       <c r="B23" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2934,10 +2792,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>477472</v>
+        <v>477562</v>
       </c>
       <c r="R23" t="n">
-        <v>7069006</v>
+        <v>7069078</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3001,15 +2859,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120040158</v>
+        <v>120040142</v>
       </c>
       <c r="B24" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3041,10 +2894,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>477446</v>
+        <v>477614</v>
       </c>
       <c r="R24" t="n">
-        <v>7069039</v>
+        <v>7069089</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3081,7 +2934,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3108,15 +2961,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120040200</v>
+        <v>120040144</v>
       </c>
       <c r="B25" t="n">
-        <v>90598</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3124,21 +2972,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3148,10 +2996,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>477439</v>
+        <v>477644</v>
       </c>
       <c r="R25" t="n">
-        <v>7069086</v>
+        <v>7069114</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3184,6 +3032,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3210,15 +3063,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120040154</v>
+        <v>120040145</v>
       </c>
       <c r="B26" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3250,10 +3098,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>477476</v>
+        <v>477626</v>
       </c>
       <c r="R26" t="n">
-        <v>7069264</v>
+        <v>7069105</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3317,15 +3165,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120040138</v>
+        <v>120040146</v>
       </c>
       <c r="B27" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3357,10 +3200,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>477726</v>
+        <v>477599</v>
       </c>
       <c r="R27" t="n">
-        <v>7069062</v>
+        <v>7069105</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3424,15 +3267,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120040169</v>
+        <v>120040147</v>
       </c>
       <c r="B28" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3464,10 +3302,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>477688</v>
+        <v>477581</v>
       </c>
       <c r="R28" t="n">
-        <v>7069010</v>
+        <v>7069095</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3531,15 +3369,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120040170</v>
+        <v>120040148</v>
       </c>
       <c r="B29" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3571,10 +3404,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>477755</v>
+        <v>477438</v>
       </c>
       <c r="R29" t="n">
-        <v>7069016</v>
+        <v>7069178</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3638,15 +3471,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120040166</v>
+        <v>120040149</v>
       </c>
       <c r="B30" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3678,10 +3506,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>477622</v>
+        <v>477423</v>
       </c>
       <c r="R30" t="n">
-        <v>7068965</v>
+        <v>7069180</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3718,7 +3546,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3745,15 +3573,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120040155</v>
+        <v>120040150</v>
       </c>
       <c r="B31" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3785,10 +3608,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>477377</v>
+        <v>477457</v>
       </c>
       <c r="R31" t="n">
-        <v>7069208</v>
+        <v>7069186</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3852,15 +3675,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120040153</v>
+        <v>120040151</v>
       </c>
       <c r="B32" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3892,10 +3710,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>477547</v>
+        <v>477460</v>
       </c>
       <c r="R32" t="n">
-        <v>7069271</v>
+        <v>7069166</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3932,7 +3750,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och något äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3959,15 +3777,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120040205</v>
+        <v>120040152</v>
       </c>
       <c r="B33" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3975,21 +3788,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3999,10 +3812,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>477382</v>
+        <v>477472</v>
       </c>
       <c r="R33" t="n">
-        <v>7069247</v>
+        <v>7069168</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4035,6 +3848,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4061,15 +3879,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120040165</v>
+        <v>120040153</v>
       </c>
       <c r="B34" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4101,10 +3914,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>477596</v>
+        <v>477547</v>
       </c>
       <c r="R34" t="n">
-        <v>7068950</v>
+        <v>7069271</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4141,7 +3954,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4168,15 +3981,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120040157</v>
+        <v>120040154</v>
       </c>
       <c r="B35" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4208,10 +4016,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>477397</v>
+        <v>477476</v>
       </c>
       <c r="R35" t="n">
-        <v>7069068</v>
+        <v>7069264</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4248,7 +4056,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4275,15 +4083,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120040150</v>
+        <v>120040155</v>
       </c>
       <c r="B36" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4315,10 +4118,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>477457</v>
+        <v>477377</v>
       </c>
       <c r="R36" t="n">
-        <v>7069186</v>
+        <v>7069208</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4382,15 +4185,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120040174</v>
+        <v>120040157</v>
       </c>
       <c r="B37" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4422,10 +4220,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>477825</v>
+        <v>477397</v>
       </c>
       <c r="R37" t="n">
-        <v>7069031</v>
+        <v>7069068</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4462,7 +4260,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4489,15 +4287,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120040171</v>
+        <v>120040158</v>
       </c>
       <c r="B38" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4529,10 +4322,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>477759</v>
+        <v>477446</v>
       </c>
       <c r="R38" t="n">
-        <v>7069019</v>
+        <v>7069039</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4569,7 +4362,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4596,15 +4389,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120040163</v>
+        <v>120040159</v>
       </c>
       <c r="B39" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4636,10 +4424,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>477544</v>
+        <v>477444</v>
       </c>
       <c r="R39" t="n">
-        <v>7068952</v>
+        <v>7068963</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4676,7 +4464,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack ganska färska till äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4703,15 +4491,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120040144</v>
+        <v>120040160</v>
       </c>
       <c r="B40" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4743,10 +4526,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>477644</v>
+        <v>477440</v>
       </c>
       <c r="R40" t="n">
-        <v>7069114</v>
+        <v>7068958</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4810,37 +4593,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120040192</v>
+        <v>120040161</v>
       </c>
       <c r="B41" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4850,10 +4628,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>477445</v>
+        <v>477426</v>
       </c>
       <c r="R41" t="n">
-        <v>7068977</v>
+        <v>7068947</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4886,6 +4664,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4912,15 +4695,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120040181</v>
+        <v>120040162</v>
       </c>
       <c r="B42" t="n">
-        <v>79623</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4928,21 +4706,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4952,10 +4730,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>477437</v>
+        <v>477471</v>
       </c>
       <c r="R42" t="n">
-        <v>7068991</v>
+        <v>7068928</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4988,6 +4766,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5014,15 +4797,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120040177</v>
+        <v>120040163</v>
       </c>
       <c r="B43" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5054,10 +4832,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>477856</v>
+        <v>477544</v>
       </c>
       <c r="R43" t="n">
-        <v>7069020</v>
+        <v>7068952</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5094,7 +4872,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5121,15 +4899,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120040141</v>
+        <v>120040164</v>
       </c>
       <c r="B44" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5161,10 +4934,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>477562</v>
+        <v>477597</v>
       </c>
       <c r="R44" t="n">
-        <v>7069078</v>
+        <v>7068964</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5201,7 +4974,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5228,37 +5001,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120040189</v>
+        <v>120040165</v>
       </c>
       <c r="B45" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5268,10 +5036,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>477498</v>
+        <v>477596</v>
       </c>
       <c r="R45" t="n">
-        <v>7069206</v>
+        <v>7068950</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5304,6 +5072,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5330,15 +5103,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120040179</v>
+        <v>120040166</v>
       </c>
       <c r="B46" t="n">
-        <v>79624</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5346,21 +5114,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5370,10 +5138,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>477437</v>
+        <v>477622</v>
       </c>
       <c r="R46" t="n">
-        <v>7068991</v>
+        <v>7068965</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5406,6 +5174,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5432,15 +5205,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120040142</v>
+        <v>120040167</v>
       </c>
       <c r="B47" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5472,10 +5240,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>477614</v>
+        <v>477641</v>
       </c>
       <c r="R47" t="n">
-        <v>7069089</v>
+        <v>7068958</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5512,7 +5280,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack ganska färska</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5539,37 +5307,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120040184</v>
+        <v>120040168</v>
       </c>
       <c r="B48" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5579,10 +5342,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>477481</v>
+        <v>477664</v>
       </c>
       <c r="R48" t="n">
-        <v>7069004</v>
+        <v>7068971</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5615,6 +5378,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5641,15 +5409,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120040162</v>
+        <v>120040169</v>
       </c>
       <c r="B49" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5681,10 +5444,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>477471</v>
+        <v>477688</v>
       </c>
       <c r="R49" t="n">
-        <v>7068928</v>
+        <v>7069010</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5748,15 +5511,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120040147</v>
+        <v>120040170</v>
       </c>
       <c r="B50" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5788,10 +5546,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>477581</v>
+        <v>477755</v>
       </c>
       <c r="R50" t="n">
-        <v>7069095</v>
+        <v>7069016</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5855,15 +5613,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120040206</v>
+        <v>120040171</v>
       </c>
       <c r="B51" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5871,21 +5624,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5895,10 +5648,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>477405</v>
+        <v>477759</v>
       </c>
       <c r="R51" t="n">
-        <v>7069105</v>
+        <v>7069019</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5931,6 +5684,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5957,15 +5715,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120040135</v>
+        <v>120040172</v>
       </c>
       <c r="B52" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5973,21 +5726,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5997,10 +5750,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>477507</v>
+        <v>477777</v>
       </c>
       <c r="R52" t="n">
-        <v>7069055</v>
+        <v>7069022</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6033,6 +5786,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6059,15 +5817,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120040172</v>
+        <v>120040173</v>
       </c>
       <c r="B53" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6099,10 +5852,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>477777</v>
+        <v>477786</v>
       </c>
       <c r="R53" t="n">
-        <v>7069022</v>
+        <v>7069029</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6166,15 +5919,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120040151</v>
+        <v>120040174</v>
       </c>
       <c r="B54" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6206,10 +5954,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>477460</v>
+        <v>477825</v>
       </c>
       <c r="R54" t="n">
-        <v>7069166</v>
+        <v>7069031</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6246,7 +5994,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack färska och något äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6273,15 +6021,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120040168</v>
+        <v>120040175</v>
       </c>
       <c r="B55" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6306,17 +6049,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>477664</v>
+        <v>477822</v>
       </c>
       <c r="R55" t="n">
-        <v>7068971</v>
+        <v>7069037</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6349,11 +6112,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6380,15 +6138,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120040204</v>
+        <v>120040176</v>
       </c>
       <c r="B56" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6396,21 +6149,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6420,10 +6173,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>477534</v>
+        <v>477852</v>
       </c>
       <c r="R56" t="n">
-        <v>7069288</v>
+        <v>7069022</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6456,6 +6209,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack ganska färska till äldre</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6482,15 +6240,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120040159</v>
+        <v>120040177</v>
       </c>
       <c r="B57" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6522,10 +6275,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>477444</v>
+        <v>477856</v>
       </c>
       <c r="R57" t="n">
-        <v>7068963</v>
+        <v>7069020</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6562,7 +6315,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack ganska färska till äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6589,15 +6342,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120040134</v>
+        <v>120040182</v>
       </c>
       <c r="B58" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6605,34 +6353,46 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>103031</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>477522</v>
+        <v>477760</v>
       </c>
       <c r="R58" t="n">
-        <v>7068987</v>
+        <v>7069037</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6691,50 +6451,57 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120040190</v>
+        <v>120040183</v>
       </c>
       <c r="B59" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>477530</v>
+        <v>477821</v>
       </c>
       <c r="R59" t="n">
-        <v>7069276</v>
+        <v>7069026</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6793,15 +6560,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120040185</v>
+        <v>120040184</v>
       </c>
       <c r="B60" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6833,10 +6595,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>477507</v>
+        <v>477481</v>
       </c>
       <c r="R60" t="n">
-        <v>7069056</v>
+        <v>7069004</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6895,37 +6657,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120040148</v>
+        <v>120040185</v>
       </c>
       <c r="B61" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6935,10 +6692,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>477438</v>
+        <v>477507</v>
       </c>
       <c r="R61" t="n">
-        <v>7069178</v>
+        <v>7069056</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6971,11 +6728,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7002,37 +6754,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120040167</v>
+        <v>120040187</v>
       </c>
       <c r="B62" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7042,10 +6789,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>477641</v>
+        <v>477525</v>
       </c>
       <c r="R62" t="n">
-        <v>7068958</v>
+        <v>7069106</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7078,11 +6825,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Ringhack ganska färska</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7109,62 +6851,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120040182</v>
+        <v>120040188</v>
       </c>
       <c r="B63" t="n">
-        <v>57431</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103031</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>477760</v>
+        <v>477454</v>
       </c>
       <c r="R63" t="n">
-        <v>7069037</v>
+        <v>7069190</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7223,37 +6948,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120040161</v>
+        <v>120040189</v>
       </c>
       <c r="B64" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7263,10 +6983,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>477426</v>
+        <v>477498</v>
       </c>
       <c r="R64" t="n">
-        <v>7068947</v>
+        <v>7069206</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7299,11 +7019,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7330,45 +7045,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129443108</v>
+        <v>120040190</v>
       </c>
       <c r="B65" t="n">
-        <v>79081</v>
+        <v>99118</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Naturskog vid Svarttjärnen, ca 8,5 km norr om Föllinge, Jmt</t>
+          <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>477451</v>
+        <v>477530</v>
       </c>
       <c r="R65" t="n">
-        <v>7068947</v>
+        <v>7069276</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7395,12 +7110,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7411,66 +7126,61 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
-      </c>
-      <c r="AI65" t="inlineStr">
-        <is>
-          <t>Stamtät och självgallrande grannaturskog, sannolikt uppkommen efter brand långt tillbaks i historien</t>
-        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129443105</v>
+        <v>120040191</v>
       </c>
       <c r="B66" t="n">
-        <v>88998</v>
+        <v>99118</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>510</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Naturskog vid Svarttjärnen, ca 8,5 km norr om Föllinge, Jmt</t>
+          <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>477510</v>
+        <v>477440</v>
       </c>
       <c r="R66" t="n">
-        <v>7068988</v>
+        <v>7069251</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7497,12 +7207,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7513,31 +7223,26 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
-      </c>
-      <c r="AI66" t="inlineStr">
-        <is>
-          <t>Stamtät och självgallrande grannaturskog, sannolikt uppkommen efter brand långt tillbaks i historien</t>
-        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129443102</v>
+        <v>120040192</v>
       </c>
       <c r="B67" t="n">
-        <v>92322</v>
+        <v>99118</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7545,34 +7250,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>67</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Naturskog vid Svarttjärnen, ca 8,5 km norr om Föllinge, Jmt</t>
+          <t>Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>477562</v>
+        <v>477445</v>
       </c>
       <c r="R67" t="n">
-        <v>7069004</v>
+        <v>7068977</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7599,12 +7304,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7615,21 +7320,16 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
-      </c>
-      <c r="AI67" t="inlineStr">
-        <is>
-          <t>Stamtät och självgallrande grannaturskog, sannolikt uppkommen efter brand långt tillbaks i historien</t>
-        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -7639,7 +7339,7 @@
         <v>129443107</v>
       </c>
       <c r="B68" t="n">
-        <v>98780</v>
+        <v>99118</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7741,7 +7441,7 @@
         <v>129443106</v>
       </c>
       <c r="B69" t="n">
-        <v>80146</v>
+        <v>80392</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7837,312 +7537,6 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>129443110</v>
-      </c>
-      <c r="B70" t="n">
-        <v>88847</v>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E70" t="n">
-        <v>4405</v>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Diskvaxskivling</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>Hygrophorus discoideus</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>(Pers.) Fr.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>Naturskog vid Svarttjärnen, ca 8,5 km norr om Föllinge, Jmt</t>
-        </is>
-      </c>
-      <c r="Q70" t="n">
-        <v>477490</v>
-      </c>
-      <c r="R70" t="n">
-        <v>7068993</v>
-      </c>
-      <c r="S70" t="n">
-        <v>10</v>
-      </c>
-      <c r="T70" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U70" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V70" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W70" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y70" t="inlineStr">
-        <is>
-          <t>2025-10-31</t>
-        </is>
-      </c>
-      <c r="AA70" t="inlineStr">
-        <is>
-          <t>2025-10-31</t>
-        </is>
-      </c>
-      <c r="AD70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI70" t="inlineStr">
-        <is>
-          <t>Stamtät grannaturskog</t>
-        </is>
-      </c>
-      <c r="AT70" t="inlineStr"/>
-      <c r="AW70" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY70" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
-        <v>129443104</v>
-      </c>
-      <c r="B71" t="n">
-        <v>91599</v>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E71" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t>Naturskog vid Svarttjärnen, ca 8,5 km norr om Föllinge, Jmt</t>
-        </is>
-      </c>
-      <c r="Q71" t="n">
-        <v>477551</v>
-      </c>
-      <c r="R71" t="n">
-        <v>7068998</v>
-      </c>
-      <c r="S71" t="n">
-        <v>10</v>
-      </c>
-      <c r="T71" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U71" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V71" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W71" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y71" t="inlineStr">
-        <is>
-          <t>2025-10-31</t>
-        </is>
-      </c>
-      <c r="AA71" t="inlineStr">
-        <is>
-          <t>2025-10-31</t>
-        </is>
-      </c>
-      <c r="AD71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI71" t="inlineStr">
-        <is>
-          <t>Stamtät och självgallrande grannaturskog, sannolikt uppkommen efter brand långt tillbaks i historien</t>
-        </is>
-      </c>
-      <c r="AT71" t="inlineStr"/>
-      <c r="AW71" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY71" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>129443103</v>
-      </c>
-      <c r="B72" t="n">
-        <v>92419</v>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E72" t="n">
-        <v>2014</v>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Koralltaggsvamp</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>Hericium coralloides</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>(Scop.) Pers.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="P72" t="inlineStr">
-        <is>
-          <t>Naturskog vid Svarttjärnen, ca 8,5 km norr om Föllinge, Jmt</t>
-        </is>
-      </c>
-      <c r="Q72" t="n">
-        <v>477498</v>
-      </c>
-      <c r="R72" t="n">
-        <v>7069244</v>
-      </c>
-      <c r="S72" t="n">
-        <v>10</v>
-      </c>
-      <c r="T72" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U72" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V72" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W72" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y72" t="inlineStr">
-        <is>
-          <t>2025-10-31</t>
-        </is>
-      </c>
-      <c r="AA72" t="inlineStr">
-        <is>
-          <t>2025-10-31</t>
-        </is>
-      </c>
-      <c r="AD72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI72" t="inlineStr">
-        <is>
-          <t>Stamtät och självgallrande grannaturskog, sannolikt uppkommen efter brand långt tillbaks i historien</t>
-        </is>
-      </c>
-      <c r="AT72" t="inlineStr"/>
-      <c r="AW72" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY72" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 36309-2024 artfynd.xlsx
+++ b/artfynd/A 36309-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY69"/>
+  <dimension ref="A1:AZ69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129443102</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120040207</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129443105</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,6 +1090,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120040199</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1167,6 +1192,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120040134</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1264,6 +1294,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120040135</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1361,6 +1396,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120040136</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1463,6 +1503,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129443104</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1565,6 +1610,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129443103</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1662,6 +1712,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120040179</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1764,6 +1819,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129443110</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1861,6 +1921,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120040203</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1958,6 +2023,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120040204</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2055,6 +2125,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120040205</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2152,6 +2227,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120040206</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2254,6 +2334,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129443108</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2351,6 +2436,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120040180</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2448,6 +2538,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120040181</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2550,6 +2645,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120040138</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2652,6 +2752,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120040139</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2754,6 +2859,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120040140</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2856,6 +2966,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120040141</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2958,6 +3073,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120040142</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3060,6 +3180,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120040144</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3162,6 +3287,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120040145</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3264,6 +3394,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120040146</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3366,6 +3501,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120040147</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3468,6 +3608,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120040148</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3570,6 +3715,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120040149</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3672,6 +3822,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120040150</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3774,6 +3929,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120040151</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3876,6 +4036,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120040152</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3978,6 +4143,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120040153</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4080,6 +4250,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120040154</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4182,6 +4357,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120040155</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4284,6 +4464,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120040157</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4386,6 +4571,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120040158</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4488,6 +4678,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120040159</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4590,6 +4785,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120040160</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4692,6 +4892,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120040161</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4794,6 +4999,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120040162</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4896,6 +5106,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120040163</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4998,6 +5213,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120040164</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5100,6 +5320,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120040165</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5202,6 +5427,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120040166</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5304,6 +5534,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120040167</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5406,6 +5641,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120040168</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5508,6 +5748,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120040169</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5610,6 +5855,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120040170</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5712,6 +5962,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120040171</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5814,6 +6069,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120040172</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5916,6 +6176,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120040173</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6018,6 +6283,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120040174</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6135,6 +6405,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120040175</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6237,6 +6512,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120040176</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6339,6 +6619,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120040177</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6448,6 +6733,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120040182</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6557,6 +6847,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120040183</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6654,6 +6949,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120040184</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6751,6 +7051,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120040185</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6848,6 +7153,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120040187</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6945,6 +7255,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120040188</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7042,6 +7357,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120040189</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7139,6 +7459,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120040190</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7236,6 +7561,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120040191</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7333,6 +7663,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120040192</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7435,6 +7770,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129443107</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7537,8 +7877,83 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129443106</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>